--- a/data/source/ontologies_source.xlsx
+++ b/data/source/ontologies_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbosche\Documents\GitHub\BE-OLS\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D2634B8-686F-4910-8802-3E189E150250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1294C1-FAEB-4722-96F6-46089FB9F58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="14" r:id="rId1"/>
@@ -390,7 +390,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2743" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="1092">
   <si>
     <t>BE Product (Building)</t>
   </si>
@@ -2655,9 +2655,6 @@
   </si>
   <si>
     <t>https://digiconstructlab-tu-delft.github.io/AiC-Ontology/</t>
-  </si>
-  <si>
-    <t>The Agents in Construction (AiC) ontology is a lightweight semantic model for coordinating on-site production in construction. It represents construction agents (human workers, robots, and other autonomous hardware) as they operate on a site: the processes they carry out, the elements they modify, the resources they handle, and the operational modes and metrics used to assess their performance and impact. To express how agent activities evolve over time, AiC introduces meta-properties that specify when a statement holds (at an instant or over an interval), what dimension of information it represents (planned, simulated, or performed), and who generated it. The ontology emphasizes generic, trade-agnostic concepts to ensure broad applicability across project types and delivery methods.</t>
   </si>
   <si>
     <t>dct</t>
@@ -3653,6 +3650,30 @@
   </si>
   <si>
     <t>This ontology provides a semantic framework for representing roof condition inspection information, including roofs and roof pitches, inspections, orthophotos, and image-derived defect observations. It is designed to support structured documentation, querying, and interoperability within digital twin–based workflows for roof condition monitoring and maintenance, particularly in the context of existing and heritage buildings.</t>
+  </si>
+  <si>
+    <t>The Agents in Construction (AiC) ontology is a lightweight semantic model for coordinating on-site production in construction. It represents construction agents (human workers, robots, and other autonomous hardware) and their state as they operate on a site: the processes they carry out, the elements they modify, the resources they handle, and the operational modes and metrics used to assess their performance and impact. To express how agents' operations evolve over time, AiC introduces meta-properties that specify when a statement holds (at an instant or over an interval), what dimension of information it represents (planned, simulated, or performed), and who generated it. The ontology emphasizes generic, trade-agnostic concepts to ensure broad applicability across project types and delivery methods.</t>
+  </si>
+  <si>
+    <t>Modelling and Standards Ontology</t>
+  </si>
+  <si>
+    <t>mns</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mns#</t>
+  </si>
+  <si>
+    <t>https:\\doi.org\10.35490/EC3.2025.439</t>
+  </si>
+  <si>
+    <t>CC-BY-4.0</t>
+  </si>
+  <si>
+    <t>This ontology is developed to make the BIM Standards Landscape Explorer machine-readable on one hand, and also to create a connction between standards and other datasets and ontologies. This is a project from EC3 Modelling and Standards Committee. This is work-in-progress.</t>
+  </si>
+  <si>
+    <t>beo; bot; csite; cto; dica; dice; dicm; dicp; dtc; ioc; nen2660</t>
   </si>
 </sst>
 </file>
@@ -3944,8 +3965,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V145" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:V145" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V146" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:V146" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V145">
     <sortCondition ref="B1:B145"/>
   </sortState>
@@ -4362,7 +4383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484B993-682B-477D-B31E-A58D58B7BF22}">
-  <dimension ref="A1:Z145"/>
+  <dimension ref="A1:Z146"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
@@ -4374,14 +4395,14 @@
     <col min="10" max="10" width="7" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="45.5703125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="26.5703125" style="3" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="46" style="3" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="32.140625" style="32" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="26.5703125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="46" style="3" customWidth="1"/>
+    <col min="15" max="15" width="32.140625" style="32" customWidth="1"/>
     <col min="16" max="16" width="26.140625" style="32" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="21.42578125" style="32" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="19.5703125" style="32" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="19" style="32" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="0" style="30" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" style="30" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="36.42578125" style="30" customWidth="1"/>
     <col min="22" max="22" width="41.28515625" style="3" customWidth="1"/>
   </cols>
@@ -4403,7 +4424,7 @@
         <v>659</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G1" s="22" t="s">
         <v>747</v>
@@ -4442,16 +4463,16 @@
         <v>743</v>
       </c>
       <c r="S1" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -4510,13 +4531,13 @@
         <v>30</v>
       </c>
       <c r="U2" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>751</v>
       </c>
@@ -4539,23 +4560,23 @@
         <v>14</v>
       </c>
       <c r="I3" s="28" t="s">
-        <v>241</v>
+        <v>393</v>
       </c>
       <c r="J3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="K3" t="s">
         <v>133</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>756</v>
-      </c>
       <c r="O3" s="32" t="s">
         <v>29</v>
       </c>
@@ -4572,10 +4593,10 @@
         <v>30</v>
       </c>
       <c r="U3" s="32" t="s">
+        <v>899</v>
+      </c>
+      <c r="V3" s="34" t="s">
         <v>900</v>
-      </c>
-      <c r="V3" s="34" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -4637,10 +4658,10 @@
         <v>15</v>
       </c>
       <c r="U4" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="195" x14ac:dyDescent="0.25">
@@ -4675,7 +4696,7 @@
         <v>35</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>36</v>
@@ -4699,10 +4720,10 @@
         <v>29</v>
       </c>
       <c r="U5" s="30" t="s">
+        <v>904</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>905</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="150" x14ac:dyDescent="0.25">
@@ -4740,7 +4761,7 @@
         <v>23</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>38</v>
@@ -4767,10 +4788,10 @@
         <v>15</v>
       </c>
       <c r="U6" s="30" t="s">
+        <v>906</v>
+      </c>
+      <c r="V6" s="3" t="s">
         <v>907</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -4829,10 +4850,10 @@
         <v>30</v>
       </c>
       <c r="U7" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="210" x14ac:dyDescent="0.25">
@@ -4867,7 +4888,7 @@
         <v>38</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>38</v>
@@ -4891,10 +4912,10 @@
         <v>30</v>
       </c>
       <c r="U8" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -4929,7 +4950,7 @@
         <v>23</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>38</v>
@@ -4956,10 +4977,10 @@
         <v>22</v>
       </c>
       <c r="U9" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="60" x14ac:dyDescent="0.25">
@@ -4994,7 +5015,7 @@
         <v>57</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>38</v>
@@ -5021,10 +5042,10 @@
         <v>15</v>
       </c>
       <c r="U10" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5083,10 +5104,10 @@
         <v>29</v>
       </c>
       <c r="U11" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5142,10 +5163,10 @@
         <v>30</v>
       </c>
       <c r="U12" s="30" t="s">
+        <v>930</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>931</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -5204,10 +5225,10 @@
         <v>15</v>
       </c>
       <c r="U13" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -5239,7 +5260,7 @@
         <v>38</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>72</v>
@@ -5266,10 +5287,10 @@
         <v>15</v>
       </c>
       <c r="U14" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5304,7 +5325,7 @@
         <v>23</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>38</v>
@@ -5331,10 +5352,10 @@
         <v>15</v>
       </c>
       <c r="U15" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5396,10 +5417,10 @@
         <v>30</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5434,13 +5455,13 @@
         <v>85</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="O17" s="32" t="s">
         <v>29</v>
@@ -5458,10 +5479,10 @@
         <v>29</v>
       </c>
       <c r="U17" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -5472,7 +5493,7 @@
         <v>90</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D18" t="s">
         <v>38</v>
@@ -5520,10 +5541,10 @@
         <v>29</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5561,7 +5582,7 @@
         <v>98</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>100</v>
@@ -5588,10 +5609,10 @@
         <v>78</v>
       </c>
       <c r="U19" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -5650,10 +5671,10 @@
         <v>29</v>
       </c>
       <c r="U20" s="30" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -5715,10 +5736,10 @@
         <v>15</v>
       </c>
       <c r="U21" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5780,10 +5801,10 @@
         <v>30</v>
       </c>
       <c r="U22" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="270" x14ac:dyDescent="0.25">
@@ -5839,10 +5860,10 @@
         <v>29</v>
       </c>
       <c r="U23" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="225" x14ac:dyDescent="0.25">
@@ -5880,7 +5901,7 @@
         <v>38</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>122</v>
@@ -5904,10 +5925,10 @@
         <v>30</v>
       </c>
       <c r="U24" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -5945,7 +5966,7 @@
         <v>38</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>38</v>
@@ -5969,10 +5990,10 @@
         <v>30</v>
       </c>
       <c r="U25" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -6031,10 +6052,10 @@
         <v>29</v>
       </c>
       <c r="U26" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -6093,10 +6114,10 @@
         <v>29</v>
       </c>
       <c r="U27" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6155,10 +6176,10 @@
         <v>29</v>
       </c>
       <c r="U28" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -6217,13 +6238,13 @@
         <v>29</v>
       </c>
       <c r="U29" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="285" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>584</v>
       </c>
@@ -6279,10 +6300,10 @@
         <v>30</v>
       </c>
       <c r="U30" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6293,7 +6314,7 @@
         <v>132</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D31" t="s">
         <v>123</v>
@@ -6314,7 +6335,7 @@
         <v>133</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>135</v>
@@ -6338,10 +6359,10 @@
         <v>30</v>
       </c>
       <c r="U31" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="60" x14ac:dyDescent="0.25">
@@ -6352,7 +6373,7 @@
         <v>576</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
@@ -6400,10 +6421,10 @@
         <v>30</v>
       </c>
       <c r="U32" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6411,7 +6432,7 @@
         <v>137</v>
       </c>
       <c r="B33" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C33" t="s">
         <v>38</v>
@@ -6441,7 +6462,7 @@
         <v>138</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>38</v>
@@ -6465,10 +6486,10 @@
         <v>29</v>
       </c>
       <c r="U33" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -6479,7 +6500,7 @@
         <v>143</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -6503,7 +6524,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>145</v>
@@ -6527,10 +6548,10 @@
         <v>29</v>
       </c>
       <c r="U34" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -6541,7 +6562,7 @@
         <v>149</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D35" t="s">
         <v>147</v>
@@ -6565,7 +6586,7 @@
         <v>133</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>151</v>
@@ -6586,10 +6607,10 @@
         <v>29</v>
       </c>
       <c r="U35" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -6600,7 +6621,7 @@
         <v>153</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D36" t="s">
         <v>147</v>
@@ -6648,10 +6669,10 @@
         <v>29</v>
       </c>
       <c r="U36" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="37" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -6662,7 +6683,7 @@
         <v>159</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D37" t="s">
         <v>147</v>
@@ -6710,10 +6731,10 @@
         <v>30</v>
       </c>
       <c r="U37" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6724,7 +6745,7 @@
         <v>164</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D38" t="s">
         <v>147</v>
@@ -6772,10 +6793,10 @@
         <v>29</v>
       </c>
       <c r="U38" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6786,7 +6807,7 @@
         <v>169</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D39" t="s">
         <v>147</v>
@@ -6810,7 +6831,7 @@
         <v>133</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>167</v>
@@ -6834,10 +6855,10 @@
         <v>30</v>
       </c>
       <c r="U39" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6867,7 +6888,7 @@
         <v>38</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>38</v>
@@ -6891,13 +6912,13 @@
         <v>30</v>
       </c>
       <c r="U40" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>172</v>
       </c>
@@ -6905,7 +6926,7 @@
         <v>173</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D41" t="s">
         <v>147</v>
@@ -6953,13 +6974,13 @@
         <v>29</v>
       </c>
       <c r="U41" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>177</v>
       </c>
@@ -6967,7 +6988,7 @@
         <v>178</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D42" t="s">
         <v>147</v>
@@ -7018,10 +7039,10 @@
         <v>30</v>
       </c>
       <c r="U42" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="300" x14ac:dyDescent="0.25">
@@ -7032,7 +7053,7 @@
         <v>183</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D43" t="s">
         <v>147</v>
@@ -7080,10 +7101,10 @@
         <v>29</v>
       </c>
       <c r="U43" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -7094,7 +7115,7 @@
         <v>188</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D44" t="s">
         <v>147</v>
@@ -7107,7 +7128,7 @@
         <v>14</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>38</v>
@@ -7131,10 +7152,10 @@
         <v>30</v>
       </c>
       <c r="U44" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7145,7 +7166,7 @@
         <v>190</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D45" t="s">
         <v>147</v>
@@ -7167,7 +7188,7 @@
         <v>133</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>38</v>
@@ -7191,10 +7212,10 @@
         <v>29</v>
       </c>
       <c r="U45" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="46" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -7205,7 +7226,7 @@
         <v>192</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D46" t="s">
         <v>147</v>
@@ -7253,10 +7274,10 @@
         <v>29</v>
       </c>
       <c r="U46" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="285" x14ac:dyDescent="0.25">
@@ -7294,7 +7315,7 @@
         <v>38</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>38</v>
@@ -7318,10 +7339,10 @@
         <v>30</v>
       </c>
       <c r="U47" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -7359,7 +7380,7 @@
         <v>38</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>38</v>
@@ -7383,13 +7404,13 @@
         <v>30</v>
       </c>
       <c r="U48" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="49" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>198</v>
       </c>
@@ -7397,7 +7418,7 @@
         <v>199</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D49" t="s">
         <v>38</v>
@@ -7442,10 +7463,10 @@
         <v>30</v>
       </c>
       <c r="U49" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="60" x14ac:dyDescent="0.25">
@@ -7483,7 +7504,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>208</v>
@@ -7507,10 +7528,10 @@
         <v>30</v>
       </c>
       <c r="U50" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -7572,13 +7593,13 @@
         <v>30</v>
       </c>
       <c r="U51" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>214</v>
       </c>
@@ -7613,7 +7634,7 @@
         <v>38</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>218</v>
@@ -7637,10 +7658,10 @@
         <v>30</v>
       </c>
       <c r="U52" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="360" x14ac:dyDescent="0.25">
@@ -7699,27 +7720,27 @@
         <v>30</v>
       </c>
       <c r="U53" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="54" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>757</v>
+      </c>
+      <c r="B54" t="s">
         <v>758</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" t="s">
         <v>760</v>
-      </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
-      <c r="E54" t="s">
-        <v>761</v>
       </c>
       <c r="G54" t="s">
         <v>609</v>
@@ -7734,14 +7755,14 @@
         <v>248</v>
       </c>
       <c r="L54" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="M54" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="N54" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>764</v>
-      </c>
       <c r="O54" s="32" t="s">
         <v>29</v>
       </c>
@@ -7758,10 +7779,10 @@
         <v>30</v>
       </c>
       <c r="U54" s="32" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V54" s="34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="55" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7796,7 +7817,7 @@
         <v>231</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>38</v>
@@ -7820,10 +7841,10 @@
         <v>30</v>
       </c>
       <c r="U55" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="56" spans="1:22" ht="135" x14ac:dyDescent="0.25">
@@ -7834,7 +7855,7 @@
         <v>235</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D56" t="s">
         <v>38</v>
@@ -7858,7 +7879,7 @@
         <v>237</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>38</v>
@@ -7882,10 +7903,10 @@
         <v>30</v>
       </c>
       <c r="U56" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -7947,10 +7968,10 @@
         <v>30</v>
       </c>
       <c r="U57" s="30" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -7985,7 +8006,7 @@
         <v>248</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>38</v>
@@ -8009,13 +8030,13 @@
         <v>30</v>
       </c>
       <c r="U58" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>251</v>
       </c>
@@ -8047,7 +8068,7 @@
         <v>23</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>256</v>
@@ -8071,10 +8092,10 @@
         <v>29</v>
       </c>
       <c r="U59" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V59" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -8085,7 +8106,7 @@
         <v>258</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D60" t="s">
         <v>38</v>
@@ -8109,7 +8130,7 @@
         <v>260</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>38</v>
@@ -8133,10 +8154,10 @@
         <v>30</v>
       </c>
       <c r="U60" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8144,7 +8165,7 @@
         <v>652</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>38</v>
@@ -8172,7 +8193,7 @@
         <v>653</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>38</v>
@@ -8196,10 +8217,10 @@
         <v>30</v>
       </c>
       <c r="U61" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8258,10 +8279,10 @@
         <v>30</v>
       </c>
       <c r="U62" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="63" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -8323,27 +8344,27 @@
         <v>30</v>
       </c>
       <c r="U63" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="64" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>764</v>
+      </c>
+      <c r="B64" t="s">
         <v>765</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>767</v>
-      </c>
-      <c r="D64" t="s">
-        <v>38</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>768</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
@@ -8361,13 +8382,13 @@
         <v>35</v>
       </c>
       <c r="L64" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="M64" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="M64" s="3" t="s">
-        <v>770</v>
-      </c>
       <c r="N64" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="O64" s="32" t="s">
         <v>29</v>
@@ -8385,10 +8406,10 @@
         <v>30</v>
       </c>
       <c r="U64" s="32" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V64" s="34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="65" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8447,10 +8468,10 @@
         <v>29</v>
       </c>
       <c r="U65" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8488,7 +8509,7 @@
         <v>23</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>83</v>
@@ -8512,10 +8533,10 @@
         <v>29</v>
       </c>
       <c r="U66" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="67" spans="1:22" ht="210" x14ac:dyDescent="0.25">
@@ -8553,7 +8574,7 @@
         <v>38</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M67" s="3" t="s">
         <v>38</v>
@@ -8577,10 +8598,10 @@
         <v>30</v>
       </c>
       <c r="U67" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="68" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -8618,7 +8639,7 @@
         <v>38</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>38</v>
@@ -8642,10 +8663,10 @@
         <v>30</v>
       </c>
       <c r="U68" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="69" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
@@ -8656,7 +8677,7 @@
         <v>665</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D69" t="s">
         <v>38</v>
@@ -8680,7 +8701,7 @@
         <v>582</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="N69" s="11"/>
       <c r="O69" s="32" t="s">
@@ -8699,10 +8720,10 @@
         <v>29</v>
       </c>
       <c r="U69" s="30" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="70" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8710,7 +8731,7 @@
         <v>502</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>38</v>
@@ -8762,10 +8783,10 @@
       </c>
       <c r="T70" s="32"/>
       <c r="U70" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -8773,7 +8794,7 @@
         <v>539</v>
       </c>
       <c r="B71" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>38</v>
@@ -8824,27 +8845,27 @@
         <v>30</v>
       </c>
       <c r="U71" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>771</v>
+      </c>
+      <c r="B72" t="s">
         <v>772</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>774</v>
-      </c>
-      <c r="D72" t="s">
-        <v>38</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>775</v>
       </c>
       <c r="G72" t="s">
         <v>0</v>
@@ -8862,14 +8883,14 @@
         <v>35</v>
       </c>
       <c r="L72" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="M72" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="M72" s="3" t="s">
+      <c r="N72" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>778</v>
-      </c>
       <c r="O72" s="32" t="s">
         <v>29</v>
       </c>
@@ -8886,10 +8907,10 @@
         <v>29</v>
       </c>
       <c r="U72" s="32" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V72" s="34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="73" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -8927,7 +8948,7 @@
         <v>23</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>278</v>
@@ -8954,10 +8975,10 @@
         <v>0</v>
       </c>
       <c r="U73" s="30" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V73" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8992,7 +9013,7 @@
         <v>23</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>509</v>
@@ -9016,10 +9037,10 @@
         <v>30</v>
       </c>
       <c r="U74" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V74" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -9030,7 +9051,7 @@
         <v>507</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D75" t="s">
         <v>38</v>
@@ -9057,7 +9078,7 @@
         <v>248</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="M75" s="3" t="s">
         <v>38</v>
@@ -9082,10 +9103,10 @@
       </c>
       <c r="T75" s="39"/>
       <c r="U75" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V75" s="3" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -9096,7 +9117,7 @@
         <v>288</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D76" t="s">
         <v>38</v>
@@ -9120,7 +9141,7 @@
         <v>35</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>38</v>
@@ -9144,10 +9165,10 @@
         <v>30</v>
       </c>
       <c r="U76" s="30" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V76" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -9182,7 +9203,7 @@
         <v>23</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="M77" s="3" t="s">
         <v>38</v>
@@ -9209,10 +9230,10 @@
         <v>15</v>
       </c>
       <c r="U77" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V77" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="78" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -9223,7 +9244,7 @@
         <v>218</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D78" t="s">
         <v>38</v>
@@ -9247,7 +9268,7 @@
         <v>231</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M78" s="3" t="s">
         <v>296</v>
@@ -9271,10 +9292,10 @@
         <v>30</v>
       </c>
       <c r="U78" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V78" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="79" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -9333,10 +9354,10 @@
         <v>29</v>
       </c>
       <c r="U79" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V79" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="80" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -9362,7 +9383,7 @@
         <v>38</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M80" s="3" t="s">
         <v>306</v>
@@ -9386,13 +9407,13 @@
         <v>29</v>
       </c>
       <c r="U80" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V80" s="3" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>510</v>
       </c>
@@ -9429,10 +9450,10 @@
       <c r="N81" s="11"/>
       <c r="S81" s="33"/>
       <c r="U81" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V81" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -9491,10 +9512,10 @@
         <v>29</v>
       </c>
       <c r="U82" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V82" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="83" spans="1:22" ht="135" x14ac:dyDescent="0.25">
@@ -9532,7 +9553,7 @@
         <v>57</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>38</v>
@@ -9556,10 +9577,10 @@
         <v>30</v>
       </c>
       <c r="U83" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V83" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -9594,7 +9615,7 @@
         <v>23</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>38</v>
@@ -9618,10 +9639,10 @@
         <v>29</v>
       </c>
       <c r="U84" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V84" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="85" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -9680,10 +9701,10 @@
         <v>30</v>
       </c>
       <c r="U85" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V85" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="86" spans="1:22" s="17" customFormat="1" ht="165" x14ac:dyDescent="0.25">
@@ -9744,10 +9765,10 @@
       </c>
       <c r="T86" s="30"/>
       <c r="U86" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V86" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="87" spans="1:22" ht="225" x14ac:dyDescent="0.25">
@@ -9806,10 +9827,10 @@
         <v>30</v>
       </c>
       <c r="U87" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V87" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="88" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -9868,10 +9889,10 @@
         <v>30</v>
       </c>
       <c r="U88" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V88" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="89" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -9933,10 +9954,10 @@
         <v>29</v>
       </c>
       <c r="U89" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V89" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="90" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -9971,7 +9992,7 @@
         <v>38</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="M90" s="3" t="s">
         <v>83</v>
@@ -9995,10 +10016,10 @@
         <v>30</v>
       </c>
       <c r="U90" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V90" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="91" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -10057,10 +10078,10 @@
         <v>29</v>
       </c>
       <c r="U91" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V91" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="92" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -10095,7 +10116,7 @@
         <v>23</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>38</v>
@@ -10119,10 +10140,10 @@
         <v>29</v>
       </c>
       <c r="U92" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V92" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="93" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -10133,7 +10154,7 @@
         <v>272</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D93" t="s">
         <v>38</v>
@@ -10181,10 +10202,10 @@
         <v>29</v>
       </c>
       <c r="U93" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V93" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="94" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -10219,7 +10240,7 @@
         <v>38</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>38</v>
@@ -10243,10 +10264,10 @@
         <v>30</v>
       </c>
       <c r="U94" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V94" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="95" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -10281,7 +10302,7 @@
         <v>38</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="M95" s="3" t="s">
         <v>38</v>
@@ -10305,10 +10326,10 @@
         <v>29</v>
       </c>
       <c r="U95" s="30" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V95" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="96" spans="1:22" ht="150" x14ac:dyDescent="0.25">
@@ -10343,7 +10364,7 @@
         <v>38</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>38</v>
@@ -10367,10 +10388,10 @@
         <v>30</v>
       </c>
       <c r="U96" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V96" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="97" spans="1:26" ht="90" x14ac:dyDescent="0.25">
@@ -10429,10 +10450,10 @@
         <v>30</v>
       </c>
       <c r="U97" s="30" t="s">
+        <v>919</v>
+      </c>
+      <c r="V97" s="3" t="s">
         <v>920</v>
-      </c>
-      <c r="V97" s="3" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="98" spans="1:26" ht="75" x14ac:dyDescent="0.25">
@@ -10491,27 +10512,27 @@
         <v>29</v>
       </c>
       <c r="U98" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V98" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="99" spans="1:26" ht="135" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>832</v>
+      </c>
+      <c r="B99" t="s">
         <v>833</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" s="27" t="s">
         <v>834</v>
       </c>
-      <c r="C99" s="27" t="s">
+      <c r="D99" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>835</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>836</v>
       </c>
       <c r="F99" t="s">
         <v>38</v>
@@ -10521,16 +10542,16 @@
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="10" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="J99">
         <v>2025</v>
       </c>
       <c r="K99" t="s">
+        <v>837</v>
+      </c>
+      <c r="L99" s="3" t="s">
         <v>838</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>839</v>
       </c>
       <c r="M99" s="3" t="s">
         <v>38</v>
@@ -10555,10 +10576,10 @@
       </c>
       <c r="T99" s="32"/>
       <c r="U99" s="32" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V99" s="34" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="100" spans="1:26" ht="105" x14ac:dyDescent="0.25">
@@ -10593,7 +10614,7 @@
         <v>23</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>377</v>
@@ -10617,10 +10638,10 @@
         <v>29</v>
       </c>
       <c r="U100" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V100" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="101" spans="1:26" ht="90" x14ac:dyDescent="0.25">
@@ -10655,7 +10676,7 @@
         <v>23</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>382</v>
@@ -10679,27 +10700,27 @@
         <v>30</v>
       </c>
       <c r="U101" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V101" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="102" spans="1:26" ht="150" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B102" t="s">
         <v>1081</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" s="41" t="s">
         <v>1082</v>
       </c>
-      <c r="C102" s="41" t="s">
-        <v>1083</v>
-      </c>
       <c r="D102" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F102" s="29" t="s">
         <v>38</v>
@@ -10720,7 +10741,7 @@
         <v>133</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="N102" s="11"/>
       <c r="S102" s="33"/>
@@ -10760,7 +10781,7 @@
         <v>385</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="M103" s="3" t="s">
         <v>387</v>
@@ -10784,13 +10805,13 @@
         <v>29</v>
       </c>
       <c r="U103" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V103" s="3" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="104" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" ht="285" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>600</v>
       </c>
@@ -10843,13 +10864,13 @@
         <v>30</v>
       </c>
       <c r="U104" s="30" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V104" s="3" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="105" spans="1:26" ht="165" x14ac:dyDescent="0.25">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" ht="195" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>389</v>
       </c>
@@ -10881,7 +10902,7 @@
         <v>57</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="M105" s="3" t="s">
         <v>38</v>
@@ -10905,10 +10926,10 @@
         <v>30</v>
       </c>
       <c r="U105" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V105" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="106" spans="1:26" ht="105" x14ac:dyDescent="0.25">
@@ -10943,7 +10964,7 @@
         <v>23</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="M106" s="3" t="s">
         <v>395</v>
@@ -10967,10 +10988,10 @@
         <v>30</v>
       </c>
       <c r="U106" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V106" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="107" spans="1:26" ht="90" x14ac:dyDescent="0.25">
@@ -11005,7 +11026,7 @@
         <v>23</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="M107" s="3" t="s">
         <v>401</v>
@@ -11029,13 +11050,13 @@
         <v>29</v>
       </c>
       <c r="U107" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V107" s="3" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="108" spans="1:26" ht="120" x14ac:dyDescent="0.25">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>419</v>
       </c>
@@ -11067,7 +11088,7 @@
         <v>23</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M108" s="3" t="s">
         <v>423</v>
@@ -11091,13 +11112,13 @@
         <v>30</v>
       </c>
       <c r="U108" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V108" s="3" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="109" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="109" spans="1:26" ht="165" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>424</v>
       </c>
@@ -11105,7 +11126,7 @@
         <v>425</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D109" t="s">
         <v>38</v>
@@ -11153,13 +11174,13 @@
         <v>30</v>
       </c>
       <c r="U109" s="30" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V109" s="3" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="110" spans="1:26" ht="105" x14ac:dyDescent="0.25">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="110" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>430</v>
       </c>
@@ -11215,18 +11236,18 @@
         <v>29</v>
       </c>
       <c r="U110" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V110" s="3" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" ht="165" x14ac:dyDescent="0.25">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
         <v>633</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C111" s="19" t="s">
         <v>634</v>
@@ -11254,7 +11275,7 @@
         <v>98</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="M111" s="15" t="s">
         <v>635</v>
@@ -11278,22 +11299,22 @@
         <v>30</v>
       </c>
       <c r="U111" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V111" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="150" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
         <v>637</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D112" s="20" t="s">
         <v>405</v>
@@ -11320,7 +11341,7 @@
         <v>98</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="M112" s="15" t="s">
         <v>639</v>
@@ -11344,18 +11365,18 @@
         <v>30</v>
       </c>
       <c r="U112" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V112" s="3" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="113" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" ht="285" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>623</v>
       </c>
       <c r="B113" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>403</v>
@@ -11385,7 +11406,7 @@
         <v>98</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="M113" s="3" t="s">
         <v>404</v>
@@ -11409,21 +11430,21 @@
         <v>29</v>
       </c>
       <c r="U113" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V113" s="3" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="114" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>625</v>
       </c>
       <c r="B114" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D114" t="s">
         <v>405</v>
@@ -11450,7 +11471,7 @@
         <v>98</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="M114" s="3" t="s">
         <v>404</v>
@@ -11474,21 +11495,21 @@
         <v>29</v>
       </c>
       <c r="U114" s="30" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V114" s="3" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="115" spans="1:22" ht="285" x14ac:dyDescent="0.25">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
         <v>641</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="D115" s="20" t="s">
         <v>405</v>
@@ -11513,7 +11534,7 @@
         <v>98</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="M115" s="15" t="s">
         <v>643</v>
@@ -11537,21 +11558,21 @@
         <v>30</v>
       </c>
       <c r="U115" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V115" s="3" t="s">
-        <v>1023</v>
-      </c>
-    </row>
-    <row r="116" spans="1:22" ht="195" x14ac:dyDescent="0.25">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>624</v>
       </c>
       <c r="B116" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D116" t="s">
         <v>405</v>
@@ -11578,7 +11599,7 @@
         <v>98</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="M116" s="3" t="s">
         <v>404</v>
@@ -11602,10 +11623,10 @@
         <v>30</v>
       </c>
       <c r="U116" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V116" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="117" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -11613,10 +11634,10 @@
         <v>629</v>
       </c>
       <c r="B117" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D117" t="s">
         <v>405</v>
@@ -11643,7 +11664,7 @@
         <v>98</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>404</v>
@@ -11667,21 +11688,21 @@
         <v>30</v>
       </c>
       <c r="U117" s="30" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V117" s="3" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="118" spans="1:22" ht="300" x14ac:dyDescent="0.25">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>628</v>
       </c>
       <c r="B118" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D118" t="s">
         <v>405</v>
@@ -11708,7 +11729,7 @@
         <v>98</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>404</v>
@@ -11732,21 +11753,21 @@
         <v>30</v>
       </c>
       <c r="U118" s="30" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V118" s="3" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="119" spans="1:22" ht="270" x14ac:dyDescent="0.25">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
         <v>645</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>405</v>
@@ -11773,7 +11794,7 @@
         <v>98</v>
       </c>
       <c r="L119" s="3" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M119" s="15" t="s">
         <v>404</v>
@@ -11797,21 +11818,21 @@
         <v>30</v>
       </c>
       <c r="U119" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V119" s="3" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="120" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>627</v>
       </c>
       <c r="B120" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D120" t="s">
         <v>405</v>
@@ -11838,7 +11859,7 @@
         <v>98</v>
       </c>
       <c r="L120" s="3" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="M120" s="3" t="s">
         <v>413</v>
@@ -11862,21 +11883,21 @@
         <v>30</v>
       </c>
       <c r="U120" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V120" s="3" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="121" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>631</v>
       </c>
       <c r="B121" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D121" t="s">
         <v>405</v>
@@ -11924,18 +11945,18 @@
         <v>29</v>
       </c>
       <c r="U121" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V121" s="3" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="122" spans="1:22" s="17" customFormat="1" ht="285" x14ac:dyDescent="0.25">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>626</v>
       </c>
       <c r="B122" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>418</v>
@@ -11965,7 +11986,7 @@
         <v>98</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="M122" s="3" t="s">
         <v>632</v>
@@ -11990,21 +12011,21 @@
       </c>
       <c r="T122" s="30"/>
       <c r="U122" s="30" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="V122" s="3" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="123" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
         <v>648</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>405</v>
@@ -12029,7 +12050,7 @@
         <v>98</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="M123" s="15" t="s">
         <v>650</v>
@@ -12053,13 +12074,13 @@
         <v>29</v>
       </c>
       <c r="U123" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V123" s="3" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="124" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>433</v>
       </c>
@@ -12067,7 +12088,7 @@
         <v>434</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D124" t="s">
         <v>38</v>
@@ -12118,13 +12139,13 @@
         <v>30</v>
       </c>
       <c r="U124" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V124" s="3" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="125" spans="1:22" s="17" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>439</v>
       </c>
@@ -12178,13 +12199,13 @@
       </c>
       <c r="T125" s="30"/>
       <c r="U125" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V125" s="3" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="126" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>444</v>
       </c>
@@ -12216,7 +12237,7 @@
         <v>38</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="M126" s="3" t="s">
         <v>38</v>
@@ -12240,10 +12261,10 @@
         <v>30</v>
       </c>
       <c r="U126" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V126" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="127" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -12302,10 +12323,10 @@
         <v>30</v>
       </c>
       <c r="U127" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V127" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="128" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -12343,7 +12364,7 @@
         <v>138</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="M128" s="3" t="s">
         <v>38</v>
@@ -12368,10 +12389,10 @@
       </c>
       <c r="T128" s="30"/>
       <c r="U128" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V128" s="3" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="129" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
@@ -12409,7 +12430,7 @@
         <v>38</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="M129" s="3" t="s">
         <v>457</v>
@@ -12434,13 +12455,13 @@
       </c>
       <c r="T129" s="30"/>
       <c r="U129" s="30" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="V129" s="3" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="130" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>547</v>
       </c>
@@ -12475,7 +12496,7 @@
         <v>38</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="M130" s="3" t="s">
         <v>245</v>
@@ -12499,13 +12520,13 @@
         <v>29</v>
       </c>
       <c r="U130" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V130" s="3" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="131" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="131" spans="1:22" ht="300" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>458</v>
       </c>
@@ -12537,7 +12558,7 @@
         <v>38</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="M131" s="3" t="s">
         <v>38</v>
@@ -12561,13 +12582,13 @@
         <v>29</v>
       </c>
       <c r="U131" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V131" s="3" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="132" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="132" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>461</v>
       </c>
@@ -12623,13 +12644,13 @@
         <v>29</v>
       </c>
       <c r="U132" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V132" s="3" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="133" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="133" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>466</v>
       </c>
@@ -12637,7 +12658,7 @@
         <v>467</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D133" t="s">
         <v>38</v>
@@ -12664,7 +12685,7 @@
         <v>38</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="M133" s="3" t="s">
         <v>470</v>
@@ -12688,13 +12709,13 @@
         <v>30</v>
       </c>
       <c r="U133" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V133" s="3" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="134" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="134" spans="1:22" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>219</v>
       </c>
@@ -12750,13 +12771,13 @@
       </c>
       <c r="T134" s="30"/>
       <c r="U134" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V134" s="3" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="135" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="135" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>471</v>
       </c>
@@ -12764,7 +12785,7 @@
         <v>472</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D135" t="s">
         <v>38</v>
@@ -12788,7 +12809,7 @@
         <v>38</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="M135" s="3" t="s">
         <v>38</v>
@@ -12812,13 +12833,13 @@
         <v>30</v>
       </c>
       <c r="U135" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V135" s="3" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="136" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="136" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>475</v>
       </c>
@@ -12826,7 +12847,7 @@
         <v>476</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D136" t="s">
         <v>38</v>
@@ -12850,13 +12871,13 @@
         <v>38</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="O136" s="32" t="s">
         <v>30</v>
@@ -12874,10 +12895,10 @@
         <v>30</v>
       </c>
       <c r="U136" s="30" t="s">
+        <v>901</v>
+      </c>
+      <c r="V136" s="3" t="s">
         <v>902</v>
-      </c>
-      <c r="V136" s="3" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="137" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -12888,7 +12909,7 @@
         <v>479</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D137" t="s">
         <v>38</v>
@@ -12912,13 +12933,13 @@
         <v>38</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M137" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N137" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="O137" s="32" t="s">
         <v>29</v>
@@ -12939,13 +12960,13 @@
         <v>15</v>
       </c>
       <c r="U137" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="V137" s="3" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="138" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="138" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>481</v>
       </c>
@@ -12953,7 +12974,7 @@
         <v>482</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="D138" t="s">
         <v>38</v>
@@ -12977,13 +12998,13 @@
         <v>38</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="M138" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="O138" s="32" t="s">
         <v>30</v>
@@ -13001,21 +13022,21 @@
         <v>29</v>
       </c>
       <c r="U138" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V138" s="3" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="139" spans="1:22" s="16" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="139" spans="1:22" s="16" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>570</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="D139" t="s">
         <v>38</v>
@@ -13040,7 +13061,7 @@
         <v>38</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="M139" s="3" t="s">
         <v>38</v>
@@ -13065,13 +13086,13 @@
       </c>
       <c r="T139" s="30"/>
       <c r="U139" s="30" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="V139" s="3" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="140" spans="1:22" s="16" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="140" spans="1:22" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>484</v>
       </c>
@@ -13079,7 +13100,7 @@
         <v>485</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D140" t="s">
         <v>38</v>
@@ -13104,7 +13125,7 @@
         <v>38</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="M140" s="3" t="s">
         <v>745</v>
@@ -13129,10 +13150,10 @@
       </c>
       <c r="T140" s="30"/>
       <c r="U140" s="30" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V140" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="141" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -13167,7 +13188,7 @@
         <v>38</v>
       </c>
       <c r="L141" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="M141" s="3" t="s">
         <v>38</v>
@@ -13191,10 +13212,10 @@
         <v>30</v>
       </c>
       <c r="U141" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V141" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="142" spans="1:22" ht="120" x14ac:dyDescent="0.25">
@@ -13205,7 +13226,7 @@
         <v>528</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D142" t="s">
         <v>38</v>
@@ -13253,13 +13274,13 @@
         <v>30</v>
       </c>
       <c r="U142" s="30" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="V142" s="3" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="143" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>490</v>
       </c>
@@ -13291,7 +13312,7 @@
         <v>38</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M143" s="3" t="s">
         <v>38</v>
@@ -13313,13 +13334,13 @@
       </c>
       <c r="S143" s="33"/>
       <c r="U143" s="30" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="V143" s="3" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="144" spans="1:22" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="144" spans="1:22" s="16" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>493</v>
       </c>
@@ -13352,7 +13373,7 @@
         <v>23</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="M144" s="3" t="s">
         <v>496</v>
@@ -13377,10 +13398,10 @@
       </c>
       <c r="T144" s="30"/>
       <c r="U144" s="30" t="s">
+        <v>923</v>
+      </c>
+      <c r="V144" s="3" t="s">
         <v>924</v>
-      </c>
-      <c r="V144" s="3" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="145" spans="1:22" ht="315" x14ac:dyDescent="0.25">
@@ -13391,7 +13412,7 @@
         <v>745</v>
       </c>
       <c r="C145" s="27" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>38</v>
@@ -13413,7 +13434,7 @@
         <v>2006</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="M145" s="3" t="s">
         <v>38</v>
@@ -13433,18 +13454,73 @@
       <c r="R145" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="S145" s="33" t="s">
+      <c r="S145" s="38" t="s">
         <v>29</v>
       </c>
       <c r="T145" s="30">
         <v>30</v>
       </c>
       <c r="U145" s="32" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="V145" s="34" t="s">
-        <v>901</v>
-      </c>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F146" t="s">
+        <v>38</v>
+      </c>
+      <c r="H146" s="1"/>
+      <c r="I146" s="10">
+        <v>1</v>
+      </c>
+      <c r="J146">
+        <v>2025</v>
+      </c>
+      <c r="K146" t="s">
+        <v>1089</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="M146" t="s">
+        <v>1091</v>
+      </c>
+      <c r="N146" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="O146" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P146" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q146" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R146" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S146" s="38"/>
+      <c r="T146" s="32"/>
+      <c r="U146" s="32"/>
+      <c r="V146" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -13693,12 +13769,13 @@
     <hyperlink ref="C140" r:id="rId242" xr:uid="{31E930C8-EAAF-4B34-8443-75427984FA75}"/>
     <hyperlink ref="C102" r:id="rId243" xr:uid="{379FD10B-9650-463A-84C0-55B4727D7D47}"/>
     <hyperlink ref="E102" r:id="rId244" xr:uid="{F803CDF1-49F8-4F15-83C4-1374EEB2B30A}"/>
+    <hyperlink ref="C146" r:id="rId245" xr:uid="{C5C87514-E810-480B-A94B-83BB9DAD7389}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId245"/>
-  <legacyDrawing r:id="rId246"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId246"/>
+  <legacyDrawing r:id="rId247"/>
   <tableParts count="1">
-    <tablePart r:id="rId247"/>
+    <tablePart r:id="rId248"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -13707,7 +13784,7 @@
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$28</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H145</xm:sqref>
+          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H145 G146</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -13877,15 +13954,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
@@ -13893,6 +13961,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14100,19 +14177,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/source/ontologies_source.xlsx
+++ b/data/source/ontologies_source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbosche\Documents\GitHub\BE-OLS\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1294C1-FAEB-4722-96F6-46089FB9F58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06C3459-009F-487D-8D0A-1E49AADB3E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="14" r:id="rId1"/>
@@ -262,7 +262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S92" authorId="9" shapeId="0" xr:uid="{51CFF48A-CD78-4902-8B0C-DC9E113097CA}">
+    <comment ref="S93" authorId="9" shapeId="0" xr:uid="{51CFF48A-CD78-4902-8B0C-DC9E113097CA}">
       <text>
         <r>
           <rPr>
@@ -283,7 +283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E95" authorId="10" shapeId="0" xr:uid="{FF38AB15-F518-4A75-8FD0-5D30FB36F963}">
+    <comment ref="E96" authorId="10" shapeId="0" xr:uid="{FF38AB15-F518-4A75-8FD0-5D30FB36F963}">
       <text>
         <r>
           <rPr>
@@ -300,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E96" authorId="11" shapeId="0" xr:uid="{C1789974-873D-4FE1-B73F-043CBD4ED103}">
+    <comment ref="E97" authorId="11" shapeId="0" xr:uid="{C1789974-873D-4FE1-B73F-043CBD4ED103}">
       <text>
         <r>
           <rPr>
@@ -317,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M103" authorId="12" shapeId="0" xr:uid="{9B4FF538-E0FF-4ED4-A111-F93178D73F43}">
+    <comment ref="M104" authorId="12" shapeId="0" xr:uid="{9B4FF538-E0FF-4ED4-A111-F93178D73F43}">
       <text>
         <r>
           <rPr>
@@ -334,7 +334,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E125" authorId="13" shapeId="0" xr:uid="{BAF4458C-FE0F-4442-9348-DACD7E1A9B32}">
+    <comment ref="E126" authorId="13" shapeId="0" xr:uid="{BAF4458C-FE0F-4442-9348-DACD7E1A9B32}">
       <text>
         <r>
           <rPr>
@@ -351,7 +351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E136" authorId="14" shapeId="0" xr:uid="{CAD6BC40-6B67-4E9E-AB3E-DA05BF8F7896}">
+    <comment ref="E137" authorId="14" shapeId="0" xr:uid="{CAD6BC40-6B67-4E9E-AB3E-DA05BF8F7896}">
       <text>
         <r>
           <rPr>
@@ -368,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E139" authorId="15" shapeId="0" xr:uid="{3EE948F8-4E0F-4FD4-8BC9-EA54C6408FF1}">
+    <comment ref="E140" authorId="15" shapeId="0" xr:uid="{3EE948F8-4E0F-4FD4-8BC9-EA54C6408FF1}">
       <text>
         <r>
           <rPr>
@@ -390,7 +390,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="1099">
   <si>
     <t>BE Product (Building)</t>
   </si>
@@ -2625,9 +2625,6 @@
   </si>
   <si>
     <t>documentation</t>
-  </si>
-  <si>
-    <t>wgs84</t>
   </si>
   <si>
     <t>secondary_domain</t>
@@ -3674,6 +3671,32 @@
   </si>
   <si>
     <t>beo; bot; csite; cto; dica; dice; dicm; dicp; dtc; ioc; nen2660</t>
+  </si>
+  <si>
+    <t>Construction Site Emission Management Ontology</t>
+  </si>
+  <si>
+    <t>xemo</t>
+  </si>
+  <si>
+    <t>https://github.com/AlessandroBruttini/XEMO</t>
+  </si>
+  <si>
+    <t>Bruttini, A., Hagedorn, P., Getuli, V., Capone, P., and König, M. (2026). XEMO: Construction Site Emission Management Ontology for Particulate Matter. EG-ICE 2026.</t>
+  </si>
+  <si>
+    <t>XEMO represents:
+an urban region containing one or more construction sites; construction sites organised into construction areas; construction activities carried out within those areas; sites, areas, and activities as emission sources at different spatial and operational scales; pollutants as observable properties of emission sources; sensors, platforms, deployments, and observations; thresholds defined by value, unit, type, averaging period, statistical method, and regulatory provenance.
+The current implementation includes PM10, PM2.5, and total suspended particles, together with example threshold definitions derived from Directive (EU) 2024/2881.</t>
+  </si>
+  <si>
+    <t>bot, sosa, ssn, dice</t>
+  </si>
+  <si>
+    <t>qudt, time, PROV-O</t>
+  </si>
+  <si>
+    <t>wgs84_pos</t>
   </si>
 </sst>
 </file>
@@ -3965,10 +3988,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V146" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:V146" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V145">
-    <sortCondition ref="B1:B145"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V147" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:V147" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V146">
+    <sortCondition ref="B1:B146"/>
   </sortState>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{9A74C9B8-D669-464E-AF30-98194DC54E48}" name="title"/>
@@ -4383,7 +4406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484B993-682B-477D-B31E-A58D58B7BF22}">
-  <dimension ref="A1:Z146"/>
+  <dimension ref="A1:Z147"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
@@ -4424,13 +4447,13 @@
         <v>659</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="I1" s="24" t="s">
         <v>660</v>
@@ -4445,13 +4468,13 @@
         <v>663</v>
       </c>
       <c r="M1" s="25" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="N1" s="25" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="O1" s="26" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="P1" s="26" t="s">
         <v>742</v>
@@ -4463,16 +4486,16 @@
         <v>743</v>
       </c>
       <c r="S1" s="26" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="V1" s="31" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="255" x14ac:dyDescent="0.25">
@@ -4531,27 +4554,27 @@
         <v>30</v>
       </c>
       <c r="U2" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>750</v>
+      </c>
+      <c r="B3" t="s">
         <v>751</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>754</v>
       </c>
       <c r="F3" t="s">
         <v>38</v>
@@ -4569,13 +4592,13 @@
         <v>133</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="O3" s="32" t="s">
         <v>29</v>
@@ -4593,10 +4616,10 @@
         <v>30</v>
       </c>
       <c r="U3" s="32" t="s">
+        <v>898</v>
+      </c>
+      <c r="V3" s="34" t="s">
         <v>899</v>
-      </c>
-      <c r="V3" s="34" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -4658,10 +4681,10 @@
         <v>15</v>
       </c>
       <c r="U4" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="195" x14ac:dyDescent="0.25">
@@ -4696,7 +4719,7 @@
         <v>35</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>36</v>
@@ -4720,10 +4743,10 @@
         <v>29</v>
       </c>
       <c r="U5" s="30" t="s">
+        <v>903</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>904</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="150" x14ac:dyDescent="0.25">
@@ -4761,7 +4784,7 @@
         <v>23</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>38</v>
@@ -4788,13 +4811,13 @@
         <v>15</v>
       </c>
       <c r="U6" s="30" t="s">
+        <v>905</v>
+      </c>
+      <c r="V6" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="V6" s="3" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:22" ht="225" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -4850,13 +4873,13 @@
         <v>30</v>
       </c>
       <c r="U7" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="210" x14ac:dyDescent="0.25">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -4888,7 +4911,7 @@
         <v>38</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>38</v>
@@ -4912,10 +4935,10 @@
         <v>30</v>
       </c>
       <c r="U8" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -4950,7 +4973,7 @@
         <v>23</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>38</v>
@@ -4977,13 +5000,13 @@
         <v>22</v>
       </c>
       <c r="U9" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -5015,7 +5038,7 @@
         <v>57</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>38</v>
@@ -5042,13 +5065,13 @@
         <v>15</v>
       </c>
       <c r="U10" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -5104,10 +5127,10 @@
         <v>29</v>
       </c>
       <c r="U11" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5163,13 +5186,13 @@
         <v>30</v>
       </c>
       <c r="U12" s="30" t="s">
+        <v>929</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -5225,13 +5248,13 @@
         <v>15</v>
       </c>
       <c r="U13" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -5260,7 +5283,7 @@
         <v>38</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>72</v>
@@ -5287,10 +5310,10 @@
         <v>15</v>
       </c>
       <c r="U14" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5325,7 +5348,7 @@
         <v>23</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>38</v>
@@ -5352,13 +5375,13 @@
         <v>15</v>
       </c>
       <c r="U15" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>77</v>
       </c>
@@ -5417,10 +5440,10 @@
         <v>30</v>
       </c>
       <c r="U16" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5455,13 +5478,13 @@
         <v>85</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O17" s="32" t="s">
         <v>29</v>
@@ -5479,13 +5502,13 @@
         <v>29</v>
       </c>
       <c r="U17" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -5493,7 +5516,7 @@
         <v>90</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D18" t="s">
         <v>38</v>
@@ -5541,10 +5564,10 @@
         <v>29</v>
       </c>
       <c r="U18" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -5582,7 +5605,7 @@
         <v>98</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="M19" s="11" t="s">
         <v>100</v>
@@ -5609,13 +5632,13 @@
         <v>78</v>
       </c>
       <c r="U19" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>102</v>
       </c>
@@ -5671,13 +5694,13 @@
         <v>29</v>
       </c>
       <c r="U20" s="30" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>107</v>
       </c>
@@ -5736,13 +5759,13 @@
         <v>15</v>
       </c>
       <c r="U21" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>114</v>
       </c>
@@ -5801,13 +5824,13 @@
         <v>30</v>
       </c>
       <c r="U22" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="270" x14ac:dyDescent="0.25">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="300" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>568</v>
       </c>
@@ -5860,13 +5883,13 @@
         <v>29</v>
       </c>
       <c r="U23" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="225" x14ac:dyDescent="0.25">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>119</v>
       </c>
@@ -5901,7 +5924,7 @@
         <v>38</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>122</v>
@@ -5925,13 +5948,13 @@
         <v>30</v>
       </c>
       <c r="U24" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -5966,7 +5989,7 @@
         <v>38</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>38</v>
@@ -5990,13 +6013,13 @@
         <v>30</v>
       </c>
       <c r="U25" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>594</v>
       </c>
@@ -6052,13 +6075,13 @@
         <v>29</v>
       </c>
       <c r="U26" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>569</v>
       </c>
@@ -6114,13 +6137,13 @@
         <v>29</v>
       </c>
       <c r="U27" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -6176,13 +6199,13 @@
         <v>29</v>
       </c>
       <c r="U28" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>589</v>
       </c>
@@ -6238,10 +6261,10 @@
         <v>29</v>
       </c>
       <c r="U29" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="285" x14ac:dyDescent="0.25">
@@ -6300,13 +6323,13 @@
         <v>30</v>
       </c>
       <c r="U30" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>131</v>
       </c>
@@ -6314,7 +6337,7 @@
         <v>132</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D31" t="s">
         <v>123</v>
@@ -6335,7 +6358,7 @@
         <v>133</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>135</v>
@@ -6359,13 +6382,13 @@
         <v>30</v>
       </c>
       <c r="U31" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>575</v>
       </c>
@@ -6373,7 +6396,7 @@
         <v>576</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
@@ -6421,10 +6444,10 @@
         <v>30</v>
       </c>
       <c r="U32" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6432,7 +6455,7 @@
         <v>137</v>
       </c>
       <c r="B33" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C33" t="s">
         <v>38</v>
@@ -6462,7 +6485,7 @@
         <v>138</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>38</v>
@@ -6486,13 +6509,13 @@
         <v>29</v>
       </c>
       <c r="U33" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>142</v>
       </c>
@@ -6500,7 +6523,7 @@
         <v>143</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -6524,7 +6547,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>145</v>
@@ -6548,13 +6571,13 @@
         <v>29</v>
       </c>
       <c r="U34" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>148</v>
       </c>
@@ -6562,7 +6585,7 @@
         <v>149</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D35" t="s">
         <v>147</v>
@@ -6586,7 +6609,7 @@
         <v>133</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>151</v>
@@ -6607,13 +6630,13 @@
         <v>29</v>
       </c>
       <c r="U35" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -6621,7 +6644,7 @@
         <v>153</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D36" t="s">
         <v>147</v>
@@ -6669,13 +6692,13 @@
         <v>29</v>
       </c>
       <c r="U36" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>158</v>
       </c>
@@ -6683,7 +6706,7 @@
         <v>159</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D37" t="s">
         <v>147</v>
@@ -6731,13 +6754,13 @@
         <v>30</v>
       </c>
       <c r="U37" s="30" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>163</v>
       </c>
@@ -6745,7 +6768,7 @@
         <v>164</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D38" t="s">
         <v>147</v>
@@ -6793,10 +6816,10 @@
         <v>29</v>
       </c>
       <c r="U38" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6807,7 +6830,7 @@
         <v>169</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D39" t="s">
         <v>147</v>
@@ -6831,7 +6854,7 @@
         <v>133</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>167</v>
@@ -6855,10 +6878,10 @@
         <v>30</v>
       </c>
       <c r="U39" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -6888,7 +6911,7 @@
         <v>38</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>38</v>
@@ -6912,10 +6935,10 @@
         <v>30</v>
       </c>
       <c r="U40" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="41" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -6926,7 +6949,7 @@
         <v>173</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D41" t="s">
         <v>147</v>
@@ -6974,10 +6997,10 @@
         <v>29</v>
       </c>
       <c r="U41" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="42" spans="1:22" ht="180" x14ac:dyDescent="0.25">
@@ -6988,7 +7011,7 @@
         <v>178</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D42" t="s">
         <v>147</v>
@@ -7039,13 +7062,13 @@
         <v>30</v>
       </c>
       <c r="U42" s="30" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" ht="300" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -7053,7 +7076,7 @@
         <v>183</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D43" t="s">
         <v>147</v>
@@ -7101,13 +7124,13 @@
         <v>29</v>
       </c>
       <c r="U43" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>187</v>
       </c>
@@ -7115,7 +7138,7 @@
         <v>188</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D44" t="s">
         <v>147</v>
@@ -7128,7 +7151,7 @@
         <v>14</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>38</v>
@@ -7152,13 +7175,13 @@
         <v>30</v>
       </c>
       <c r="U44" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>189</v>
       </c>
@@ -7166,7 +7189,7 @@
         <v>190</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D45" t="s">
         <v>147</v>
@@ -7188,7 +7211,7 @@
         <v>133</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>38</v>
@@ -7212,13 +7235,13 @@
         <v>29</v>
       </c>
       <c r="U45" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>191</v>
       </c>
@@ -7226,7 +7249,7 @@
         <v>192</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D46" t="s">
         <v>147</v>
@@ -7274,13 +7297,13 @@
         <v>29</v>
       </c>
       <c r="U46" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" ht="285" x14ac:dyDescent="0.25">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>195</v>
       </c>
@@ -7315,7 +7338,7 @@
         <v>38</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>38</v>
@@ -7339,13 +7362,13 @@
         <v>30</v>
       </c>
       <c r="U47" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>620</v>
       </c>
@@ -7380,7 +7403,7 @@
         <v>38</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>38</v>
@@ -7404,10 +7427,10 @@
         <v>30</v>
       </c>
       <c r="U48" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -7418,7 +7441,7 @@
         <v>199</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D49" t="s">
         <v>38</v>
@@ -7463,13 +7486,13 @@
         <v>30</v>
       </c>
       <c r="U49" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="360" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>203</v>
       </c>
@@ -7504,7 +7527,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>208</v>
@@ -7528,10 +7551,10 @@
         <v>30</v>
       </c>
       <c r="U50" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="75" x14ac:dyDescent="0.25">
@@ -7593,10 +7616,10 @@
         <v>30</v>
       </c>
       <c r="U51" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -7634,7 +7657,7 @@
         <v>38</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>218</v>
@@ -7658,13 +7681,13 @@
         <v>30</v>
       </c>
       <c r="U52" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" ht="360" x14ac:dyDescent="0.25">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>224</v>
       </c>
@@ -7720,27 +7743,27 @@
         <v>30</v>
       </c>
       <c r="U53" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>756</v>
+      </c>
+      <c r="B54" t="s">
         <v>757</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="D54" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" t="s">
         <v>759</v>
-      </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
-      <c r="E54" t="s">
-        <v>760</v>
       </c>
       <c r="G54" t="s">
         <v>609</v>
@@ -7755,14 +7778,14 @@
         <v>248</v>
       </c>
       <c r="L54" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="M54" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="N54" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>763</v>
-      </c>
       <c r="O54" s="32" t="s">
         <v>29</v>
       </c>
@@ -7779,13 +7802,13 @@
         <v>30</v>
       </c>
       <c r="U54" s="32" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V54" s="34" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
         <v>229</v>
       </c>
@@ -7817,7 +7840,7 @@
         <v>231</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M55" s="3" t="s">
         <v>38</v>
@@ -7841,13 +7864,13 @@
         <v>30</v>
       </c>
       <c r="U55" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>234</v>
       </c>
@@ -7855,7 +7878,7 @@
         <v>235</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D56" t="s">
         <v>38</v>
@@ -7879,7 +7902,7 @@
         <v>237</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>38</v>
@@ -7903,13 +7926,13 @@
         <v>30</v>
       </c>
       <c r="U56" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>239</v>
       </c>
@@ -7968,10 +7991,10 @@
         <v>30</v>
       </c>
       <c r="U57" s="30" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8006,7 +8029,7 @@
         <v>248</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>38</v>
@@ -8030,10 +8053,10 @@
         <v>30</v>
       </c>
       <c r="U58" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -8068,7 +8091,7 @@
         <v>23</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>256</v>
@@ -8092,13 +8115,13 @@
         <v>29</v>
       </c>
       <c r="U59" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V59" s="3" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>257</v>
       </c>
@@ -8106,7 +8129,7 @@
         <v>258</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D60" t="s">
         <v>38</v>
@@ -8130,7 +8153,7 @@
         <v>260</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>38</v>
@@ -8154,10 +8177,10 @@
         <v>30</v>
       </c>
       <c r="U60" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8165,7 +8188,7 @@
         <v>652</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>38</v>
@@ -8193,7 +8216,7 @@
         <v>653</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="M61" s="15" t="s">
         <v>38</v>
@@ -8217,13 +8240,13 @@
         <v>30</v>
       </c>
       <c r="U61" s="30" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>262</v>
       </c>
@@ -8279,13 +8302,13 @@
         <v>30</v>
       </c>
       <c r="U62" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>497</v>
       </c>
@@ -8344,27 +8367,27 @@
         <v>30</v>
       </c>
       <c r="U63" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>763</v>
+      </c>
+      <c r="B64" t="s">
         <v>764</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="D64" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="D64" t="s">
-        <v>38</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>767</v>
       </c>
       <c r="G64" t="s">
         <v>15</v>
@@ -8382,13 +8405,13 @@
         <v>35</v>
       </c>
       <c r="L64" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="M64" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="M64" s="3" t="s">
-        <v>769</v>
-      </c>
       <c r="N64" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="O64" s="32" t="s">
         <v>29</v>
@@ -8406,13 +8429,13 @@
         <v>30</v>
       </c>
       <c r="U64" s="32" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V64" s="34" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>267</v>
       </c>
@@ -8468,10 +8491,10 @@
         <v>29</v>
       </c>
       <c r="U65" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -8509,7 +8532,7 @@
         <v>23</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>83</v>
@@ -8533,13 +8556,13 @@
         <v>29</v>
       </c>
       <c r="U66" s="30" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" ht="210" x14ac:dyDescent="0.25">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>615</v>
       </c>
@@ -8574,7 +8597,7 @@
         <v>38</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="M67" s="3" t="s">
         <v>38</v>
@@ -8598,13 +8621,13 @@
         <v>30</v>
       </c>
       <c r="U67" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>617</v>
       </c>
@@ -8639,7 +8662,7 @@
         <v>38</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>38</v>
@@ -8663,13 +8686,13 @@
         <v>30</v>
       </c>
       <c r="U68" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>581</v>
       </c>
@@ -8677,7 +8700,7 @@
         <v>665</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D69" t="s">
         <v>38</v>
@@ -8701,7 +8724,7 @@
         <v>582</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N69" s="11"/>
       <c r="O69" s="32" t="s">
@@ -8720,18 +8743,18 @@
         <v>29</v>
       </c>
       <c r="U69" s="30" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="225" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>502</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>38</v>
@@ -8783,18 +8806,18 @@
       </c>
       <c r="T70" s="32"/>
       <c r="U70" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>539</v>
       </c>
       <c r="B71" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>38</v>
@@ -8845,27 +8868,27 @@
         <v>30</v>
       </c>
       <c r="U71" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="72" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>770</v>
+      </c>
+      <c r="B72" t="s">
         <v>771</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="D72" t="s">
+        <v>38</v>
+      </c>
+      <c r="E72" s="1" t="s">
         <v>773</v>
-      </c>
-      <c r="D72" t="s">
-        <v>38</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>774</v>
       </c>
       <c r="G72" t="s">
         <v>0</v>
@@ -8883,14 +8906,14 @@
         <v>35</v>
       </c>
       <c r="L72" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="M72" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="M72" s="3" t="s">
+      <c r="N72" s="3" t="s">
         <v>776</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>777</v>
-      </c>
       <c r="O72" s="32" t="s">
         <v>29</v>
       </c>
@@ -8907,13 +8930,13 @@
         <v>29</v>
       </c>
       <c r="U72" s="32" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V72" s="34" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>273</v>
       </c>
@@ -8948,7 +8971,7 @@
         <v>23</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>278</v>
@@ -8975,10 +8998,10 @@
         <v>0</v>
       </c>
       <c r="U73" s="30" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="V73" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="74" spans="1:22" ht="90" x14ac:dyDescent="0.25">
@@ -9013,7 +9036,7 @@
         <v>23</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>509</v>
@@ -9037,13 +9060,13 @@
         <v>30</v>
       </c>
       <c r="U74" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V74" s="3" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>284</v>
       </c>
@@ -9051,7 +9074,7 @@
         <v>507</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D75" t="s">
         <v>38</v>
@@ -9078,7 +9101,7 @@
         <v>248</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="M75" s="3" t="s">
         <v>38</v>
@@ -9103,13 +9126,13 @@
       </c>
       <c r="T75" s="39"/>
       <c r="U75" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V75" s="3" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>287</v>
       </c>
@@ -9117,7 +9140,7 @@
         <v>288</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D76" t="s">
         <v>38</v>
@@ -9141,7 +9164,7 @@
         <v>35</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>38</v>
@@ -9165,13 +9188,13 @@
         <v>30</v>
       </c>
       <c r="U76" s="30" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="V76" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>290</v>
       </c>
@@ -9203,7 +9226,7 @@
         <v>23</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="M77" s="3" t="s">
         <v>38</v>
@@ -9230,13 +9253,13 @@
         <v>15</v>
       </c>
       <c r="U77" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V77" s="3" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>294</v>
       </c>
@@ -9244,7 +9267,7 @@
         <v>218</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D78" t="s">
         <v>38</v>
@@ -9268,7 +9291,7 @@
         <v>231</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M78" s="3" t="s">
         <v>296</v>
@@ -9292,13 +9315,13 @@
         <v>30</v>
       </c>
       <c r="U78" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V78" s="3" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>297</v>
       </c>
@@ -9354,13 +9377,13 @@
         <v>29</v>
       </c>
       <c r="U79" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V79" s="3" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>303</v>
       </c>
@@ -9383,7 +9406,7 @@
         <v>38</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M80" s="3" t="s">
         <v>306</v>
@@ -9407,10 +9430,10 @@
         <v>29</v>
       </c>
       <c r="U80" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V80" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="165" x14ac:dyDescent="0.25">
@@ -9450,10 +9473,10 @@
       <c r="N81" s="11"/>
       <c r="S81" s="33"/>
       <c r="U81" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V81" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="105" x14ac:dyDescent="0.25">
@@ -9512,13 +9535,13 @@
         <v>29</v>
       </c>
       <c r="U82" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V82" s="3" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>312</v>
       </c>
@@ -9553,7 +9576,7 @@
         <v>57</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>38</v>
@@ -9577,13 +9600,13 @@
         <v>30</v>
       </c>
       <c r="U83" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V83" s="3" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>315</v>
       </c>
@@ -9615,7 +9638,7 @@
         <v>23</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>38</v>
@@ -9639,13 +9662,13 @@
         <v>29</v>
       </c>
       <c r="U84" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V84" s="3" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>319</v>
       </c>
@@ -9701,13 +9724,13 @@
         <v>30</v>
       </c>
       <c r="U85" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V85" s="3" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" s="17" customFormat="1" ht="165" x14ac:dyDescent="0.25">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>325</v>
       </c>
@@ -9765,13 +9788,13 @@
       </c>
       <c r="T86" s="30"/>
       <c r="U86" s="30" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="V86" s="3" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" ht="225" x14ac:dyDescent="0.25">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>330</v>
       </c>
@@ -9827,163 +9850,156 @@
         <v>30</v>
       </c>
       <c r="U87" s="30" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="V87" s="3" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F88" t="s">
+        <v>38</v>
+      </c>
+      <c r="H88" s="1"/>
+      <c r="I88" s="10">
+        <v>1</v>
+      </c>
+      <c r="J88">
+        <v>2025</v>
+      </c>
+      <c r="K88" t="s">
+        <v>1088</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M88" t="s">
+        <v>1090</v>
+      </c>
+      <c r="N88" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="O88" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P88" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q88" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R88" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S88" s="38"/>
+      <c r="T88" s="32"/>
+      <c r="U88" s="32"/>
+      <c r="V88" s="34"/>
+    </row>
+    <row r="89" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>334</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>335</v>
       </c>
-      <c r="C88" t="s">
-        <v>38</v>
-      </c>
-      <c r="D88" t="s">
-        <v>38</v>
-      </c>
-      <c r="E88" s="1" t="s">
+      <c r="C89" t="s">
+        <v>38</v>
+      </c>
+      <c r="D89" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="F88" t="s">
-        <v>38</v>
-      </c>
-      <c r="G88" t="s">
+      <c r="F89" t="s">
+        <v>38</v>
+      </c>
+      <c r="G89" t="s">
         <v>2</v>
       </c>
-      <c r="I88" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J88">
+      <c r="I89" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J89">
         <v>2024</v>
       </c>
-      <c r="K88" t="s">
+      <c r="K89" t="s">
         <v>327</v>
       </c>
-      <c r="L88" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="M88" s="3" t="s">
+      <c r="M89" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="N88" s="3" t="s">
+      <c r="N89" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="O88" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P88" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q88" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R88" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S88" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U88" s="30" t="s">
-        <v>904</v>
-      </c>
-      <c r="V88" s="3" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22" ht="75" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="O89" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P89" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q89" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R89" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S89" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U89" s="30" t="s">
+        <v>903</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>551</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B90" t="s">
         <v>552</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C90" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D90" t="s">
         <v>558</v>
       </c>
-      <c r="E89" s="1" t="s">
+      <c r="E90" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F90" t="s">
         <v>555</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G90" t="s">
         <v>19</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H90" t="s">
         <v>9</v>
       </c>
-      <c r="I89" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J89">
-        <v>2022</v>
-      </c>
-      <c r="K89" t="s">
-        <v>38</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="O89" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P89" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q89" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R89" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S89" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="U89" s="30" t="s">
-        <v>901</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" ht="255" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>340</v>
-      </c>
-      <c r="B90" t="s">
-        <v>341</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D90" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="F90" t="s">
-        <v>38</v>
-      </c>
-      <c r="G90" t="s">
-        <v>13</v>
-      </c>
-      <c r="I90" s="10">
-        <v>0.3</v>
+      <c r="I90" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="J90">
         <v>2022</v>
@@ -9992,13 +10008,13 @@
         <v>38</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>873</v>
+        <v>557</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>716</v>
+        <v>556</v>
       </c>
       <c r="O90" s="32" t="s">
         <v>29</v>
@@ -10013,54 +10029,54 @@
         <v>29</v>
       </c>
       <c r="S90" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U90" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V90" s="3" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" ht="165" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>533</v>
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>340</v>
       </c>
       <c r="B91" t="s">
-        <v>534</v>
+        <v>341</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>536</v>
+        <v>342</v>
       </c>
       <c r="D91" t="s">
         <v>38</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>537</v>
+        <v>343</v>
       </c>
       <c r="F91" t="s">
         <v>38</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I91" s="10">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J91">
         <v>2022</v>
       </c>
       <c r="K91" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>535</v>
+        <v>872</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>538</v>
+        <v>83</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="O91" s="32" t="s">
         <v>29</v>
@@ -10075,36 +10091,36 @@
         <v>29</v>
       </c>
       <c r="S91" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U91" s="30" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="V91" s="3" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" ht="105" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>344</v>
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>533</v>
       </c>
       <c r="B92" t="s">
-        <v>345</v>
+        <v>534</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>346</v>
+        <v>536</v>
       </c>
       <c r="D92" t="s">
         <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>347</v>
+        <v>537</v>
       </c>
       <c r="F92" t="s">
         <v>38</v>
       </c>
       <c r="G92" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I92" s="10">
         <v>1</v>
@@ -10113,16 +10129,16 @@
         <v>2022</v>
       </c>
       <c r="K92" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>871</v>
+        <v>535</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>38</v>
+        <v>538</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="O92" s="32" t="s">
         <v>29</v>
@@ -10140,51 +10156,51 @@
         <v>29</v>
       </c>
       <c r="U92" s="30" t="s">
-        <v>919</v>
+        <v>898</v>
       </c>
       <c r="V92" s="3" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B93" t="s">
-        <v>272</v>
+        <v>345</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>808</v>
+        <v>346</v>
       </c>
       <c r="D93" t="s">
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F93" t="s">
         <v>38</v>
       </c>
       <c r="G93" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I93" s="10">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J93">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K93" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>349</v>
+        <v>870</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>351</v>
+        <v>38</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="O93" s="32" t="s">
         <v>29</v>
@@ -10202,51 +10218,51 @@
         <v>29</v>
       </c>
       <c r="U93" s="30" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
       <c r="V93" s="3" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B94" t="s">
-        <v>353</v>
-      </c>
-      <c r="C94" t="s">
-        <v>38</v>
+        <v>272</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>807</v>
       </c>
       <c r="D94" t="s">
         <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="F94" t="s">
-        <v>355</v>
+        <v>38</v>
       </c>
       <c r="G94" t="s">
-        <v>10</v>
-      </c>
-      <c r="I94" s="10" t="s">
-        <v>354</v>
+        <v>0</v>
+      </c>
+      <c r="I94" s="10">
+        <v>0.3</v>
       </c>
       <c r="J94">
         <v>2019</v>
       </c>
       <c r="K94" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>872</v>
+        <v>349</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>38</v>
+        <v>351</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>38</v>
+        <v>719</v>
       </c>
       <c r="O94" s="32" t="s">
         <v>29</v>
@@ -10255,372 +10271,371 @@
         <v>29</v>
       </c>
       <c r="Q94" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R94" s="32" t="s">
         <v>29</v>
       </c>
       <c r="S94" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U94" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V94" s="3" t="s">
-        <v>1005</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>352</v>
+      </c>
+      <c r="B95" t="s">
+        <v>353</v>
+      </c>
+      <c r="C95" t="s">
+        <v>38</v>
+      </c>
+      <c r="D95" t="s">
+        <v>38</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F95" t="s">
+        <v>355</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="J95">
+        <v>2019</v>
+      </c>
+      <c r="K95" t="s">
+        <v>38</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O95" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P95" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q95" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R95" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S95" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U95" s="30" t="s">
+        <v>900</v>
+      </c>
+      <c r="V95" s="3" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>357</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>358</v>
       </c>
-      <c r="C95" t="s">
-        <v>38</v>
-      </c>
-      <c r="D95" t="s">
-        <v>38</v>
-      </c>
-      <c r="E95" s="1" t="s">
+      <c r="C96" t="s">
+        <v>38</v>
+      </c>
+      <c r="D96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="F95" t="s">
-        <v>38</v>
-      </c>
-      <c r="G95" t="s">
+      <c r="F96" t="s">
+        <v>38</v>
+      </c>
+      <c r="G96" t="s">
         <v>7</v>
       </c>
-      <c r="I95" s="10" t="s">
+      <c r="I96" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="J95">
+      <c r="J96">
         <v>2020</v>
       </c>
-      <c r="K95" t="s">
-        <v>38</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>1060</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N95" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O95" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P95" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q95" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="R95" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S95" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="U95" s="30" t="s">
-        <v>923</v>
-      </c>
-      <c r="V95" s="3" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22" ht="150" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>361</v>
-      </c>
-      <c r="B96" t="s">
-        <v>362</v>
-      </c>
-      <c r="C96" t="s">
-        <v>38</v>
-      </c>
-      <c r="D96" t="s">
-        <v>38</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F96" t="s">
-        <v>38</v>
-      </c>
-      <c r="G96" t="s">
-        <v>12</v>
-      </c>
-      <c r="I96" s="10">
-        <v>5</v>
-      </c>
-      <c r="J96">
-        <v>2005</v>
-      </c>
       <c r="K96" t="s">
         <v>38</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>864</v>
+        <v>1059</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O96" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="P96" s="37" t="s">
-        <v>29</v>
+      <c r="P96" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="Q96" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R96" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S96" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U96" s="30" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="V96" s="3" t="s">
-        <v>994</v>
+        <v>938</v>
       </c>
     </row>
     <row r="97" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>361</v>
+      </c>
+      <c r="B97" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" t="s">
+        <v>38</v>
+      </c>
+      <c r="D97" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="F97" t="s">
+        <v>38</v>
+      </c>
+      <c r="G97" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" s="10">
+        <v>5</v>
+      </c>
+      <c r="J97">
+        <v>2005</v>
+      </c>
+      <c r="K97" t="s">
+        <v>38</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O97" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P97" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q97" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R97" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S97" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U97" s="30" t="s">
+        <v>918</v>
+      </c>
+      <c r="V97" s="3" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>364</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B98" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D98" t="s">
         <v>32</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F97" t="s">
-        <v>38</v>
-      </c>
-      <c r="G97" t="s">
+      <c r="F98" t="s">
+        <v>38</v>
+      </c>
+      <c r="G98" t="s">
         <v>3</v>
       </c>
-      <c r="I97" s="10" t="s">
+      <c r="I98" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="J97">
+      <c r="J98">
         <v>2020</v>
       </c>
-      <c r="K97" t="s">
+      <c r="K98" t="s">
         <v>23</v>
       </c>
-      <c r="L97" s="3" t="s">
+      <c r="L98" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="M97" s="3" t="s">
+      <c r="M98" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="N97" s="3" t="s">
+      <c r="N98" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="O97" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P97" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q97" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R97" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S97" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U97" s="30" t="s">
+      <c r="O98" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P98" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q98" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R98" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S98" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U98" s="30" t="s">
+        <v>918</v>
+      </c>
+      <c r="V98" s="3" t="s">
         <v>919</v>
-      </c>
-      <c r="V97" s="3" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="98" spans="1:26" ht="75" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>369</v>
-      </c>
-      <c r="B98" t="s">
-        <v>306</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="D98" t="s">
-        <v>38</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="F98" t="s">
-        <v>38</v>
-      </c>
-      <c r="G98" t="s">
-        <v>5</v>
-      </c>
-      <c r="I98" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J98">
-        <v>2018</v>
-      </c>
-      <c r="K98" t="s">
-        <v>85</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="N98" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="O98" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P98" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q98" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R98" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S98" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="U98" s="30" t="s">
-        <v>901</v>
-      </c>
-      <c r="V98" s="3" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="99" spans="1:26" ht="135" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>369</v>
+      </c>
+      <c r="B99" t="s">
+        <v>306</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D99" t="s">
+        <v>38</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F99" t="s">
+        <v>38</v>
+      </c>
+      <c r="G99" t="s">
+        <v>5</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J99">
+        <v>2018</v>
+      </c>
+      <c r="K99" t="s">
+        <v>85</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="O99" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P99" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q99" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R99" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S99" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="U99" s="30" t="s">
+        <v>900</v>
+      </c>
+      <c r="V99" s="3" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>831</v>
+      </c>
+      <c r="B100" t="s">
         <v>832</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C100" s="27" t="s">
         <v>833</v>
       </c>
-      <c r="C99" s="27" t="s">
+      <c r="D100" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="D99" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="F100" t="s">
+        <v>38</v>
+      </c>
+      <c r="G100" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H100" s="1"/>
+      <c r="I100" s="10" t="s">
         <v>835</v>
       </c>
-      <c r="F99" t="s">
-        <v>38</v>
-      </c>
-      <c r="G99" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="H99" s="1"/>
-      <c r="I99" s="10" t="s">
+      <c r="J100">
+        <v>2025</v>
+      </c>
+      <c r="K100" t="s">
         <v>836</v>
       </c>
-      <c r="J99">
-        <v>2025</v>
-      </c>
-      <c r="K99" t="s">
+      <c r="L100" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="L99" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N99" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O99" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P99" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q99" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R99" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S99" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="T99" s="32"/>
-      <c r="U99" s="32" t="s">
-        <v>930</v>
-      </c>
-      <c r="V99" s="34" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="100" spans="1:26" ht="105" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>373</v>
-      </c>
-      <c r="B100" t="s">
-        <v>374</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D100" t="s">
-        <v>123</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="F100" t="s">
-        <v>38</v>
-      </c>
-      <c r="G100" t="s">
-        <v>14</v>
-      </c>
-      <c r="I100" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="J100">
-        <v>2022</v>
-      </c>
-      <c r="K100" t="s">
-        <v>23</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>1062</v>
-      </c>
       <c r="M100" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>721</v>
+        <v>38</v>
+      </c>
+      <c r="N100" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="O100" s="32" t="s">
         <v>29</v>
@@ -10637,37 +10652,38 @@
       <c r="S100" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="U100" s="30" t="s">
+      <c r="T100" s="32"/>
+      <c r="U100" s="32" t="s">
+        <v>929</v>
+      </c>
+      <c r="V100" s="34" t="s">
         <v>899</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="101" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B101" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D101" t="s">
         <v>123</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="F101" t="s">
         <v>38</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I101" s="10" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="J101">
         <v>2022</v>
@@ -10676,13 +10692,13 @@
         <v>23</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="O101" s="32" t="s">
         <v>29</v>
@@ -10697,156 +10713,159 @@
         <v>29</v>
       </c>
       <c r="S101" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U101" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V101" s="3" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="102" spans="1:26" ht="150" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1080</v>
+        <v>378</v>
       </c>
       <c r="B102" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C102" s="41" t="s">
-        <v>1082</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>38</v>
+        <v>379</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D102" t="s">
+        <v>123</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F102" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="G102" s="29" t="s">
+        <v>381</v>
+      </c>
+      <c r="F102" t="s">
+        <v>38</v>
+      </c>
+      <c r="G102" t="s">
         <v>15</v>
       </c>
-      <c r="H102" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="I102" s="10">
-        <v>0.5</v>
+      <c r="I102" s="10" t="s">
+        <v>380</v>
       </c>
       <c r="J102">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="K102" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>1083</v>
-      </c>
-      <c r="N102" s="11"/>
-      <c r="S102" s="33"/>
-      <c r="T102" s="32"/>
-      <c r="U102" s="32"/>
-      <c r="V102" s="34"/>
+        <v>1062</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="O102" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P102" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q102" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R102" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S102" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U102" s="30" t="s">
+        <v>898</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>942</v>
+      </c>
     </row>
     <row r="103" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>383</v>
+        <v>1079</v>
       </c>
       <c r="B103" t="s">
-        <v>384</v>
-      </c>
-      <c r="C103" t="s">
-        <v>38</v>
-      </c>
-      <c r="D103" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C103" s="41" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D103" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="F103" t="s">
-        <v>38</v>
-      </c>
-      <c r="G103" t="s">
-        <v>611</v>
+        <v>1081</v>
+      </c>
+      <c r="F103" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G103" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="29" t="s">
+        <v>17</v>
       </c>
       <c r="I103" s="10">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J103">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="K103" t="s">
-        <v>385</v>
+        <v>133</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="O103" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P103" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q103" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R103" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S103" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="U103" s="30" t="s">
-        <v>901</v>
-      </c>
-      <c r="V103" s="3" t="s">
-        <v>1013</v>
-      </c>
+        <v>1082</v>
+      </c>
+      <c r="N103" s="11"/>
+      <c r="S103" s="33"/>
+      <c r="T103" s="32"/>
+      <c r="U103" s="32"/>
+      <c r="V103" s="34"/>
     </row>
     <row r="104" spans="1:26" ht="285" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>600</v>
+        <v>383</v>
       </c>
       <c r="B104" t="s">
-        <v>601</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>603</v>
+        <v>384</v>
+      </c>
+      <c r="C104" t="s">
+        <v>38</v>
+      </c>
+      <c r="D104" t="s">
+        <v>38</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>604</v>
+        <v>386</v>
       </c>
       <c r="F104" t="s">
         <v>38</v>
       </c>
       <c r="G104" t="s">
-        <v>8</v>
-      </c>
-      <c r="I104" s="10" t="s">
-        <v>236</v>
+        <v>611</v>
+      </c>
+      <c r="I104" s="10">
+        <v>4</v>
       </c>
       <c r="J104">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="K104" t="s">
-        <v>133</v>
+        <v>385</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>602</v>
+        <v>874</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>38</v>
+        <v>387</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>723</v>
+        <v>388</v>
       </c>
       <c r="O104" s="32" t="s">
         <v>29</v>
@@ -10858,57 +10877,54 @@
         <v>29</v>
       </c>
       <c r="R104" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S104" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U104" s="30" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="V104" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="105" spans="1:26" ht="195" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>389</v>
-      </c>
-      <c r="B105" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="C105" t="s">
-        <v>38</v>
-      </c>
-      <c r="D105" t="s">
-        <v>38</v>
+        <v>600</v>
+      </c>
+      <c r="B105" t="s">
+        <v>601</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>603</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>58</v>
+        <v>604</v>
       </c>
       <c r="F105" t="s">
         <v>38</v>
       </c>
       <c r="G105" t="s">
-        <v>4</v>
-      </c>
-      <c r="I105" s="10">
-        <v>1.1000000000000001</v>
+        <v>8</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="J105">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="K105" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="L105" s="3" t="s">
-        <v>876</v>
+        <v>602</v>
       </c>
       <c r="M105" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="N105" s="15" t="s">
-        <v>38</v>
+      <c r="N105" s="3" t="s">
+        <v>723</v>
       </c>
       <c r="O105" s="32" t="s">
         <v>29</v>
@@ -10917,60 +10933,60 @@
         <v>29</v>
       </c>
       <c r="Q105" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R105" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S105" s="33" t="s">
         <v>30</v>
       </c>
       <c r="U105" s="30" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="V105" s="3" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="106" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>391</v>
-      </c>
-      <c r="B106" t="s">
-        <v>392</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C106" t="s">
+        <v>38</v>
       </c>
       <c r="D106" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="F106" t="s">
         <v>38</v>
       </c>
       <c r="G106" t="s">
-        <v>14</v>
-      </c>
-      <c r="I106" s="10" t="s">
-        <v>393</v>
+        <v>4</v>
+      </c>
+      <c r="I106" s="10">
+        <v>1.1000000000000001</v>
       </c>
       <c r="J106">
         <v>2020</v>
       </c>
       <c r="K106" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L106" s="3" t="s">
-        <v>1053</v>
+        <v>875</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="N106" s="3" t="s">
-        <v>396</v>
+        <v>38</v>
+      </c>
+      <c r="N106" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="O106" s="32" t="s">
         <v>29</v>
@@ -10979,60 +10995,60 @@
         <v>29</v>
       </c>
       <c r="Q106" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R106" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S106" s="33" t="s">
         <v>30</v>
       </c>
       <c r="U106" s="30" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="V106" s="3" t="s">
-        <v>921</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="107" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B107" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D107" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>400</v>
+        <v>26</v>
       </c>
       <c r="F107" t="s">
         <v>38</v>
       </c>
       <c r="G107" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I107" s="10" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="J107">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K107" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>724</v>
+        <v>396</v>
       </c>
       <c r="O107" s="32" t="s">
         <v>29</v>
@@ -11047,39 +11063,39 @@
         <v>29</v>
       </c>
       <c r="S107" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U107" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V107" s="3" t="s">
-        <v>944</v>
+        <v>920</v>
       </c>
     </row>
     <row r="108" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="B108" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="D108" t="s">
         <v>123</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="F108" t="s">
         <v>38</v>
       </c>
       <c r="G108" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I108" s="10" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="J108">
         <v>2022</v>
@@ -11088,13 +11104,13 @@
         <v>23</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="O108" s="32" t="s">
         <v>29</v>
@@ -11109,54 +11125,54 @@
         <v>29</v>
       </c>
       <c r="S108" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U108" s="30" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="V108" s="3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="109" spans="1:26" ht="165" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B109" t="s">
-        <v>425</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>807</v>
+        <v>420</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="D109" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F109" t="s">
         <v>38</v>
       </c>
       <c r="G109" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I109" s="10" t="s">
-        <v>38</v>
+        <v>421</v>
       </c>
       <c r="J109">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="K109" t="s">
-        <v>248</v>
+        <v>23</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>426</v>
+        <v>1064</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>429</v>
+        <v>733</v>
       </c>
       <c r="O109" s="32" t="s">
         <v>29</v>
@@ -11168,33 +11184,33 @@
         <v>29</v>
       </c>
       <c r="R109" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S109" s="33" t="s">
         <v>30</v>
       </c>
       <c r="U109" s="30" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="V109" s="3" t="s">
-        <v>1036</v>
+        <v>944</v>
       </c>
     </row>
     <row r="110" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B110" t="s">
-        <v>404</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>432</v>
+        <v>425</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>806</v>
       </c>
       <c r="D110" t="s">
-        <v>405</v>
+        <v>38</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="F110" t="s">
         <v>38</v>
@@ -11203,124 +11219,123 @@
         <v>10</v>
       </c>
       <c r="I110" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J110">
+        <v>2016</v>
+      </c>
+      <c r="K110" t="s">
+        <v>248</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="N110" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="O110" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P110" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q110" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R110" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S110" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U110" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="V110" s="3" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="111" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>430</v>
+      </c>
+      <c r="B111" t="s">
+        <v>404</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D111" t="s">
+        <v>405</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F111" t="s">
+        <v>38</v>
+      </c>
+      <c r="G111" t="s">
+        <v>10</v>
+      </c>
+      <c r="I111" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="J110">
+      <c r="J111">
         <v>2024</v>
       </c>
-      <c r="K110" t="s">
+      <c r="K111" t="s">
         <v>98</v>
       </c>
-      <c r="L110" s="3" t="s">
+      <c r="L111" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="M110" s="3" t="s">
+      <c r="M111" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="N110" s="3" t="s">
+      <c r="N111" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="O110" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P110" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q110" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R110" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S110" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="U110" s="30" t="s">
-        <v>901</v>
-      </c>
-      <c r="V110" s="3" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" ht="90" x14ac:dyDescent="0.25">
-      <c r="A111" s="17" t="s">
-        <v>633</v>
-      </c>
-      <c r="B111" s="17" t="s">
-        <v>779</v>
-      </c>
-      <c r="C111" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="D111" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="E111" s="19" t="s">
-        <v>634</v>
-      </c>
-      <c r="F111" t="s">
-        <v>38</v>
-      </c>
-      <c r="G111" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H111" s="17"/>
-      <c r="I111" s="21" t="s">
-        <v>622</v>
-      </c>
-      <c r="J111" s="17">
-        <v>2025</v>
-      </c>
-      <c r="K111" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="L111" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="M111" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="N111" s="15" t="s">
-        <v>636</v>
-      </c>
-      <c r="O111" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P111" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q111" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="R111" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="S111" s="38" t="s">
-        <v>30</v>
+      <c r="O111" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P111" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q111" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R111" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S111" s="33" t="s">
+        <v>29</v>
       </c>
       <c r="U111" s="30" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="V111" s="3" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="Z111" s="3"/>
     </row>
     <row r="112" spans="1:26" ht="150" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>792</v>
+        <v>634</v>
       </c>
       <c r="D112" s="20" t="s">
         <v>405</v>
       </c>
       <c r="E112" s="19" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="F112" t="s">
         <v>38</v>
@@ -11328,9 +11343,7 @@
       <c r="G112" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H112" s="17" t="s">
-        <v>608</v>
-      </c>
+      <c r="H112" s="17"/>
       <c r="I112" s="21" t="s">
         <v>622</v>
       </c>
@@ -11341,125 +11354,125 @@
         <v>98</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="M112" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="N112" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="O112" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="P112" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q112" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="R112" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="S112" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="U112" s="30" t="s">
+        <v>898</v>
+      </c>
+      <c r="V112" s="3" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22" ht="285" x14ac:dyDescent="0.25">
+      <c r="A113" s="17" t="s">
+        <v>637</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>779</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="D113" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>638</v>
+      </c>
+      <c r="F113" t="s">
+        <v>38</v>
+      </c>
+      <c r="G113" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H113" s="17" t="s">
+        <v>608</v>
+      </c>
+      <c r="I113" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="J113" s="17">
+        <v>2025</v>
+      </c>
+      <c r="K113" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="L113" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="M113" s="15" t="s">
         <v>639</v>
       </c>
-      <c r="N112" s="15" t="s">
+      <c r="N113" s="15" t="s">
         <v>640</v>
       </c>
-      <c r="O112" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P112" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q112" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="R112" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="S112" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="U112" s="30" t="s">
-        <v>904</v>
-      </c>
-      <c r="V112" s="3" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="113" spans="1:22" ht="285" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>623</v>
-      </c>
-      <c r="B113" t="s">
-        <v>781</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D113" t="s">
-        <v>405</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="F113" t="s">
-        <v>402</v>
-      </c>
-      <c r="G113" t="s">
-        <v>10</v>
-      </c>
-      <c r="H113" t="s">
-        <v>0</v>
-      </c>
-      <c r="I113" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="J113">
-        <v>2025</v>
-      </c>
-      <c r="K113" t="s">
-        <v>98</v>
-      </c>
-      <c r="L113" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="M113" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="N113" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="O113" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P113" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q113" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R113" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S113" s="33" t="s">
-        <v>29</v>
+      <c r="O113" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="P113" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q113" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="R113" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="S113" s="38" t="s">
+        <v>30</v>
       </c>
       <c r="U113" s="30" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="V113" s="3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="114" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B114" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>793</v>
+        <v>403</v>
       </c>
       <c r="D114" t="s">
         <v>405</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F114" t="s">
-        <v>38</v>
+        <v>402</v>
       </c>
       <c r="G114" t="s">
         <v>10</v>
       </c>
       <c r="H114" t="s">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="I114" s="10" t="s">
         <v>622</v>
@@ -11471,179 +11484,179 @@
         <v>98</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="M114" s="3" t="s">
         <v>404</v>
       </c>
       <c r="N114" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="O114" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P114" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q114" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R114" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S114" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="U114" s="30" t="s">
+        <v>900</v>
+      </c>
+      <c r="V114" s="3" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>625</v>
+      </c>
+      <c r="B115" t="s">
+        <v>781</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="D115" t="s">
+        <v>405</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F115" t="s">
+        <v>38</v>
+      </c>
+      <c r="G115" t="s">
+        <v>10</v>
+      </c>
+      <c r="H115" t="s">
+        <v>242</v>
+      </c>
+      <c r="I115" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="J115">
+        <v>2025</v>
+      </c>
+      <c r="K115" t="s">
+        <v>98</v>
+      </c>
+      <c r="L115" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="M115" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="N115" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="O114" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P114" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q114" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R114" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S114" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="U114" s="30" t="s">
-        <v>923</v>
-      </c>
-      <c r="V114" s="3" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="115" spans="1:22" ht="255" x14ac:dyDescent="0.25">
-      <c r="A115" s="17" t="s">
+      <c r="O115" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P115" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q115" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R115" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S115" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="U115" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="V115" s="3" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+      <c r="A116" s="17" t="s">
         <v>641</v>
       </c>
-      <c r="B115" s="17" t="s">
-        <v>783</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>794</v>
-      </c>
-      <c r="D115" s="20" t="s">
+      <c r="B116" s="17" t="s">
+        <v>782</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>793</v>
+      </c>
+      <c r="D116" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="E115" s="19" t="s">
+      <c r="E116" s="19" t="s">
         <v>642</v>
       </c>
-      <c r="F115" t="s">
-        <v>38</v>
-      </c>
-      <c r="G115" s="17" t="s">
+      <c r="F116" t="s">
+        <v>38</v>
+      </c>
+      <c r="G116" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H115" s="17"/>
-      <c r="I115" s="21" t="s">
+      <c r="H116" s="17"/>
+      <c r="I116" s="21" t="s">
         <v>622</v>
       </c>
-      <c r="J115" s="17">
+      <c r="J116" s="17">
         <v>2025</v>
       </c>
-      <c r="K115" s="17" t="s">
+      <c r="K116" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="L115" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="M115" s="15" t="s">
+      <c r="L116" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="M116" s="15" t="s">
         <v>643</v>
       </c>
-      <c r="N115" s="15" t="s">
+      <c r="N116" s="15" t="s">
         <v>644</v>
       </c>
-      <c r="O115" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P115" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q115" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="R115" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="S115" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="U115" s="30" t="s">
-        <v>919</v>
-      </c>
-      <c r="V115" s="3" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="116" spans="1:22" ht="135" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>624</v>
-      </c>
-      <c r="B116" t="s">
-        <v>784</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D116" t="s">
-        <v>405</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="F116" t="s">
-        <v>38</v>
-      </c>
-      <c r="G116" t="s">
-        <v>10</v>
-      </c>
-      <c r="H116" t="s">
-        <v>4</v>
-      </c>
-      <c r="I116" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="J116">
-        <v>2025</v>
-      </c>
-      <c r="K116" t="s">
-        <v>98</v>
-      </c>
-      <c r="L116" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="M116" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="N116" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="O116" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P116" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q116" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R116" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S116" s="33" t="s">
+      <c r="O116" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="P116" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q116" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="R116" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="S116" s="38" t="s">
         <v>30</v>
       </c>
       <c r="U116" s="30" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
       <c r="V116" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="117" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B117" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D117" t="s">
         <v>405</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F117" t="s">
         <v>38</v>
@@ -11652,7 +11665,7 @@
         <v>10</v>
       </c>
       <c r="H117" t="s">
-        <v>409</v>
+        <v>4</v>
       </c>
       <c r="I117" s="10" t="s">
         <v>622</v>
@@ -11664,13 +11677,13 @@
         <v>98</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M117" s="3" t="s">
         <v>404</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="O117" s="32" t="s">
         <v>29</v>
@@ -11688,27 +11701,27 @@
         <v>30</v>
       </c>
       <c r="U117" s="30" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
       <c r="V117" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="118" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B118" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D118" t="s">
         <v>405</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F118" t="s">
         <v>38</v>
@@ -11717,7 +11730,7 @@
         <v>10</v>
       </c>
       <c r="H118" t="s">
-        <v>4</v>
+        <v>409</v>
       </c>
       <c r="I118" s="10" t="s">
         <v>622</v>
@@ -11729,181 +11742,181 @@
         <v>98</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="M118" s="3" t="s">
         <v>404</v>
       </c>
       <c r="N118" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="O118" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P118" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q118" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R118" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S118" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U118" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="V118" s="3" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>628</v>
+      </c>
+      <c r="B119" t="s">
+        <v>785</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="D119" t="s">
+        <v>405</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F119" t="s">
+        <v>38</v>
+      </c>
+      <c r="G119" t="s">
+        <v>10</v>
+      </c>
+      <c r="H119" t="s">
+        <v>4</v>
+      </c>
+      <c r="I119" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="J119">
+        <v>2025</v>
+      </c>
+      <c r="K119" t="s">
+        <v>98</v>
+      </c>
+      <c r="L119" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="M119" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="N119" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="O118" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P118" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q118" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R118" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S118" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U118" s="30" t="s">
-        <v>906</v>
-      </c>
-      <c r="V118" s="3" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="119" spans="1:22" ht="120" x14ac:dyDescent="0.25">
-      <c r="A119" s="17" t="s">
+      <c r="O119" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P119" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q119" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R119" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S119" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U119" s="30" t="s">
+        <v>905</v>
+      </c>
+      <c r="V119" s="3" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A120" s="17" t="s">
         <v>645</v>
       </c>
-      <c r="B119" s="17" t="s">
-        <v>787</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>798</v>
-      </c>
-      <c r="D119" s="20" t="s">
+      <c r="B120" s="17" t="s">
+        <v>786</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>797</v>
+      </c>
+      <c r="D120" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="E119" s="19" t="s">
+      <c r="E120" s="19" t="s">
         <v>646</v>
       </c>
-      <c r="F119" t="s">
-        <v>38</v>
-      </c>
-      <c r="G119" s="17" t="s">
+      <c r="F120" t="s">
+        <v>38</v>
+      </c>
+      <c r="G120" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H119" s="17" t="s">
+      <c r="H120" s="17" t="s">
         <v>610</v>
       </c>
-      <c r="I119" s="21" t="s">
+      <c r="I120" s="21" t="s">
         <v>622</v>
       </c>
-      <c r="J119" s="17">
+      <c r="J120" s="17">
         <v>2025</v>
       </c>
-      <c r="K119" s="17" t="s">
+      <c r="K120" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="L119" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="M119" s="15" t="s">
+      <c r="L120" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="M120" s="15" t="s">
         <v>404</v>
       </c>
-      <c r="N119" s="15" t="s">
+      <c r="N120" s="15" t="s">
         <v>647</v>
       </c>
-      <c r="O119" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P119" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q119" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="R119" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="S119" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="U119" s="30" t="s">
-        <v>899</v>
-      </c>
-      <c r="V119" s="3" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="120" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>627</v>
-      </c>
-      <c r="B120" t="s">
-        <v>788</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D120" t="s">
-        <v>405</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F120" t="s">
-        <v>38</v>
-      </c>
-      <c r="G120" t="s">
-        <v>10</v>
-      </c>
-      <c r="H120" t="s">
-        <v>0</v>
-      </c>
-      <c r="I120" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="J120">
-        <v>2025</v>
-      </c>
-      <c r="K120" t="s">
-        <v>98</v>
-      </c>
-      <c r="L120" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="M120" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="N120" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="O120" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P120" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q120" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R120" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S120" s="33" t="s">
+      <c r="O120" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="P120" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q120" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="R120" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="S120" s="38" t="s">
         <v>30</v>
       </c>
       <c r="U120" s="30" t="s">
-        <v>930</v>
+        <v>898</v>
       </c>
       <c r="V120" s="3" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="121" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B121" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D121" t="s">
         <v>405</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F121" t="s">
         <v>38</v>
@@ -11911,23 +11924,26 @@
       <c r="G121" t="s">
         <v>10</v>
       </c>
+      <c r="H121" t="s">
+        <v>0</v>
+      </c>
       <c r="I121" s="10" t="s">
-        <v>406</v>
+        <v>622</v>
       </c>
       <c r="J121">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="K121" t="s">
         <v>98</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>415</v>
+        <v>887</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>38</v>
+        <v>413</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="O121" s="32" t="s">
         <v>29</v>
@@ -11942,30 +11958,30 @@
         <v>29</v>
       </c>
       <c r="S121" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U121" s="30" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="V121" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="122" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B122" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>418</v>
+        <v>799</v>
       </c>
       <c r="D122" t="s">
         <v>405</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F122" t="s">
         <v>38</v>
@@ -11973,26 +11989,24 @@
       <c r="G122" t="s">
         <v>10</v>
       </c>
-      <c r="H122" t="s">
-        <v>417</v>
-      </c>
+      <c r="H122"/>
       <c r="I122" s="10" t="s">
-        <v>622</v>
+        <v>406</v>
       </c>
       <c r="J122">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="K122" t="s">
         <v>98</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>889</v>
+        <v>415</v>
       </c>
       <c r="M122" s="3" t="s">
-        <v>632</v>
+        <v>38</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="O122" s="32" t="s">
         <v>29</v>
@@ -12007,210 +12021,216 @@
         <v>29</v>
       </c>
       <c r="S122" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T122" s="30"/>
       <c r="U122" s="30" t="s">
-        <v>906</v>
+        <v>929</v>
       </c>
       <c r="V122" s="3" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>626</v>
+      </c>
+      <c r="B123" t="s">
+        <v>789</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D123" t="s">
+        <v>405</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F123" t="s">
+        <v>38</v>
+      </c>
+      <c r="G123" t="s">
+        <v>10</v>
+      </c>
+      <c r="H123" t="s">
+        <v>417</v>
+      </c>
+      <c r="I123" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="J123">
+        <v>2025</v>
+      </c>
+      <c r="K123" t="s">
+        <v>98</v>
+      </c>
+      <c r="L123" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="M123" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="N123" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="O123" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P123" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q123" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R123" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S123" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U123" s="30" t="s">
+        <v>905</v>
+      </c>
+      <c r="V123" s="3" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+      <c r="A124" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>790</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>800</v>
+      </c>
+      <c r="D124" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E124" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="F124" t="s">
+        <v>38</v>
+      </c>
+      <c r="G124" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H124" s="17"/>
+      <c r="I124" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="J124" s="17">
+        <v>2025</v>
+      </c>
+      <c r="K124" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="L124" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="M124" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="N124" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="O124" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="P124" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q124" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="R124" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="S124" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="U124" s="30" t="s">
+        <v>903</v>
+      </c>
+      <c r="V124" s="3" t="s">
         <v>1031</v>
-      </c>
-    </row>
-    <row r="123" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A123" s="17" t="s">
-        <v>648</v>
-      </c>
-      <c r="B123" s="17" t="s">
-        <v>791</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>801</v>
-      </c>
-      <c r="D123" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="E123" s="19" t="s">
-        <v>649</v>
-      </c>
-      <c r="F123" t="s">
-        <v>38</v>
-      </c>
-      <c r="G123" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="H123" s="17"/>
-      <c r="I123" s="21" t="s">
-        <v>622</v>
-      </c>
-      <c r="J123" s="17">
-        <v>2025</v>
-      </c>
-      <c r="K123" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="L123" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="M123" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="N123" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="O123" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P123" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q123" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="R123" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="S123" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="U123" s="30" t="s">
-        <v>904</v>
-      </c>
-      <c r="V123" s="3" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="124" spans="1:22" ht="150" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>433</v>
-      </c>
-      <c r="B124" t="s">
-        <v>434</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="D124" t="s">
-        <v>38</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="F124" t="s">
-        <v>38</v>
-      </c>
-      <c r="G124" t="s">
-        <v>17</v>
-      </c>
-      <c r="H124" t="s">
-        <v>6</v>
-      </c>
-      <c r="I124" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="J124">
-        <v>2020</v>
-      </c>
-      <c r="K124" t="s">
-        <v>435</v>
-      </c>
-      <c r="L124" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="M124" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="N124" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="O124" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P124" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q124" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R124" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S124" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U124" s="30" t="s">
-        <v>901</v>
-      </c>
-      <c r="V124" s="3" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="125" spans="1:22" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B125" t="s">
-        <v>440</v>
-      </c>
-      <c r="C125" t="s">
-        <v>38</v>
+        <v>434</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>805</v>
       </c>
       <c r="D125" t="s">
         <v>38</v>
       </c>
-      <c r="E125" s="8" t="s">
-        <v>442</v>
+      <c r="E125" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="F125" t="s">
         <v>38</v>
       </c>
       <c r="G125" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H125" t="s">
-        <v>1</v>
-      </c>
-      <c r="I125" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J125" t="s">
-        <v>38</v>
+        <v>6</v>
+      </c>
+      <c r="I125" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="J125">
+        <v>2020</v>
       </c>
       <c r="K125" t="s">
-        <v>38</v>
+        <v>435</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="O125" s="32"/>
+        <v>735</v>
+      </c>
+      <c r="O125" s="32" t="s">
+        <v>29</v>
+      </c>
       <c r="P125" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="Q125" s="40"/>
-      <c r="R125" s="32"/>
+      <c r="Q125" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R125" s="32" t="s">
+        <v>29</v>
+      </c>
       <c r="S125" s="33" t="s">
         <v>30</v>
       </c>
       <c r="T125" s="30"/>
       <c r="U125" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V125" s="3" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="126" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B126" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C126" t="s">
         <v>38</v>
@@ -12218,159 +12238,152 @@
       <c r="D126" t="s">
         <v>38</v>
       </c>
-      <c r="E126" s="1" t="s">
-        <v>446</v>
+      <c r="E126" s="8" t="s">
+        <v>442</v>
       </c>
       <c r="F126" t="s">
         <v>38</v>
       </c>
       <c r="G126" t="s">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="H126" t="s">
+        <v>1</v>
       </c>
       <c r="I126" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J126">
-        <v>2017</v>
+      <c r="J126" t="s">
+        <v>38</v>
       </c>
       <c r="K126" t="s">
         <v>38</v>
       </c>
       <c r="L126" s="3" t="s">
-        <v>874</v>
+        <v>441</v>
       </c>
       <c r="M126" s="3" t="s">
-        <v>38</v>
+        <v>443</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O126" s="32" t="s">
-        <v>30</v>
+        <v>739</v>
       </c>
       <c r="P126" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q126" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="R126" s="32" t="s">
-        <v>30</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q126" s="40"/>
       <c r="S126" s="33" t="s">
         <v>30</v>
       </c>
       <c r="U126" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V126" s="3" t="s">
-        <v>1012</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="127" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B127" t="s">
-        <v>448</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>450</v>
+        <v>445</v>
+      </c>
+      <c r="C127" t="s">
+        <v>38</v>
       </c>
       <c r="D127" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>446</v>
       </c>
       <c r="F127" t="s">
         <v>38</v>
       </c>
       <c r="G127" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I127" s="10" t="s">
-        <v>292</v>
+        <v>38</v>
       </c>
       <c r="J127">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="K127" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="L127" s="3" t="s">
-        <v>449</v>
+        <v>873</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>323</v>
+        <v>38</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>737</v>
+        <v>38</v>
       </c>
       <c r="O127" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P127" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q127" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R127" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S127" s="33" t="s">
         <v>30</v>
       </c>
       <c r="U127" s="30" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="V127" s="3" t="s">
-        <v>922</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="128" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B128" t="s">
-        <v>93</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="D128" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>453</v>
+        <v>26</v>
       </c>
       <c r="F128" t="s">
         <v>38</v>
       </c>
       <c r="G128" t="s">
-        <v>4</v>
-      </c>
-      <c r="H128" t="s">
-        <v>0</v>
-      </c>
-      <c r="I128" s="10">
-        <v>1.1000000000000001</v>
+        <v>10</v>
+      </c>
+      <c r="H128"/>
+      <c r="I128" s="10" t="s">
+        <v>292</v>
       </c>
       <c r="J128">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="K128" t="s">
-        <v>138</v>
+        <v>23</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>891</v>
+        <v>449</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>38</v>
+        <v>323</v>
       </c>
       <c r="N128" s="3" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="O128" s="32" t="s">
         <v>29</v>
@@ -12385,186 +12398,189 @@
         <v>29</v>
       </c>
       <c r="S128" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T128" s="30"/>
       <c r="U128" s="30" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="V128" s="3" t="s">
-        <v>1034</v>
+        <v>921</v>
       </c>
     </row>
     <row r="129" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B129" t="s">
-        <v>455</v>
-      </c>
-      <c r="C129" t="s">
-        <v>38</v>
+        <v>93</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="D129" t="s">
         <v>38</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F129" t="s">
         <v>38</v>
       </c>
       <c r="G129" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H129" t="s">
-        <v>11</v>
-      </c>
-      <c r="I129" s="10" t="s">
-        <v>38</v>
+        <v>0</v>
+      </c>
+      <c r="I129" s="10">
+        <v>1.1000000000000001</v>
       </c>
       <c r="J129">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="K129" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="N129" s="12" t="s">
-        <v>38</v>
+        <v>38</v>
+      </c>
+      <c r="N129" s="3" t="s">
+        <v>740</v>
       </c>
       <c r="O129" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P129" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q129" s="32" t="s">
         <v>29</v>
       </c>
       <c r="R129" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S129" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T129" s="30"/>
       <c r="U129" s="30" t="s">
-        <v>904</v>
+        <v>929</v>
       </c>
       <c r="V129" s="3" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="130" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>547</v>
+        <v>454</v>
       </c>
       <c r="B130" t="s">
-        <v>544</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>545</v>
+        <v>455</v>
+      </c>
+      <c r="C130" t="s">
+        <v>38</v>
       </c>
       <c r="D130" t="s">
-        <v>550</v>
+        <v>38</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>546</v>
+        <v>456</v>
       </c>
       <c r="F130" t="s">
-        <v>548</v>
+        <v>38</v>
       </c>
       <c r="G130" t="s">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H130" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I130" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J130" t="s">
-        <v>38</v>
+      <c r="J130">
+        <v>2024</v>
       </c>
       <c r="K130" t="s">
         <v>38</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>853</v>
+        <v>891</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="N130" s="3" t="s">
-        <v>549</v>
+        <v>457</v>
+      </c>
+      <c r="N130" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="O130" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P130" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q130" s="32" t="s">
         <v>29</v>
       </c>
       <c r="R130" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S130" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U130" s="30" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="V130" s="3" t="s">
-        <v>978</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="131" spans="1:22" ht="300" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="B131" t="s">
+        <v>544</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D131" t="s">
+        <v>550</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F131" t="s">
+        <v>548</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
+      </c>
+      <c r="H131" t="s">
+        <v>9</v>
+      </c>
+      <c r="I131" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J131" t="s">
+        <v>38</v>
+      </c>
+      <c r="K131" t="s">
+        <v>38</v>
+      </c>
+      <c r="L131" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="M131" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="D131" t="s">
-        <v>38</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="F131" t="s">
-        <v>38</v>
-      </c>
-      <c r="G131" t="s">
-        <v>10</v>
-      </c>
-      <c r="I131" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J131">
-        <v>2017</v>
-      </c>
-      <c r="K131" t="s">
-        <v>38</v>
-      </c>
-      <c r="L131" s="3" t="s">
-        <v>878</v>
-      </c>
-      <c r="M131" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="N131" s="3" t="s">
-        <v>460</v>
+        <v>549</v>
       </c>
       <c r="O131" s="32" t="s">
         <v>29</v>
@@ -12582,27 +12598,27 @@
         <v>29</v>
       </c>
       <c r="U131" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V131" s="3" t="s">
-        <v>1017</v>
+        <v>977</v>
       </c>
     </row>
     <row r="132" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B132" t="s">
-        <v>428</v>
+        <v>245</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D132" t="s">
         <v>38</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F132" t="s">
         <v>38</v>
@@ -12620,13 +12636,13 @@
         <v>38</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>462</v>
+        <v>877</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>245</v>
+        <v>38</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="O132" s="32" t="s">
         <v>29</v>
@@ -12644,54 +12660,51 @@
         <v>29</v>
       </c>
       <c r="U132" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V132" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="133" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B133" t="s">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>803</v>
+        <v>463</v>
       </c>
       <c r="D133" t="s">
         <v>38</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F133" t="s">
         <v>38</v>
       </c>
       <c r="G133" t="s">
-        <v>0</v>
-      </c>
-      <c r="H133" t="s">
-        <v>468</v>
+        <v>10</v>
       </c>
       <c r="I133" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J133">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="K133" t="s">
         <v>38</v>
       </c>
       <c r="L133" s="3" t="s">
-        <v>877</v>
+        <v>462</v>
       </c>
       <c r="M133" s="3" t="s">
-        <v>470</v>
+        <v>245</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>38</v>
+        <v>465</v>
       </c>
       <c r="O133" s="32" t="s">
         <v>29</v>
@@ -12703,13 +12716,13 @@
         <v>29</v>
       </c>
       <c r="R133" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S133" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U133" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V133" s="3" t="s">
         <v>1016</v>
@@ -12717,42 +12730,46 @@
     </row>
     <row r="134" spans="1:22" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>219</v>
+        <v>466</v>
       </c>
       <c r="B134" t="s">
-        <v>668</v>
+        <v>467</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>669</v>
+        <v>802</v>
       </c>
       <c r="D134" t="s">
         <v>38</v>
       </c>
-      <c r="E134"/>
+      <c r="E134" s="1" t="s">
+        <v>469</v>
+      </c>
       <c r="F134" t="s">
-        <v>220</v>
+        <v>38</v>
       </c>
       <c r="G134" t="s">
         <v>0</v>
       </c>
       <c r="H134" t="s">
-        <v>1</v>
-      </c>
-      <c r="I134" s="10"/>
+        <v>468</v>
+      </c>
+      <c r="I134" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="J134">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="K134" t="s">
-        <v>133</v>
+        <v>38</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>221</v>
+        <v>876</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>222</v>
+        <v>470</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>223</v>
+        <v>38</v>
       </c>
       <c r="O134" s="32" t="s">
         <v>29</v>
@@ -12764,58 +12781,55 @@
         <v>29</v>
       </c>
       <c r="R134" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S134" s="33" t="s">
         <v>30</v>
       </c>
       <c r="T134" s="30"/>
       <c r="U134" s="30" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="V134" s="3" t="s">
-        <v>956</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="135" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>471</v>
-      </c>
-      <c r="B135" s="17" t="s">
-        <v>472</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>841</v>
+        <v>219</v>
+      </c>
+      <c r="B135" t="s">
+        <v>668</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>669</v>
       </c>
       <c r="D135" t="s">
         <v>38</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>473</v>
-      </c>
       <c r="F135" t="s">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="G135" t="s">
-        <v>3</v>
-      </c>
-      <c r="I135" s="10">
-        <v>1.01</v>
+        <v>0</v>
+      </c>
+      <c r="H135" t="s">
+        <v>1</v>
       </c>
       <c r="J135">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="K135" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>896</v>
+        <v>221</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="N135" s="3" t="s">
-        <v>474</v>
+        <v>223</v>
       </c>
       <c r="O135" s="32" t="s">
         <v>29</v>
@@ -12824,7 +12838,7 @@
         <v>29</v>
       </c>
       <c r="Q135" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R135" s="32" t="s">
         <v>29</v>
@@ -12833,36 +12847,36 @@
         <v>30</v>
       </c>
       <c r="U135" s="30" t="s">
-        <v>919</v>
+        <v>900</v>
       </c>
       <c r="V135" s="3" t="s">
-        <v>1041</v>
+        <v>955</v>
       </c>
     </row>
     <row r="136" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C136" s="19" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="D136" t="s">
         <v>38</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F136" t="s">
         <v>38</v>
       </c>
       <c r="G136" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I136" s="10">
-        <v>1.1200000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="J136">
         <v>2013</v>
@@ -12871,16 +12885,16 @@
         <v>38</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>1044</v>
+        <v>895</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>842</v>
+        <v>38</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>850</v>
+        <v>474</v>
       </c>
       <c r="O136" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P136" s="32" t="s">
         <v>29</v>
@@ -12889,24 +12903,24 @@
         <v>30</v>
       </c>
       <c r="R136" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S136" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S136" s="33" t="s">
         <v>30</v>
       </c>
       <c r="U136" s="30" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
       <c r="V136" s="3" t="s">
-        <v>902</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="137" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C137" s="19" t="s">
         <v>843</v>
@@ -12915,16 +12929,16 @@
         <v>38</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F137" t="s">
         <v>38</v>
       </c>
       <c r="G137" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I137" s="10">
-        <v>1.03</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J137">
         <v>2013</v>
@@ -12933,16 +12947,16 @@
         <v>38</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>854</v>
+        <v>1043</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>38</v>
+        <v>841</v>
       </c>
       <c r="N137" s="3" t="s">
         <v>849</v>
       </c>
       <c r="O137" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P137" s="32" t="s">
         <v>29</v>
@@ -12951,36 +12965,33 @@
         <v>30</v>
       </c>
       <c r="R137" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S137" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="T137" s="30">
-        <v>15</v>
+        <v>30</v>
+      </c>
+      <c r="S137" s="32" t="s">
+        <v>30</v>
       </c>
       <c r="U137" s="30" t="s">
-        <v>930</v>
+        <v>900</v>
       </c>
       <c r="V137" s="3" t="s">
-        <v>979</v>
+        <v>901</v>
       </c>
     </row>
     <row r="138" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C138" s="19" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D138" t="s">
         <v>38</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F138" t="s">
         <v>38</v>
@@ -12989,7 +13000,7 @@
         <v>4</v>
       </c>
       <c r="I138" s="10">
-        <v>1.1399999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="J138">
         <v>2013</v>
@@ -12998,16 +13009,16 @@
         <v>38</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>893</v>
+        <v>853</v>
       </c>
       <c r="M138" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="O138" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P138" s="32" t="s">
         <v>29</v>
@@ -13019,40 +13030,43 @@
         <v>29</v>
       </c>
       <c r="S138" s="33" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="T138" s="30">
+        <v>15</v>
       </c>
       <c r="U138" s="30" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="V138" s="3" t="s">
-        <v>1038</v>
+        <v>978</v>
       </c>
     </row>
     <row r="139" spans="1:22" s="16" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>570</v>
+        <v>481</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>842</v>
+        <v>482</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="D139" t="s">
         <v>38</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F139" t="s">
         <v>38</v>
       </c>
       <c r="G139" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H139"/>
       <c r="I139" s="10">
-        <v>1.1200000000000001</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="J139">
         <v>2013</v>
@@ -13061,13 +13075,13 @@
         <v>38</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>1058</v>
+        <v>892</v>
       </c>
       <c r="M139" s="3" t="s">
         <v>38</v>
       </c>
       <c r="N139" s="3" t="s">
-        <v>38</v>
+        <v>846</v>
       </c>
       <c r="O139" s="32" t="s">
         <v>30</v>
@@ -13079,44 +13093,44 @@
         <v>30</v>
       </c>
       <c r="R139" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S139" s="33" t="s">
         <v>29</v>
       </c>
       <c r="T139" s="30"/>
       <c r="U139" s="30" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
       <c r="V139" s="3" t="s">
-        <v>935</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="140" spans="1:22" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>484</v>
+        <v>570</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>485</v>
+        <v>841</v>
       </c>
       <c r="C140" s="19" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D140" t="s">
         <v>38</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="F140" t="s">
         <v>38</v>
       </c>
       <c r="G140" t="s">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H140"/>
       <c r="I140" s="10">
-        <v>1.03</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="J140">
         <v>2013</v>
@@ -13125,13 +13139,13 @@
         <v>38</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>897</v>
+        <v>1057</v>
       </c>
       <c r="M140" s="3" t="s">
-        <v>745</v>
+        <v>38</v>
       </c>
       <c r="N140" s="3" t="s">
-        <v>474</v>
+        <v>38</v>
       </c>
       <c r="O140" s="32" t="s">
         <v>30</v>
@@ -13146,381 +13160,438 @@
         <v>30</v>
       </c>
       <c r="S140" s="33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T140" s="30"/>
       <c r="U140" s="30" t="s">
-        <v>923</v>
+        <v>900</v>
       </c>
       <c r="V140" s="3" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="141" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="141" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>484</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="C141" s="19" t="s">
+        <v>845</v>
+      </c>
+      <c r="D141" t="s">
+        <v>38</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="F141" t="s">
+        <v>38</v>
+      </c>
+      <c r="G141" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" s="10">
+        <v>1.03</v>
+      </c>
+      <c r="J141">
+        <v>2013</v>
+      </c>
+      <c r="K141" t="s">
+        <v>38</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="M141" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="N141" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="O141" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="P141" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q141" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="R141" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S141" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U141" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="V141" s="3" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="142" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
         <v>487</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B142" t="s">
         <v>488</v>
       </c>
-      <c r="C141" t="s">
-        <v>38</v>
-      </c>
-      <c r="D141" t="s">
-        <v>38</v>
-      </c>
-      <c r="E141" s="1" t="s">
+      <c r="C142" t="s">
+        <v>38</v>
+      </c>
+      <c r="D142" t="s">
+        <v>38</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="F141" t="s">
-        <v>38</v>
-      </c>
-      <c r="G141" t="s">
+      <c r="F142" t="s">
+        <v>38</v>
+      </c>
+      <c r="G142" t="s">
         <v>12</v>
       </c>
-      <c r="I141" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J141">
+      <c r="I142" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J142">
         <v>2009</v>
       </c>
-      <c r="K141" t="s">
-        <v>38</v>
-      </c>
-      <c r="L141" s="3" t="s">
-        <v>894</v>
-      </c>
-      <c r="M141" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N141" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O141" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P141" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q141" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R141" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S141" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U141" s="30" t="s">
-        <v>919</v>
-      </c>
-      <c r="V141" s="3" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="142" spans="1:22" ht="120" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
+      <c r="K142" t="s">
+        <v>38</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="M142" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N142" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O142" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P142" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q142" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R142" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S142" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U142" s="30" t="s">
+        <v>918</v>
+      </c>
+      <c r="V142" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="143" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
         <v>527</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B143" t="s">
         <v>528</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="D142" t="s">
-        <v>38</v>
-      </c>
-      <c r="E142" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D143" t="s">
+        <v>38</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="F142" t="s">
-        <v>38</v>
-      </c>
-      <c r="G142" t="s">
+      <c r="F143" t="s">
+        <v>38</v>
+      </c>
+      <c r="G143" t="s">
         <v>17</v>
       </c>
-      <c r="I142" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J142">
+      <c r="I143" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J143">
         <v>2024</v>
       </c>
-      <c r="K142" t="s">
+      <c r="K143" t="s">
         <v>133</v>
       </c>
-      <c r="L142" s="3" t="s">
+      <c r="L143" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="M142" s="3" t="s">
+      <c r="M143" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="N142" s="3" t="s">
+      <c r="N143" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="O142" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P142" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q142" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R142" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S142" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="U142" s="30" t="s">
-        <v>899</v>
-      </c>
-      <c r="V142" s="3" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="143" spans="1:22" ht="120" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>490</v>
-      </c>
-      <c r="B143" t="s">
-        <v>491</v>
-      </c>
-      <c r="C143" t="s">
-        <v>38</v>
-      </c>
-      <c r="D143" t="s">
-        <v>38</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="F143" t="s">
-        <v>38</v>
-      </c>
-      <c r="G143" t="s">
-        <v>12</v>
-      </c>
-      <c r="I143" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J143">
-        <v>2009</v>
-      </c>
-      <c r="K143" t="s">
-        <v>38</v>
-      </c>
-      <c r="L143" s="3" t="s">
-        <v>895</v>
-      </c>
-      <c r="M143" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N143" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="O143" s="32" t="s">
         <v>29</v>
       </c>
       <c r="P143" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q143" s="32" t="s">
         <v>29</v>
       </c>
       <c r="R143" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S143" s="33"/>
+        <v>29</v>
+      </c>
+      <c r="S143" s="33" t="s">
+        <v>30</v>
+      </c>
       <c r="U143" s="30" t="s">
-        <v>919</v>
+        <v>898</v>
       </c>
       <c r="V143" s="3" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="144" spans="1:22" s="16" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B144" t="s">
-        <v>494</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
+      </c>
+      <c r="C144" t="s">
+        <v>38</v>
       </c>
       <c r="D144" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>26</v>
+        <v>492</v>
       </c>
       <c r="F144" t="s">
         <v>38</v>
       </c>
       <c r="G144" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H144"/>
       <c r="I144" s="10" t="s">
         <v>38</v>
       </c>
       <c r="J144">
-        <v>2020</v>
+        <v>2009</v>
       </c>
       <c r="K144" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>1054</v>
+        <v>894</v>
       </c>
       <c r="M144" s="3" t="s">
-        <v>496</v>
+        <v>38</v>
       </c>
       <c r="N144" s="3" t="s">
-        <v>738</v>
+        <v>38</v>
       </c>
       <c r="O144" s="32" t="s">
         <v>29</v>
       </c>
       <c r="P144" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q144" s="32" t="s">
         <v>29</v>
       </c>
       <c r="R144" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S144" s="33" t="s">
-        <v>30</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="S144" s="33"/>
       <c r="T144" s="30"/>
       <c r="U144" s="30" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="V144" s="3" t="s">
-        <v>924</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="145" spans="1:22" ht="315" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>493</v>
+      </c>
+      <c r="B145" t="s">
+        <v>494</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D145" t="s">
+        <v>32</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F145" t="s">
+        <v>38</v>
+      </c>
+      <c r="G145" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J145">
+        <v>2020</v>
+      </c>
+      <c r="K145" t="s">
+        <v>23</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M145" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="N145" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="O145" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="P145" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q145" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R145" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S145" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="U145" s="30" t="s">
+        <v>922</v>
+      </c>
+      <c r="V145" s="3" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="146" spans="1:22" ht="315" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
         <v>741</v>
       </c>
-      <c r="B145" t="s">
-        <v>745</v>
-      </c>
-      <c r="C145" s="27" t="s">
-        <v>805</v>
-      </c>
-      <c r="D145" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E145" s="1" t="s">
+      <c r="B146" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C146" s="27" t="s">
+        <v>804</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="F145" t="s">
-        <v>38</v>
-      </c>
-      <c r="G145" t="s">
+      <c r="F146" t="s">
+        <v>38</v>
+      </c>
+      <c r="G146" t="s">
         <v>7</v>
       </c>
-      <c r="H145" s="1"/>
-      <c r="I145" s="10">
+      <c r="I146" s="10">
         <v>1.21</v>
       </c>
-      <c r="J145">
+      <c r="J146">
         <v>2006</v>
       </c>
-      <c r="L145" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="M145" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N145" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O145" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="P145" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q145" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R145" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S145" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="T145" s="30">
-        <v>30</v>
-      </c>
-      <c r="U145" s="32" t="s">
-        <v>923</v>
-      </c>
-      <c r="V145" s="34" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="146" spans="1:22" ht="105" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B146" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F146" t="s">
-        <v>38</v>
-      </c>
-      <c r="H146" s="1"/>
-      <c r="I146" s="10">
-        <v>1</v>
-      </c>
-      <c r="J146">
-        <v>2025</v>
-      </c>
-      <c r="K146" t="s">
-        <v>1089</v>
-      </c>
       <c r="L146" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="M146" t="s">
+        <v>897</v>
+      </c>
+      <c r="M146" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N146" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="O146" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="P146" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q146" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="R146" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S146" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="T146" s="30">
+        <v>30</v>
+      </c>
+      <c r="U146" s="32" t="s">
+        <v>922</v>
+      </c>
+      <c r="V146" s="34" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="147" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
         <v>1091</v>
       </c>
-      <c r="N146" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O146" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="P146" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q146" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="R146" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S146" s="38"/>
-      <c r="T146" s="32"/>
-      <c r="U146" s="32"/>
-      <c r="V146" s="34"/>
+      <c r="B147" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C147" s="27" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E147" s="29" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F147" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G147" t="s">
+        <v>4</v>
+      </c>
+      <c r="H147" t="s">
+        <v>14</v>
+      </c>
+      <c r="I147" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J147">
+        <v>2026</v>
+      </c>
+      <c r="K147" t="s">
+        <v>23</v>
+      </c>
+      <c r="L147" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="M147" t="s">
+        <v>1096</v>
+      </c>
+      <c r="N147" s="15" t="s">
+        <v>1097</v>
+      </c>
+      <c r="O147" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S147" s="33"/>
+      <c r="T147" s="32"/>
+      <c r="U147" s="32"/>
+      <c r="V147" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -13528,17 +13599,17 @@
     <hyperlink ref="C60" r:id="rId1" xr:uid="{09689414-3477-4574-B4C1-145654B8F872}"/>
     <hyperlink ref="C9" r:id="rId2" xr:uid="{093A01EE-86EE-45C4-8EB3-9E2035175000}"/>
     <hyperlink ref="C20" r:id="rId3" xr:uid="{647907ED-3EF1-4900-B2E2-99B4EA674B9D}"/>
-    <hyperlink ref="C98" r:id="rId4" xr:uid="{FAE6907E-C81E-4A5D-817E-230B91B1B725}"/>
+    <hyperlink ref="C99" r:id="rId4" xr:uid="{FAE6907E-C81E-4A5D-817E-230B91B1B725}"/>
     <hyperlink ref="C49" r:id="rId5" xr:uid="{C753E4AB-C43C-4DA7-BCBB-4C6B42AE449C}"/>
-    <hyperlink ref="C133" r:id="rId6" xr:uid="{371EC661-68AD-4E55-A1EB-3AD1B3210212}"/>
-    <hyperlink ref="C132" r:id="rId7" xr:uid="{87EC244C-7916-48F7-AB46-F1434A4E3208}"/>
+    <hyperlink ref="C134" r:id="rId6" xr:uid="{371EC661-68AD-4E55-A1EB-3AD1B3210212}"/>
+    <hyperlink ref="C133" r:id="rId7" xr:uid="{87EC244C-7916-48F7-AB46-F1434A4E3208}"/>
     <hyperlink ref="C53" r:id="rId8" xr:uid="{C7C324AF-CD50-4932-996A-89F85253BFD5}"/>
     <hyperlink ref="C4" r:id="rId9" xr:uid="{EDB880A2-AA3E-4F26-A446-E9157F173772}"/>
     <hyperlink ref="C35" r:id="rId10" xr:uid="{9A17C16E-C332-458A-ADE6-19BE3A083F23}"/>
     <hyperlink ref="C42" r:id="rId11" xr:uid="{B6233385-F901-40C6-AEFB-2742E1A95C52}"/>
     <hyperlink ref="C6" r:id="rId12" xr:uid="{17CBE166-8555-4ADF-8563-DD807A994D87}"/>
     <hyperlink ref="C73" r:id="rId13" xr:uid="{5A5F426A-1EDA-41D8-B9CB-7227502B01CB}"/>
-    <hyperlink ref="C124" r:id="rId14" xr:uid="{82446CC2-3C94-440E-AAD6-8D54906361E8}"/>
+    <hyperlink ref="C125" r:id="rId14" xr:uid="{82446CC2-3C94-440E-AAD6-8D54906361E8}"/>
     <hyperlink ref="C16" r:id="rId15" xr:uid="{7A9FCCD8-8795-4FEF-A34B-74181A73AEB9}"/>
     <hyperlink ref="C31" r:id="rId16" xr:uid="{8EACE7F8-9420-4163-ABD1-0A6C80C10BC0}"/>
     <hyperlink ref="C37" r:id="rId17" xr:uid="{4E230D6B-A2E5-482B-847D-728150A3AAC3}"/>
@@ -13553,11 +13624,11 @@
     <hyperlink ref="C17" r:id="rId26" xr:uid="{D53591D3-EF0A-4301-B038-F4C64E0F14B1}"/>
     <hyperlink ref="C57" r:id="rId27" xr:uid="{6774AFFC-3F72-4FC8-83D4-C6E9745490F7}"/>
     <hyperlink ref="C28" r:id="rId28" xr:uid="{D01E6549-8C0C-4A44-AF08-ED09A47D4252}"/>
-    <hyperlink ref="C109" r:id="rId29" xr:uid="{DE66E60B-BA52-4BF5-91BF-04E031C85DF4}"/>
-    <hyperlink ref="C144" r:id="rId30" xr:uid="{6B7C0C1E-80A1-4C90-B400-939A08EB9E26}"/>
-    <hyperlink ref="C131" r:id="rId31" xr:uid="{39C94BCA-35A0-4C33-8523-A608427AF1AC}"/>
-    <hyperlink ref="C128" r:id="rId32" xr:uid="{0078D0DD-F4F6-49B0-885D-B066223BAE60}"/>
-    <hyperlink ref="C127" r:id="rId33" xr:uid="{C5712289-6DD8-4698-B94D-78A55B1677AB}"/>
+    <hyperlink ref="C110" r:id="rId29" xr:uid="{DE66E60B-BA52-4BF5-91BF-04E031C85DF4}"/>
+    <hyperlink ref="C145" r:id="rId30" xr:uid="{6B7C0C1E-80A1-4C90-B400-939A08EB9E26}"/>
+    <hyperlink ref="C132" r:id="rId31" xr:uid="{39C94BCA-35A0-4C33-8523-A608427AF1AC}"/>
+    <hyperlink ref="C129" r:id="rId32" xr:uid="{0078D0DD-F4F6-49B0-885D-B066223BAE60}"/>
+    <hyperlink ref="C128" r:id="rId33" xr:uid="{C5712289-6DD8-4698-B94D-78A55B1677AB}"/>
     <hyperlink ref="C45" r:id="rId34" xr:uid="{009176AE-ADE1-49A3-B8B5-187A70213738}"/>
     <hyperlink ref="C40" r:id="rId35" xr:uid="{53B27E08-A450-4488-BA16-0EBEE4AF4455}"/>
     <hyperlink ref="C44" r:id="rId36" xr:uid="{A5096D46-1AA5-4208-813B-8023926F7367}"/>
@@ -13582,33 +13653,33 @@
     <hyperlink ref="C84" r:id="rId55" xr:uid="{42BCD2DF-E790-4589-A30F-037C5CC98618}"/>
     <hyperlink ref="C85" r:id="rId56" xr:uid="{D04172B2-FA86-479A-B554-457A76AC12EB}"/>
     <hyperlink ref="C86" r:id="rId57" xr:uid="{4D285DE5-B50D-4CAB-A92F-4534B3369428}"/>
-    <hyperlink ref="C90" r:id="rId58" xr:uid="{4788DE4E-DD21-4F17-A0F5-F0127C036B93}"/>
-    <hyperlink ref="C92" r:id="rId59" xr:uid="{F8DE4A00-90C4-4883-8925-84D02A72603D}"/>
-    <hyperlink ref="C93" r:id="rId60" xr:uid="{537D1EAA-FB2D-4A1A-A7EF-263F86E9B731}"/>
-    <hyperlink ref="C97" r:id="rId61" xr:uid="{ACD371A2-0E1B-4667-A917-FB870D976F44}"/>
-    <hyperlink ref="C100" r:id="rId62" xr:uid="{280984BC-9AF6-43D6-B7C6-0B942360A963}"/>
-    <hyperlink ref="C101" r:id="rId63" xr:uid="{076877CE-8ABA-4EB5-BBFC-50357A612F35}"/>
-    <hyperlink ref="C106" r:id="rId64" xr:uid="{5628464F-D8DE-4F76-9B77-04A7AFF90F62}"/>
-    <hyperlink ref="C107" r:id="rId65" xr:uid="{03CB87A5-498E-4649-8556-4CBF15C6B9FD}"/>
-    <hyperlink ref="C113" r:id="rId66" xr:uid="{CF37847B-1569-47B2-9A5A-E969CE56BF8B}"/>
-    <hyperlink ref="C114" r:id="rId67" xr:uid="{434996DF-4908-4245-B541-2571CDFEF5CA}"/>
-    <hyperlink ref="C116" r:id="rId68" xr:uid="{7F8DD870-012B-4FA5-B272-8F9C10BE0F67}"/>
-    <hyperlink ref="C117" r:id="rId69" xr:uid="{811E91E6-D722-4048-979A-0A1B3944C89F}"/>
-    <hyperlink ref="C118" r:id="rId70" xr:uid="{D712678C-0ED2-435A-B50F-8727B237AA85}"/>
-    <hyperlink ref="C120" r:id="rId71" xr:uid="{23570306-858B-4CEB-A34A-C76767C43F2C}"/>
-    <hyperlink ref="C121" r:id="rId72" xr:uid="{8A4373FA-901A-4FE5-A250-36C1CBE1C863}"/>
-    <hyperlink ref="C122" r:id="rId73" xr:uid="{04465534-930B-4B39-A965-677749107D82}"/>
-    <hyperlink ref="C108" r:id="rId74" xr:uid="{54C7F5BF-5DB5-4C4D-AED8-A9EF695BADE3}"/>
-    <hyperlink ref="C110" r:id="rId75" xr:uid="{722E83D6-EBD5-4CA8-87EC-CF744B148F5E}"/>
+    <hyperlink ref="C91" r:id="rId58" xr:uid="{4788DE4E-DD21-4F17-A0F5-F0127C036B93}"/>
+    <hyperlink ref="C93" r:id="rId59" xr:uid="{F8DE4A00-90C4-4883-8925-84D02A72603D}"/>
+    <hyperlink ref="C94" r:id="rId60" xr:uid="{537D1EAA-FB2D-4A1A-A7EF-263F86E9B731}"/>
+    <hyperlink ref="C98" r:id="rId61" xr:uid="{ACD371A2-0E1B-4667-A917-FB870D976F44}"/>
+    <hyperlink ref="C101" r:id="rId62" xr:uid="{280984BC-9AF6-43D6-B7C6-0B942360A963}"/>
+    <hyperlink ref="C102" r:id="rId63" xr:uid="{076877CE-8ABA-4EB5-BBFC-50357A612F35}"/>
+    <hyperlink ref="C107" r:id="rId64" xr:uid="{5628464F-D8DE-4F76-9B77-04A7AFF90F62}"/>
+    <hyperlink ref="C108" r:id="rId65" xr:uid="{03CB87A5-498E-4649-8556-4CBF15C6B9FD}"/>
+    <hyperlink ref="C114" r:id="rId66" xr:uid="{CF37847B-1569-47B2-9A5A-E969CE56BF8B}"/>
+    <hyperlink ref="C115" r:id="rId67" xr:uid="{434996DF-4908-4245-B541-2571CDFEF5CA}"/>
+    <hyperlink ref="C117" r:id="rId68" xr:uid="{7F8DD870-012B-4FA5-B272-8F9C10BE0F67}"/>
+    <hyperlink ref="C118" r:id="rId69" xr:uid="{811E91E6-D722-4048-979A-0A1B3944C89F}"/>
+    <hyperlink ref="C119" r:id="rId70" xr:uid="{D712678C-0ED2-435A-B50F-8727B237AA85}"/>
+    <hyperlink ref="C121" r:id="rId71" xr:uid="{23570306-858B-4CEB-A34A-C76767C43F2C}"/>
+    <hyperlink ref="C122" r:id="rId72" xr:uid="{8A4373FA-901A-4FE5-A250-36C1CBE1C863}"/>
+    <hyperlink ref="C123" r:id="rId73" xr:uid="{04465534-930B-4B39-A965-677749107D82}"/>
+    <hyperlink ref="C109" r:id="rId74" xr:uid="{54C7F5BF-5DB5-4C4D-AED8-A9EF695BADE3}"/>
+    <hyperlink ref="C111" r:id="rId75" xr:uid="{722E83D6-EBD5-4CA8-87EC-CF744B148F5E}"/>
     <hyperlink ref="C7" r:id="rId76" xr:uid="{B9D7E0EF-7657-47FA-A60E-18C7906C6F64}"/>
     <hyperlink ref="C15" r:id="rId77" xr:uid="{DF815018-1A91-4EEA-97A8-53FCF3C51484}"/>
     <hyperlink ref="C21" r:id="rId78" xr:uid="{741DF32C-57B4-4296-8D2B-447F78C164E4}"/>
     <hyperlink ref="C2" r:id="rId79" xr:uid="{9C1B3465-ED4E-4642-BA4D-5C7E5510B7B6}"/>
     <hyperlink ref="C66" r:id="rId80" xr:uid="{AB3EAE1F-65EA-44FC-AB99-16D2D5ED71B3}"/>
-    <hyperlink ref="C142" r:id="rId81" xr:uid="{CF6EACC9-E6EB-45BD-B707-52712C2A62C9}"/>
-    <hyperlink ref="C91" r:id="rId82" xr:uid="{02D0ECDA-FD32-4CF7-8440-EC4C7DCD63E5}"/>
-    <hyperlink ref="C130" r:id="rId83" location=" " xr:uid="{2FFDF6BA-7A97-4D5C-9D4F-2CCB9C0E6DED}"/>
-    <hyperlink ref="C89" r:id="rId84" xr:uid="{7F7A3FF6-CCE9-4E2E-982B-1B4E31731333}"/>
+    <hyperlink ref="C143" r:id="rId81" xr:uid="{CF6EACC9-E6EB-45BD-B707-52712C2A62C9}"/>
+    <hyperlink ref="C92" r:id="rId82" xr:uid="{02D0ECDA-FD32-4CF7-8440-EC4C7DCD63E5}"/>
+    <hyperlink ref="C131" r:id="rId83" location=" " xr:uid="{2FFDF6BA-7A97-4D5C-9D4F-2CCB9C0E6DED}"/>
+    <hyperlink ref="C90" r:id="rId84" xr:uid="{7F7A3FF6-CCE9-4E2E-982B-1B4E31731333}"/>
     <hyperlink ref="C23" r:id="rId85" xr:uid="{17D56B7A-25AE-48DC-87D5-86A3E9DAEC57}"/>
     <hyperlink ref="C81" r:id="rId86" xr:uid="{D8CE449C-151D-4D39-B26F-B961900B9F5D}"/>
     <hyperlink ref="C32" r:id="rId87" xr:uid="{8083253A-88C3-43D3-9D68-6E726A4F9587}"/>
@@ -13616,57 +13687,57 @@
     <hyperlink ref="C30" r:id="rId89" xr:uid="{4972827C-BEE0-44B4-A458-FDE24FCE89C0}"/>
     <hyperlink ref="C29" r:id="rId90" xr:uid="{AA048B82-F6AA-4179-9DA8-92CB88AA34CD}"/>
     <hyperlink ref="C26" r:id="rId91" xr:uid="{1218E00E-EF0C-494E-BECE-099FB05742E5}"/>
-    <hyperlink ref="C104" r:id="rId92" xr:uid="{860357C4-6C5E-4883-814C-F21FA9C924DE}"/>
-    <hyperlink ref="C111" r:id="rId93" xr:uid="{16AB466E-682E-47B8-A4E2-382FD289A028}"/>
-    <hyperlink ref="C112" r:id="rId94" xr:uid="{6DCCCDA1-E5B8-4573-BC96-2C385646B65F}"/>
-    <hyperlink ref="C115" r:id="rId95" xr:uid="{5ED2B850-5619-4803-9E96-99424F17CB82}"/>
-    <hyperlink ref="C119" r:id="rId96" xr:uid="{F046FA23-A48D-4FEC-B2CE-9AD00AACEB66}"/>
-    <hyperlink ref="C123" r:id="rId97" xr:uid="{1F850D9E-5286-41BA-90F6-0FD05DFBBBE5}"/>
+    <hyperlink ref="C105" r:id="rId92" xr:uid="{860357C4-6C5E-4883-814C-F21FA9C924DE}"/>
+    <hyperlink ref="C112" r:id="rId93" xr:uid="{16AB466E-682E-47B8-A4E2-382FD289A028}"/>
+    <hyperlink ref="C113" r:id="rId94" xr:uid="{6DCCCDA1-E5B8-4573-BC96-2C385646B65F}"/>
+    <hyperlink ref="C116" r:id="rId95" xr:uid="{5ED2B850-5619-4803-9E96-99424F17CB82}"/>
+    <hyperlink ref="C120" r:id="rId96" xr:uid="{F046FA23-A48D-4FEC-B2CE-9AD00AACEB66}"/>
+    <hyperlink ref="C124" r:id="rId97" xr:uid="{1F850D9E-5286-41BA-90F6-0FD05DFBBBE5}"/>
     <hyperlink ref="E4" r:id="rId98" xr:uid="{811C4818-C847-4731-BB38-2D52F1834045}"/>
     <hyperlink ref="E10" r:id="rId99" xr:uid="{94100DD3-02BF-4E61-A172-C4A9D09569F8}"/>
     <hyperlink ref="E14" r:id="rId100" location="s0035" xr:uid="{13AE09A2-4522-46D1-AC75-5B95A8D15C9C}"/>
     <hyperlink ref="E47" r:id="rId101" xr:uid="{5C414BC3-1364-419D-9DDD-1A6F60C0D845}"/>
     <hyperlink ref="E60" r:id="rId102" xr:uid="{C5A0DFB4-1FB7-49B8-8FD3-9AC01312958D}"/>
-    <hyperlink ref="E95" r:id="rId103" xr:uid="{51CBF759-50E7-428F-81D5-CB1BF0D6F9DE}"/>
-    <hyperlink ref="E126" r:id="rId104" xr:uid="{DD230CEE-1804-40FB-BD78-0C67303DB967}"/>
-    <hyperlink ref="E133" r:id="rId105" location="f0020" xr:uid="{3778DDB7-E612-4F6A-A3B0-B453CF8B64A9}"/>
-    <hyperlink ref="E88" r:id="rId106" xr:uid="{88E00939-FB4B-46C7-8C26-9BF914C2DEFC}"/>
-    <hyperlink ref="E109" r:id="rId107" xr:uid="{1BF75D9D-D348-4E2D-9C84-905D4A8F3B25}"/>
+    <hyperlink ref="E96" r:id="rId103" xr:uid="{51CBF759-50E7-428F-81D5-CB1BF0D6F9DE}"/>
+    <hyperlink ref="E127" r:id="rId104" xr:uid="{DD230CEE-1804-40FB-BD78-0C67303DB967}"/>
+    <hyperlink ref="E134" r:id="rId105" location="f0020" xr:uid="{3778DDB7-E612-4F6A-A3B0-B453CF8B64A9}"/>
+    <hyperlink ref="E89" r:id="rId106" xr:uid="{88E00939-FB4B-46C7-8C26-9BF914C2DEFC}"/>
+    <hyperlink ref="E110" r:id="rId107" xr:uid="{1BF75D9D-D348-4E2D-9C84-905D4A8F3B25}"/>
     <hyperlink ref="E42" r:id="rId108" xr:uid="{731847B6-AFA8-4FD0-B2B9-DA4073CF6576}"/>
-    <hyperlink ref="E140" r:id="rId109" xr:uid="{A734FA6A-1E5E-4197-893E-26AEB8863486}"/>
-    <hyperlink ref="E136" r:id="rId110" xr:uid="{2DAAFB64-43EF-4609-9512-3EECAF83A0D8}"/>
+    <hyperlink ref="E141" r:id="rId109" xr:uid="{A734FA6A-1E5E-4197-893E-26AEB8863486}"/>
+    <hyperlink ref="E137" r:id="rId110" xr:uid="{2DAAFB64-43EF-4609-9512-3EECAF83A0D8}"/>
     <hyperlink ref="E13" r:id="rId111" location="s0035" xr:uid="{B0E30218-34ED-4F0F-8578-9A603C364391}"/>
-    <hyperlink ref="E141" r:id="rId112" xr:uid="{33D09351-6D20-4F3E-B2E7-73DE845CAB80}"/>
-    <hyperlink ref="E143" r:id="rId113" xr:uid="{BA5C5148-161B-4925-9347-1EBB2828D7A5}"/>
-    <hyperlink ref="E124" r:id="rId114" xr:uid="{686C1381-B3D9-4F4F-B355-F6C8BDA10898}"/>
+    <hyperlink ref="E142" r:id="rId112" xr:uid="{33D09351-6D20-4F3E-B2E7-73DE845CAB80}"/>
+    <hyperlink ref="E144" r:id="rId113" xr:uid="{BA5C5148-161B-4925-9347-1EBB2828D7A5}"/>
+    <hyperlink ref="E125" r:id="rId114" xr:uid="{686C1381-B3D9-4F4F-B355-F6C8BDA10898}"/>
     <hyperlink ref="E70" r:id="rId115" xr:uid="{8A34E89F-B55C-44D1-9032-56436D05CE5D}"/>
     <hyperlink ref="E24" r:id="rId116" xr:uid="{F267D5CF-D0FE-473C-A3F7-FECCC233A441}"/>
     <hyperlink ref="E31" r:id="rId117" xr:uid="{442EB302-E477-4F77-B393-3E4D99A564E5}"/>
     <hyperlink ref="E46" r:id="rId118" xr:uid="{D135E4D3-2F2E-469B-85FF-8BEC89A2618B}"/>
     <hyperlink ref="E5" r:id="rId119" xr:uid="{12D8EB59-83CA-4597-928E-5FE6B23E156B}"/>
-    <hyperlink ref="E131" r:id="rId120" xr:uid="{81632F3A-005C-4176-BECE-2F3B9EEB6891}"/>
-    <hyperlink ref="E94" r:id="rId121" xr:uid="{37A04716-A03F-4D57-96D9-A5BFAD7D2359}"/>
-    <hyperlink ref="E129" r:id="rId122" xr:uid="{0E7FBF6C-CAA7-4FF2-A8EE-7F2D8A88BF96}"/>
-    <hyperlink ref="E137" r:id="rId123" xr:uid="{D55E6DD1-6984-4A50-A0AD-BA6FF596E41C}"/>
-    <hyperlink ref="E105" r:id="rId124" xr:uid="{2B877B96-8FD1-4F41-B88E-AD70830BE725}"/>
-    <hyperlink ref="E135" r:id="rId125" xr:uid="{7CB9413F-F297-47A4-B2F8-2E8BEC8F96E8}"/>
+    <hyperlink ref="E132" r:id="rId120" xr:uid="{81632F3A-005C-4176-BECE-2F3B9EEB6891}"/>
+    <hyperlink ref="E95" r:id="rId121" xr:uid="{37A04716-A03F-4D57-96D9-A5BFAD7D2359}"/>
+    <hyperlink ref="E130" r:id="rId122" xr:uid="{0E7FBF6C-CAA7-4FF2-A8EE-7F2D8A88BF96}"/>
+    <hyperlink ref="E138" r:id="rId123" xr:uid="{D55E6DD1-6984-4A50-A0AD-BA6FF596E41C}"/>
+    <hyperlink ref="E106" r:id="rId124" xr:uid="{2B877B96-8FD1-4F41-B88E-AD70830BE725}"/>
+    <hyperlink ref="E136" r:id="rId125" xr:uid="{7CB9413F-F297-47A4-B2F8-2E8BEC8F96E8}"/>
     <hyperlink ref="E25" r:id="rId126" xr:uid="{FA27BDCB-DB0A-480B-876B-7B017E0E677B}"/>
     <hyperlink ref="E20" r:id="rId127" xr:uid="{48520E64-60FA-43C7-9523-3F8A2187E6CC}"/>
     <hyperlink ref="E22" r:id="rId128" xr:uid="{05E3211D-230E-48F4-BB1E-822C21AAAFED}"/>
     <hyperlink ref="E59" r:id="rId129" xr:uid="{FD6A6FF4-BD3D-4A75-A3F7-C6081FFB6C91}"/>
     <hyperlink ref="E79" r:id="rId130" xr:uid="{A79F7F03-9B5B-4489-B080-107B98530A6B}"/>
-    <hyperlink ref="E100" r:id="rId131" xr:uid="{F431B0F7-5D38-4E60-AD18-2B301C1F824A}"/>
-    <hyperlink ref="E101" r:id="rId132" xr:uid="{8D237475-1999-48E3-B25D-339AE9C8EDD4}"/>
-    <hyperlink ref="E107" r:id="rId133" xr:uid="{6CFEE99F-77B8-453F-B0EB-481B5544EB7E}"/>
-    <hyperlink ref="E108" r:id="rId134" xr:uid="{0095BCC3-FA71-4827-B8E0-87D678153928}"/>
+    <hyperlink ref="E101" r:id="rId131" xr:uid="{F431B0F7-5D38-4E60-AD18-2B301C1F824A}"/>
+    <hyperlink ref="E102" r:id="rId132" xr:uid="{8D237475-1999-48E3-B25D-339AE9C8EDD4}"/>
+    <hyperlink ref="E108" r:id="rId133" xr:uid="{6CFEE99F-77B8-453F-B0EB-481B5544EB7E}"/>
+    <hyperlink ref="E109" r:id="rId134" xr:uid="{0095BCC3-FA71-4827-B8E0-87D678153928}"/>
     <hyperlink ref="E28" r:id="rId135" xr:uid="{620BDACF-75EA-4500-BA77-23B953049278}"/>
-    <hyperlink ref="E103" r:id="rId136" xr:uid="{E4CE47AF-12EB-4DBE-9E99-0FABFC9402A8}"/>
-    <hyperlink ref="E125" r:id="rId137" xr:uid="{A59ECC74-526B-4136-A3D5-05BA9BB6787C}"/>
-    <hyperlink ref="E128" r:id="rId138" xr:uid="{D6FF6640-82FF-4A0D-A828-72ED67D3AD4F}"/>
-    <hyperlink ref="E144" r:id="rId139" xr:uid="{9B13D64B-97F0-4098-BAE2-F0343CD81A80}"/>
-    <hyperlink ref="E138" r:id="rId140" xr:uid="{BADE4669-D317-4460-B448-C8D94D35753B}"/>
-    <hyperlink ref="E132" r:id="rId141" xr:uid="{850A2301-83A8-46A6-86BC-61587D12CD21}"/>
-    <hyperlink ref="E127" r:id="rId142" xr:uid="{7E135D94-3307-4285-876D-E50B63D987DF}"/>
+    <hyperlink ref="E104" r:id="rId136" xr:uid="{E4CE47AF-12EB-4DBE-9E99-0FABFC9402A8}"/>
+    <hyperlink ref="E126" r:id="rId137" xr:uid="{A59ECC74-526B-4136-A3D5-05BA9BB6787C}"/>
+    <hyperlink ref="E129" r:id="rId138" xr:uid="{D6FF6640-82FF-4A0D-A828-72ED67D3AD4F}"/>
+    <hyperlink ref="E145" r:id="rId139" xr:uid="{9B13D64B-97F0-4098-BAE2-F0343CD81A80}"/>
+    <hyperlink ref="E139" r:id="rId140" xr:uid="{BADE4669-D317-4460-B448-C8D94D35753B}"/>
+    <hyperlink ref="E133" r:id="rId141" xr:uid="{850A2301-83A8-46A6-86BC-61587D12CD21}"/>
+    <hyperlink ref="E128" r:id="rId142" xr:uid="{7E135D94-3307-4285-876D-E50B63D987DF}"/>
     <hyperlink ref="E58" r:id="rId143" xr:uid="{1AED701A-018D-49C9-969C-0C378A17C522}"/>
     <hyperlink ref="E63" r:id="rId144" xr:uid="{184F465E-B6F3-4207-8050-030FFF3C7183}"/>
     <hyperlink ref="E33" r:id="rId145" xr:uid="{6543D113-650C-4476-8130-C0483837619C}"/>
@@ -13708,52 +13779,52 @@
     <hyperlink ref="E84" r:id="rId181" xr:uid="{1AA34E58-053E-4462-B269-60B1C19E26FF}"/>
     <hyperlink ref="E85" r:id="rId182" xr:uid="{BEF77FE6-2F82-47F6-B96C-ADAF84945125}"/>
     <hyperlink ref="E86" r:id="rId183" xr:uid="{F2874A98-0A0B-45C2-8CD6-EA4A785A2370}"/>
-    <hyperlink ref="E90" r:id="rId184" xr:uid="{CA4C0D7C-9C19-4E48-A158-F4413BD6178C}"/>
-    <hyperlink ref="E92" r:id="rId185" xr:uid="{EEFF914F-ABA0-4E3C-9FD5-12FBECFDBB91}"/>
-    <hyperlink ref="E93" r:id="rId186" xr:uid="{88EE7216-4A06-465B-8FC6-606F50CBCFBC}"/>
-    <hyperlink ref="E96" r:id="rId187" xr:uid="{7BDEE9B8-5D7C-4202-B74C-6BE982C328AB}"/>
-    <hyperlink ref="E97" r:id="rId188" xr:uid="{77709C72-C9F9-499D-B133-6DF9E7E61890}"/>
-    <hyperlink ref="E98" r:id="rId189" xr:uid="{4F359565-B34E-4BD5-803D-7DC3D9732BAD}"/>
-    <hyperlink ref="E106" r:id="rId190" xr:uid="{A5574257-EDF9-4DC4-9A80-018F938B8B76}"/>
-    <hyperlink ref="E113" r:id="rId191" xr:uid="{E6837BC7-5BFC-4721-BAEC-5150ACC2E92A}"/>
-    <hyperlink ref="E114" r:id="rId192" xr:uid="{5AE70EB7-4DA2-4D5D-B00B-AE08DC919335}"/>
-    <hyperlink ref="E116" r:id="rId193" xr:uid="{C7A06CCF-1682-41F2-925C-4CCAC157C4E2}"/>
-    <hyperlink ref="E117" r:id="rId194" xr:uid="{2C04A538-B780-4A40-A836-B3954133A859}"/>
-    <hyperlink ref="E118" r:id="rId195" xr:uid="{533F3B58-531B-4E96-AF2B-08DB72D544CF}"/>
-    <hyperlink ref="E120" r:id="rId196" xr:uid="{62821B07-9EEB-41DA-A82A-CCDC6B6E1FB3}"/>
-    <hyperlink ref="E121" r:id="rId197" xr:uid="{B0802ADB-CF30-44C5-89E2-BCFA655BA70A}"/>
-    <hyperlink ref="E122" r:id="rId198" xr:uid="{9471BEB4-CC62-4A65-95D9-0E8F08554CFE}"/>
-    <hyperlink ref="E110" r:id="rId199" xr:uid="{349E9ACC-59EC-49C5-8729-16D1175BEF4F}"/>
+    <hyperlink ref="E91" r:id="rId184" xr:uid="{CA4C0D7C-9C19-4E48-A158-F4413BD6178C}"/>
+    <hyperlink ref="E93" r:id="rId185" xr:uid="{EEFF914F-ABA0-4E3C-9FD5-12FBECFDBB91}"/>
+    <hyperlink ref="E94" r:id="rId186" xr:uid="{88EE7216-4A06-465B-8FC6-606F50CBCFBC}"/>
+    <hyperlink ref="E97" r:id="rId187" xr:uid="{7BDEE9B8-5D7C-4202-B74C-6BE982C328AB}"/>
+    <hyperlink ref="E98" r:id="rId188" xr:uid="{77709C72-C9F9-499D-B133-6DF9E7E61890}"/>
+    <hyperlink ref="E99" r:id="rId189" xr:uid="{4F359565-B34E-4BD5-803D-7DC3D9732BAD}"/>
+    <hyperlink ref="E107" r:id="rId190" xr:uid="{A5574257-EDF9-4DC4-9A80-018F938B8B76}"/>
+    <hyperlink ref="E114" r:id="rId191" xr:uid="{E6837BC7-5BFC-4721-BAEC-5150ACC2E92A}"/>
+    <hyperlink ref="E115" r:id="rId192" xr:uid="{5AE70EB7-4DA2-4D5D-B00B-AE08DC919335}"/>
+    <hyperlink ref="E117" r:id="rId193" xr:uid="{C7A06CCF-1682-41F2-925C-4CCAC157C4E2}"/>
+    <hyperlink ref="E118" r:id="rId194" xr:uid="{2C04A538-B780-4A40-A836-B3954133A859}"/>
+    <hyperlink ref="E119" r:id="rId195" xr:uid="{533F3B58-531B-4E96-AF2B-08DB72D544CF}"/>
+    <hyperlink ref="E121" r:id="rId196" xr:uid="{62821B07-9EEB-41DA-A82A-CCDC6B6E1FB3}"/>
+    <hyperlink ref="E122" r:id="rId197" xr:uid="{B0802ADB-CF30-44C5-89E2-BCFA655BA70A}"/>
+    <hyperlink ref="E123" r:id="rId198" xr:uid="{9471BEB4-CC62-4A65-95D9-0E8F08554CFE}"/>
+    <hyperlink ref="E111" r:id="rId199" xr:uid="{349E9ACC-59EC-49C5-8729-16D1175BEF4F}"/>
     <hyperlink ref="E57" r:id="rId200" xr:uid="{BB6956D7-23ED-4A46-A37D-A8372BE7A10E}"/>
     <hyperlink ref="E2" r:id="rId201" xr:uid="{FA6C54D1-21A6-4366-A61A-B63E45510502}"/>
     <hyperlink ref="E12" r:id="rId202" xr:uid="{1811DDC7-B1CB-48D6-97CC-8589C8A392B3}"/>
     <hyperlink ref="E66" r:id="rId203" xr:uid="{C5DA3CF3-7B30-4A03-82DD-7F2E14081684}"/>
-    <hyperlink ref="E142" r:id="rId204" xr:uid="{7115DB7A-AE90-495D-9676-EA1BA0F179A0}"/>
-    <hyperlink ref="E91" r:id="rId205" xr:uid="{E875AA82-E9BD-43BA-B96A-443BE71A661D}"/>
-    <hyperlink ref="E130" r:id="rId206" display="https://standards.cencenelec.eu/dyn/www/f?p=CEN:110:0::::FSP_PROJECT,FSP_ORG_ID:67839,1991542&amp;cs=1BCE2DE4154949B53FB406C2D4EE5011D " xr:uid="{1198A376-FAFB-4B63-8F31-3CC40DDC0188}"/>
-    <hyperlink ref="E89" r:id="rId207" xr:uid="{CDB629AC-7318-4A45-902E-8C95EF4661CF}"/>
+    <hyperlink ref="E143" r:id="rId204" xr:uid="{7115DB7A-AE90-495D-9676-EA1BA0F179A0}"/>
+    <hyperlink ref="E92" r:id="rId205" xr:uid="{E875AA82-E9BD-43BA-B96A-443BE71A661D}"/>
+    <hyperlink ref="E131" r:id="rId206" display="https://standards.cencenelec.eu/dyn/www/f?p=CEN:110:0::::FSP_PROJECT,FSP_ORG_ID:67839,1991542&amp;cs=1BCE2DE4154949B53FB406C2D4EE5011D " xr:uid="{1198A376-FAFB-4B63-8F31-3CC40DDC0188}"/>
+    <hyperlink ref="E90" r:id="rId207" xr:uid="{CDB629AC-7318-4A45-902E-8C95EF4661CF}"/>
     <hyperlink ref="E27" r:id="rId208" xr:uid="{F20CB13F-7541-474A-BB7F-D8B745D301C0}"/>
-    <hyperlink ref="E139" r:id="rId209" xr:uid="{62676230-6266-4D08-B848-64E61BE4B592}"/>
+    <hyperlink ref="E140" r:id="rId209" xr:uid="{62676230-6266-4D08-B848-64E61BE4B592}"/>
     <hyperlink ref="E81" r:id="rId210" display="https://lov.linkeddata.es/dataset/lov/vocabs/jup/versions/2016-07-14.n3" xr:uid="{AE487E94-18DC-4254-BE84-4C41E95CF5BD}"/>
     <hyperlink ref="E32" r:id="rId211" xr:uid="{3B2D46D8-B3FB-420A-B722-C4AE65399511}"/>
     <hyperlink ref="E69" r:id="rId212" xr:uid="{CEDD056B-0AF1-476A-BD5E-3BDADF64D853}"/>
     <hyperlink ref="E30" r:id="rId213" xr:uid="{5E225EF5-93E6-41EE-89D9-FFE8A5198461}"/>
     <hyperlink ref="E29" r:id="rId214" xr:uid="{074596C3-DC36-46D9-B1FA-6177FB0CE294}"/>
     <hyperlink ref="E26" r:id="rId215" xr:uid="{8839DCA9-B1C9-4B05-BAA3-2A9B25F26A93}"/>
-    <hyperlink ref="E104" r:id="rId216" xr:uid="{16B53E58-79E0-4B7C-AC2E-C71F2322D92F}"/>
+    <hyperlink ref="E105" r:id="rId216" xr:uid="{16B53E58-79E0-4B7C-AC2E-C71F2322D92F}"/>
     <hyperlink ref="E68" r:id="rId217" xr:uid="{7E895DE5-2CE7-45C1-A136-57B4BCE29015}"/>
     <hyperlink ref="E67" r:id="rId218" xr:uid="{47784ED5-2C28-44C3-81EB-31DA2532A95A}"/>
     <hyperlink ref="E48" r:id="rId219" xr:uid="{D997BB59-BF3F-477F-A29B-A26EC0C6DB4C}"/>
-    <hyperlink ref="E111" r:id="rId220" xr:uid="{8B03E269-70CC-43E2-802D-196D1A76D2C6}"/>
-    <hyperlink ref="E112" r:id="rId221" xr:uid="{4CB1390B-88E8-414B-819B-3EBA1096C650}"/>
-    <hyperlink ref="E115" r:id="rId222" xr:uid="{7E0BEE99-7810-43FE-8B6E-F313CACD1280}"/>
-    <hyperlink ref="E119" r:id="rId223" xr:uid="{A941CDD9-0B08-4ACA-8885-324C2A700E2F}"/>
-    <hyperlink ref="E123" r:id="rId224" xr:uid="{4183CDB1-AB57-415B-91B7-AABB33124063}"/>
+    <hyperlink ref="E112" r:id="rId220" xr:uid="{8B03E269-70CC-43E2-802D-196D1A76D2C6}"/>
+    <hyperlink ref="E113" r:id="rId221" xr:uid="{4CB1390B-88E8-414B-819B-3EBA1096C650}"/>
+    <hyperlink ref="E116" r:id="rId222" xr:uid="{7E0BEE99-7810-43FE-8B6E-F313CACD1280}"/>
+    <hyperlink ref="E120" r:id="rId223" xr:uid="{A941CDD9-0B08-4ACA-8885-324C2A700E2F}"/>
+    <hyperlink ref="E124" r:id="rId224" xr:uid="{4183CDB1-AB57-415B-91B7-AABB33124063}"/>
     <hyperlink ref="E61" r:id="rId225" xr:uid="{BE8311D4-A8A6-4008-870A-9CEF9052ED5C}"/>
-    <hyperlink ref="C134" r:id="rId226" xr:uid="{8A2C5288-ADB4-463A-85BA-B1183BAF8DDF}"/>
+    <hyperlink ref="C135" r:id="rId226" xr:uid="{8A2C5288-ADB4-463A-85BA-B1183BAF8DDF}"/>
     <hyperlink ref="C55" r:id="rId227" xr:uid="{07F92C0D-DB82-4582-A72B-52659867C160}"/>
     <hyperlink ref="C8" r:id="rId228" xr:uid="{A84DDA47-6ACC-464D-952D-0387101E0611}"/>
-    <hyperlink ref="C145" r:id="rId229" xr:uid="{AE033172-A711-4880-AB36-40FB9AE60B05}"/>
+    <hyperlink ref="C146" r:id="rId229" xr:uid="{AE033172-A711-4880-AB36-40FB9AE60B05}"/>
     <hyperlink ref="C3" r:id="rId230" xr:uid="{87BD7AD7-F7D3-4FFD-A9E2-12853E86A7FE}"/>
     <hyperlink ref="E3" r:id="rId231" xr:uid="{512DDB69-1C56-4690-B2D9-AC64B48E7A6E}"/>
     <hyperlink ref="C54" r:id="rId232" xr:uid="{0F674644-7FE0-46D4-B1A3-3075C11E0658}"/>
@@ -13761,21 +13832,22 @@
     <hyperlink ref="E64" r:id="rId234" xr:uid="{D09DEDB3-49E2-4C48-B494-81711DA43BF0}"/>
     <hyperlink ref="C72" r:id="rId235" display="https://w3id.org/hmo" xr:uid="{E4AF1C6F-DF28-43F7-ACA9-70BE220B042B}"/>
     <hyperlink ref="E72" r:id="rId236" xr:uid="{49B2000D-4C70-49FD-A5F3-84C8A5029347}"/>
-    <hyperlink ref="C135" r:id="rId237" xr:uid="{0D2D8DED-68FD-46CA-AE92-1461FF576E92}"/>
-    <hyperlink ref="C137" r:id="rId238" xr:uid="{290C515B-CDF1-463F-85EB-BCFC5378D1E4}"/>
-    <hyperlink ref="C136" r:id="rId239" xr:uid="{DFE53865-6A47-46EC-BB35-4A0B7009EA86}"/>
-    <hyperlink ref="C138" r:id="rId240" xr:uid="{54FC6350-1D41-40D1-85C1-5FEB82150346}"/>
-    <hyperlink ref="C139" r:id="rId241" xr:uid="{218ED3BE-F2B1-4A98-ADC4-F128684E3B28}"/>
-    <hyperlink ref="C140" r:id="rId242" xr:uid="{31E930C8-EAAF-4B34-8443-75427984FA75}"/>
-    <hyperlink ref="C102" r:id="rId243" xr:uid="{379FD10B-9650-463A-84C0-55B4727D7D47}"/>
-    <hyperlink ref="E102" r:id="rId244" xr:uid="{F803CDF1-49F8-4F15-83C4-1374EEB2B30A}"/>
-    <hyperlink ref="C146" r:id="rId245" xr:uid="{C5C87514-E810-480B-A94B-83BB9DAD7389}"/>
+    <hyperlink ref="C136" r:id="rId237" xr:uid="{0D2D8DED-68FD-46CA-AE92-1461FF576E92}"/>
+    <hyperlink ref="C138" r:id="rId238" xr:uid="{290C515B-CDF1-463F-85EB-BCFC5378D1E4}"/>
+    <hyperlink ref="C137" r:id="rId239" xr:uid="{DFE53865-6A47-46EC-BB35-4A0B7009EA86}"/>
+    <hyperlink ref="C139" r:id="rId240" xr:uid="{54FC6350-1D41-40D1-85C1-5FEB82150346}"/>
+    <hyperlink ref="C140" r:id="rId241" xr:uid="{218ED3BE-F2B1-4A98-ADC4-F128684E3B28}"/>
+    <hyperlink ref="C141" r:id="rId242" xr:uid="{31E930C8-EAAF-4B34-8443-75427984FA75}"/>
+    <hyperlink ref="C103" r:id="rId243" xr:uid="{379FD10B-9650-463A-84C0-55B4727D7D47}"/>
+    <hyperlink ref="E103" r:id="rId244" xr:uid="{F803CDF1-49F8-4F15-83C4-1374EEB2B30A}"/>
+    <hyperlink ref="C88" r:id="rId245" xr:uid="{C5C87514-E810-480B-A94B-83BB9DAD7389}"/>
+    <hyperlink ref="C147" r:id="rId246" xr:uid="{6EEE95DA-9BE0-4E1F-8E9A-8A354ABF1F8F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId246"/>
-  <legacyDrawing r:id="rId247"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId247"/>
+  <legacyDrawing r:id="rId248"/>
   <tableParts count="1">
-    <tablePart r:id="rId248"/>
+    <tablePart r:id="rId249"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -13784,7 +13856,7 @@
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$28</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H145 G146</xm:sqref>
+          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H147</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -13954,25 +14026,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100617EB9F8E3ABAA489A6191778AAEABC8" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="be0c97903f599d62d21cd63252cde9aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e06419a-bc24-4bca-aaf1-3b90bf7d837a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="784cf5edc76b43144e46369ffdbd4f65" ns2:_="">
     <xsd:import namespace="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
@@ -14176,25 +14229,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719C6BFD-522D-4738-8247-E6F78DD5AA9E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14212,6 +14266,24 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{1faf88fe-a998-4c5b-93c9-210a11d9a5c2}" enabled="0" method="" siteId="{1faf88fe-a998-4c5b-93c9-210a11d9a5c2}" removed="1"/>

--- a/data/source/ontologies_source.xlsx
+++ b/data/source/ontologies_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbosche\Documents\GitHub\BE-OLS\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06C3459-009F-487D-8D0A-1E49AADB3E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FB22AE-7EE7-4006-983B-676E781C7091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="23730" windowHeight="15585" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="14" r:id="rId1"/>
@@ -390,7 +390,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="1099">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2899" uniqueCount="1155">
   <si>
     <t>BE Product (Building)</t>
   </si>
@@ -3679,12 +3679,6 @@
     <t>xemo</t>
   </si>
   <si>
-    <t>https://github.com/AlessandroBruttini/XEMO</t>
-  </si>
-  <si>
-    <t>Bruttini, A., Hagedorn, P., Getuli, V., Capone, P., and König, M. (2026). XEMO: Construction Site Emission Management Ontology for Particulate Matter. EG-ICE 2026.</t>
-  </si>
-  <si>
     <t>XEMO represents:
 an urban region containing one or more construction sites; construction sites organised into construction areas; construction activities carried out within those areas; sites, areas, and activities as emission sources at different spatial and operational scales; pollutants as observable properties of emission sources; sensors, platforms, deployments, and observations; thresholds defined by value, unit, type, averaging period, statistical method, and regulatory provenance.
 The current implementation includes PM10, PM2.5, and total suspended particles, together with example threshold definitions derived from Directive (EU) 2024/2881.</t>
@@ -3697,6 +3691,185 @@
   </si>
   <si>
     <t>wgs84_pos</t>
+  </si>
+  <si>
+    <t>bimxel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
+    <t>BIMxel: Ontology for Sustainable Building Information Management</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bimxel#</t>
+  </si>
+  <si>
+    <t>https://example.org/xemo#</t>
+  </si>
+  <si>
+    <t>Bruttini, A., Hagedorn, P., Getuli, V., Capone, P., and König, M. (2026). XEMO: Construction Site Emission Management Ontology for Particulate Matter. EG-ICE 2026; https://github.com/AlessandroBruttini/XEMO</t>
+  </si>
+  <si>
+    <t>The BIMxel ontology acts as a semantic bridge between widely adopted ontologies and standards—including BOT, SAREF, SAREF4ENER, PROV-O, DCAT, QUDT, GeoSPARQL, and BEO—to support the interoperable generation of building digital twins. BIMxel integrates BIM data, sensors, measurements, external data services, and provenance information into a unified knowledge graph, enabling continuous monitoring of building operation and energy consumption. By linking heterogeneous sources such as IFC models, IoT devices and physical properties, the ontology provides a scalable semantic foundation for assessing operational carbon impact and supporting data-driven strategies for more sustainable buildings.</t>
+  </si>
+  <si>
+    <t>beo, bot, mep, saref, s4bldg, s4city, s4ener, s4watr</t>
+  </si>
+  <si>
+    <t>prov, schema, dcat, dcterms</t>
+  </si>
+  <si>
+    <t>BCore</t>
+  </si>
+  <si>
+    <t>Bcore</t>
+  </si>
+  <si>
+    <t>Bridge Core Ontology</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore</t>
+  </si>
+  <si>
+    <t>https://github.com/TUD-IMB/Bcore</t>
+  </si>
+  <si>
+    <t>0.1.1</t>
+  </si>
+  <si>
+    <t>The Bridge Core Ontology (BCore) enables the representation of a bridge structure, its components and material, as well as the infrastructure and media files connected to it and the environment and location of the bridge. BCore is created by the Institute of Concrete Structures (IMB) at the Dresden University of Technology (TUD).</t>
+  </si>
+  <si>
+    <t>reloc, brot, brcomp, bot, bmat, infraspatialot</t>
+  </si>
+  <si>
+    <t>Bridge Core Ontology – Media Extension</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/media</t>
+  </si>
+  <si>
+    <t>https://github.com/TUD-IMB/BCore</t>
+  </si>
+  <si>
+    <t>The BCoreMedia Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing bridge‑related media and documentation.
+It models any analog or digital asset from images and videos to inspection reports and sensor recordings, that support the documentation, monitoring, and analysis of a bridge throughout its lifecycle.
+BCoreMedia builds directly on BCore’s top‑level structure, ensuring that every media item can be consistently linked to the bridge, its components, its materials, or its spatial context. It integrates seamlessly with component, material, infrastructure, and zone modules to enable rich, multi‑domain documentation workflows.</t>
+  </si>
+  <si>
+    <t>bcore, brot</t>
+  </si>
+  <si>
+    <t>Bridge Core Ontology – Zones Extension</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/zones</t>
+  </si>
+  <si>
+    <t>The BCoreZones Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing spatial zones and environmental context around a bridge.
+It models regions, environmental areas, and contextual spatial relationships that help characterize where a bridge is situated and how it interacts with its surroundings.
+BCoreZones builds directly on BCore’s top‑level structure, ensuring that every spatial zone can be consistently linked to the bridge or its components. It integrates seamlessly with component, material, infrastructure, and media modules to support comprehensive, multi‑domain bridge modeling.</t>
+  </si>
+  <si>
+    <t>Bridge Core Ontology – Infrastructure Extension</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/infra</t>
+  </si>
+  <si>
+    <t>The BCoreInfra Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing bridge-related infrastructure.
+It models roads, railways, waterways, and other contextual infrastructure elements that interact with or influence the bridge. BCoreInfra builds directly on BCore’s top‑level structure, ensuring that every infrastructure element can be consistently linked to the bridge it serves or affects. It integrates seamlessly with component, material, media, and spatial‑zone modules to support comprehensive, multi‑domain bridge modeling.</t>
+  </si>
+  <si>
+    <t>bcore</t>
+  </si>
+  <si>
+    <t>vann, foaf, schema, bibo</t>
+  </si>
+  <si>
+    <t>Bridge Core Ontology – Material Extension</t>
+  </si>
+  <si>
+    <t>bcoremat</t>
+  </si>
+  <si>
+    <t>bcoreinfra</t>
+  </si>
+  <si>
+    <t>bcorezones</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/mat</t>
+  </si>
+  <si>
+    <t>The BCoreMat Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing materials used in bridge construction. It models concrete, steel, composites, coatings, and other material types, along with their properties and classifications. This enables consistent, semantically rich descriptions of what bridges and their components are made of. BCoreMat builds directly on BCore’s top‑level structure, ensuring that every material can be consistently linked to the bridge or its components. It integrates seamlessly with component, infrastructure, media, and spatial‑zone modules to support comprehensive, multi‑domain bridge modeling. #### BCore Ontology Suite: | Module | Purpose | |--------|---------| | BCore | Core identity, top‑level bridge concepts, and shared linking structure. | | BCoreComp | Structural and functional bridge components. | | BCoreMat | Materials used in bridge construction. | | BCoreInfra | Bridge-related transport and utility infrastructure. | | BCoreZones | Spatial zones, geometric context, and environmental regions. | | BCoreMedia | Media files, documentation, and digital assets. | #### About BCoreMat: BCoreMat provides a structured, extensible model for representing the various materials used in bridge construction. Main focus: - Material types such as concrete, steel, composites, and coatings - Material properties relevant for structural and durability assessment - Clear relationships between materials and bridge components - Consistent integration with BCore’s core identity and structure - Interoperability across all BCore modules → Thus, it is the right choice when you need to describe what a bridge is made of and how material information supports analysis, inspection, and lifecycle management.</t>
+  </si>
+  <si>
+    <t>Bridge Core Ontology – Components Extension</t>
+  </si>
+  <si>
+    <t>bcorecomp</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/comp</t>
+  </si>
+  <si>
+    <t>The Bridge Core Ontology (BCore) enables the representation of a bridge structure, its components and material, as well as the infrastructure and media files connected to it and the environment and location of the bridge. BCore is created by the Institute of Concrete Structures (IMB) at the Dresden University of Technology (TUD). This ontology contains the corresponding components extension.</t>
+  </si>
+  <si>
+    <t>brot, brcomp, infraspatialot</t>
+  </si>
+  <si>
+    <t>Ontology for structuring design rules for bridge components</t>
+  </si>
+  <si>
+    <t>bedro</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bedro</t>
+  </si>
+  <si>
+    <t>The Bridge Element Design Rule Ontology (BEDRO) is a concept for the implementation of German bridge design rules via the Semantic Web Rule Language (SWRL) and the SHACL Rule Language (SRL). BEDRO includes many geometric bridge design parameters named after a newly developed naming convention.</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>bcore, bcorecomp, bcoreinfra, bcoremat, bcorezones, brot, brcomp, reloc, bot, infraspatialot, bmat</t>
+  </si>
+  <si>
+    <t>Bridge Engineering Drawing Ontology</t>
+  </si>
+  <si>
+    <t>bedo</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bedo#</t>
+  </si>
+  <si>
+    <t>bmat, brot</t>
+  </si>
+  <si>
+    <t>vann, foaf</t>
+  </si>
+  <si>
+    <t>The Bridge Engineering Drawing Ontology (BEDO) is an ontology designed to represent and organize semantic information extracted from bridge engineering drawings. It provides a structured vocabulary for describing engineering documents, drawings, drawing series, title blocks, drawing views, view titles, lifecycle stages, and their relationships to bridges and bridge components. BEDO supports the explicit modeling of both document-level metadata and view-level graphical information, including drawing identifiers, project names, organization names, scales, file paths, bounding boxes, and OCR-extracted textual content. By linking drawings and drawing views to bridge components, the ontology enables semantic integration between engineering documentation, computer vision outputs, and bridge asset information. BEDO is intended to support downstream tasks such as automated drawing interpretation, information retrieval, knowledge graph construction, and lifecycle-oriented bridge information management.</t>
+  </si>
+  <si>
+    <t>Ontology submission: Ontology for spatial relationships in Road Infastructure</t>
+  </si>
+  <si>
+    <t>infraspatialot</t>
+  </si>
+  <si>
+    <t>https://dtc-ontology.cms.ed.tum.de/infraspatialot</t>
+  </si>
+  <si>
+    <t>https://ceur-ws.org/Vol-3824/paper5.pdf</t>
+  </si>
+  <si>
+    <t>This ontology enables the description of spatial relationships in a road infrastructure system. For this purpose, the spatial relationships of road infrastructure elements to a reference element are explicitly recorded. The explicit recording of the relationship of several road infrastructure elements to the same reference element then implicitly contains the relationship of the road infrastructure elements to each other, which can then be analysed depending on the usecase.</t>
   </si>
 </sst>
 </file>
@@ -3988,8 +4161,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V147" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:V147" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V157" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:V157" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V146">
     <sortCondition ref="B1:B146"/>
   </sortState>
@@ -4406,17 +4579,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484B993-682B-477D-B31E-A58D58B7BF22}">
-  <dimension ref="A1:Z147"/>
+  <dimension ref="A1:Z157"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" customWidth="1"/>
     <col min="3" max="3" width="42.7109375" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="8" width="26.85546875" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" customWidth="1"/>
+    <col min="6" max="8" width="26.85546875" customWidth="1"/>
     <col min="9" max="9" width="10" style="10" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
     <col min="12" max="12" width="45.5703125" style="3" customWidth="1"/>
     <col min="13" max="13" width="26.5703125" style="3" customWidth="1"/>
     <col min="14" max="14" width="46" style="3" customWidth="1"/>
@@ -4498,7 +4672,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>512</v>
       </c>
@@ -10472,7 +10646,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="98" spans="1:26" ht="60" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>364</v>
       </c>
@@ -10784,7 +10958,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="103" spans="1:26" ht="105" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" ht="150" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1079</v>
       </c>
@@ -12159,7 +12333,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="125" spans="1:22" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:22" s="17" customFormat="1" ht="150" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>433</v>
       </c>
@@ -12728,7 +12902,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="134" spans="1:22" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:22" s="17" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>466</v>
       </c>
@@ -13205,7 +13379,7 @@
         <v>896</v>
       </c>
       <c r="M141" s="3" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="N141" s="3" t="s">
         <v>474</v>
@@ -13485,7 +13659,7 @@
         <v>741</v>
       </c>
       <c r="B146" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C146" s="27" t="s">
         <v>804</v>
@@ -13550,13 +13724,13 @@
         <v>1092</v>
       </c>
       <c r="C147" s="27" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E147" s="29" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="F147" s="29" t="s">
         <v>38</v>
@@ -13577,13 +13751,13 @@
         <v>23</v>
       </c>
       <c r="L147" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="M147" t="s">
+        <v>1094</v>
+      </c>
+      <c r="N147" s="15" t="s">
         <v>1095</v>
-      </c>
-      <c r="M147" t="s">
-        <v>1096</v>
-      </c>
-      <c r="N147" s="15" t="s">
-        <v>1097</v>
       </c>
       <c r="O147" s="32" t="s">
         <v>29</v>
@@ -13592,6 +13766,488 @@
       <c r="T147" s="32"/>
       <c r="U147" s="32"/>
       <c r="V147" s="34"/>
+    </row>
+    <row r="148" spans="1:22" ht="240" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C148" s="27" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F148" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G148" t="s">
+        <v>5</v>
+      </c>
+      <c r="H148" t="s">
+        <v>4</v>
+      </c>
+      <c r="I148" t="s">
+        <v>1098</v>
+      </c>
+      <c r="J148">
+        <v>2026</v>
+      </c>
+      <c r="K148" t="s">
+        <v>133</v>
+      </c>
+      <c r="L148" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="M148" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="N148" s="15" t="s">
+        <v>1105</v>
+      </c>
+      <c r="O148" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="S148" s="33"/>
+      <c r="T148" s="32"/>
+      <c r="U148" s="32"/>
+      <c r="V148" s="34"/>
+    </row>
+    <row r="149" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C149" s="27" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F149" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G149" t="s">
+        <v>1</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J149">
+        <v>2025</v>
+      </c>
+      <c r="K149" t="s">
+        <v>133</v>
+      </c>
+      <c r="L149" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="M149" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="N149" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="O149" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S149" s="33"/>
+      <c r="T149" s="32"/>
+      <c r="U149" s="32"/>
+      <c r="V149" s="34"/>
+    </row>
+    <row r="150" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C150" s="27" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F150" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I150" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J150">
+        <v>2025</v>
+      </c>
+      <c r="K150" t="s">
+        <v>133</v>
+      </c>
+      <c r="L150" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="M150" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="N150" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="O150" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S150" s="33"/>
+      <c r="T150" s="32"/>
+      <c r="U150" s="32"/>
+      <c r="V150" s="34"/>
+    </row>
+    <row r="151" spans="1:22" ht="225" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C151" s="27" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F151" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G151" t="s">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>8</v>
+      </c>
+      <c r="I151" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J151">
+        <v>2025</v>
+      </c>
+      <c r="K151" t="s">
+        <v>133</v>
+      </c>
+      <c r="L151" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="M151" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N151" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="O151" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S151" s="33"/>
+      <c r="T151" s="32"/>
+      <c r="U151" s="32"/>
+      <c r="V151" s="34"/>
+    </row>
+    <row r="152" spans="1:22" ht="210" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C152" s="27" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F152" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G152" t="s">
+        <v>1</v>
+      </c>
+      <c r="I152" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J152">
+        <v>2025</v>
+      </c>
+      <c r="K152" t="s">
+        <v>133</v>
+      </c>
+      <c r="L152" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M152" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="N152" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="O152" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S152" s="33"/>
+      <c r="T152" s="32"/>
+      <c r="U152" s="32"/>
+      <c r="V152" s="34"/>
+    </row>
+    <row r="153" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C153" s="27" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F153" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G153" t="s">
+        <v>11</v>
+      </c>
+      <c r="H153" t="s">
+        <v>1</v>
+      </c>
+      <c r="I153" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J153">
+        <v>2025</v>
+      </c>
+      <c r="K153" t="s">
+        <v>133</v>
+      </c>
+      <c r="L153" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="M153" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="N153" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="O153" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S153" s="33"/>
+      <c r="T153" s="32"/>
+      <c r="U153" s="32"/>
+      <c r="V153" s="34"/>
+    </row>
+    <row r="154" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C154" s="27" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F154" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G154" t="s">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>5</v>
+      </c>
+      <c r="I154" s="10" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J154">
+        <v>2025</v>
+      </c>
+      <c r="K154" t="s">
+        <v>133</v>
+      </c>
+      <c r="L154" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="M154" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="N154" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="O154" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S154" s="33"/>
+      <c r="T154" s="32"/>
+      <c r="U154" s="32"/>
+      <c r="V154" s="34"/>
+    </row>
+    <row r="155" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D155" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="F155" s="1"/>
+      <c r="G155" t="s">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
+        <v>11</v>
+      </c>
+      <c r="I155" s="10" t="s">
+        <v>1142</v>
+      </c>
+      <c r="J155">
+        <v>2025</v>
+      </c>
+      <c r="K155" t="s">
+        <v>133</v>
+      </c>
+      <c r="L155" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="M155" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="N155" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="O155" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S155" s="33"/>
+      <c r="T155" s="32"/>
+      <c r="U155" s="32"/>
+      <c r="V155" s="34"/>
+    </row>
+    <row r="156" spans="1:22" ht="345" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C156" s="27" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D156" s="7"/>
+      <c r="E156" s="1"/>
+      <c r="F156" s="1"/>
+      <c r="G156" t="s">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>8</v>
+      </c>
+      <c r="I156" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="J156">
+        <v>2026</v>
+      </c>
+      <c r="K156" t="s">
+        <v>133</v>
+      </c>
+      <c r="L156" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="M156" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="N156" s="15" t="s">
+        <v>1148</v>
+      </c>
+      <c r="O156" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S156" s="33"/>
+      <c r="T156" s="32"/>
+      <c r="U156" s="32"/>
+      <c r="V156" s="34"/>
+    </row>
+    <row r="157" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C157" s="27" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F157" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G157" t="s">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>8</v>
+      </c>
+      <c r="I157" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="J157">
+        <v>2024</v>
+      </c>
+      <c r="K157" t="s">
+        <v>133</v>
+      </c>
+      <c r="L157" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="N157" s="15"/>
+      <c r="S157" s="33"/>
+      <c r="T157" s="32"/>
+      <c r="U157" s="32"/>
+      <c r="V157" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -13842,12 +14498,30 @@
     <hyperlink ref="E103" r:id="rId244" xr:uid="{F803CDF1-49F8-4F15-83C4-1374EEB2B30A}"/>
     <hyperlink ref="C88" r:id="rId245" xr:uid="{C5C87514-E810-480B-A94B-83BB9DAD7389}"/>
     <hyperlink ref="C147" r:id="rId246" xr:uid="{6EEE95DA-9BE0-4E1F-8E9A-8A354ABF1F8F}"/>
+    <hyperlink ref="C148" r:id="rId247" xr:uid="{0379DD25-CEE8-4F75-8C9B-E81D3B61747B}"/>
+    <hyperlink ref="E148" r:id="rId248" xr:uid="{E2A3119B-37AA-43A8-A582-4ED028637960}"/>
+    <hyperlink ref="C149" r:id="rId249" xr:uid="{A32D057F-0E64-4CBF-9B62-C57706447D34}"/>
+    <hyperlink ref="E149" r:id="rId250" xr:uid="{A65F3CDA-CD7D-4433-A029-81CC9238D823}"/>
+    <hyperlink ref="C150" r:id="rId251" xr:uid="{CBACED67-B915-430A-ABFB-6E922C06F5DB}"/>
+    <hyperlink ref="E150" r:id="rId252" xr:uid="{D19A3F16-CA81-4C85-B42A-FE0EB7D29FD6}"/>
+    <hyperlink ref="E151" r:id="rId253" xr:uid="{892CE20C-2CEA-4A57-8CB2-DE1FFDF67484}"/>
+    <hyperlink ref="E152" r:id="rId254" xr:uid="{73DE6366-9616-419D-A431-4F1008663A9E}"/>
+    <hyperlink ref="E153" r:id="rId255" xr:uid="{FC638811-A0C3-41F5-B132-5E9AC65F5A04}"/>
+    <hyperlink ref="E154" r:id="rId256" xr:uid="{64C26841-E8E4-4556-A67D-888111E8C883}"/>
+    <hyperlink ref="C151" r:id="rId257" xr:uid="{EEE203C4-C0DB-4A31-9B51-43E0DFF8BE38}"/>
+    <hyperlink ref="C152" r:id="rId258" xr:uid="{9E4FAC27-1581-492F-A27D-78631630D968}"/>
+    <hyperlink ref="C153" r:id="rId259" xr:uid="{3E4C2CEC-A992-4071-8AE1-06983D54F46F}"/>
+    <hyperlink ref="C154" r:id="rId260" xr:uid="{39874698-1D5A-41F0-90EF-FA837F5C1B23}"/>
+    <hyperlink ref="C155" r:id="rId261" xr:uid="{CBF98465-F451-41BC-8811-E98E321BE048}"/>
+    <hyperlink ref="C156" r:id="rId262" xr:uid="{1C6A0EA2-A8D6-4C7E-8833-72CD216F91B6}"/>
+    <hyperlink ref="C157" r:id="rId263" xr:uid="{3EAB1B23-E180-46E2-9E59-CF59E174BE8D}"/>
+    <hyperlink ref="E157" r:id="rId264" xr:uid="{9C03D4EC-81F8-4A0E-AE28-7FCE9FEC76F3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId247"/>
-  <legacyDrawing r:id="rId248"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId265"/>
+  <legacyDrawing r:id="rId266"/>
   <tableParts count="1">
-    <tablePart r:id="rId249"/>
+    <tablePart r:id="rId267"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -13856,7 +14530,7 @@
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$28</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H147</xm:sqref>
+          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H157</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -14026,6 +14700,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100617EB9F8E3ABAA489A6191778AAEABC8" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="be0c97903f599d62d21cd63252cde9aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7e06419a-bc24-4bca-aaf1-3b90bf7d837a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="784cf5edc76b43144e46369ffdbd4f65" ns2:_="">
     <xsd:import namespace="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
@@ -14229,26 +14922,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719C6BFD-522D-4738-8247-E6F78DD5AA9E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14266,24 +14958,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{1faf88fe-a998-4c5b-93c9-210a11d9a5c2}" enabled="0" method="" siteId="{1faf88fe-a998-4c5b-93c9-210a11d9a5c2}" removed="1"/>

--- a/data/source/ontologies_source.xlsx
+++ b/data/source/ontologies_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbosche\Documents\GitHub\BE-OLS\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FB22AE-7EE7-4006-983B-676E781C7091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F865C2FC-A4BA-4F85-AFB1-F833352BEAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="23730" windowHeight="15585" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="14" r:id="rId1"/>
@@ -3723,9 +3723,6 @@
     <t>BCore</t>
   </si>
   <si>
-    <t>Bcore</t>
-  </si>
-  <si>
     <t>Bridge Core Ontology</t>
   </si>
   <si>
@@ -3870,6 +3867,9 @@
   </si>
   <si>
     <t>This ontology enables the description of spatial relationships in a road infrastructure system. For this purpose, the spatial relationships of road infrastructure elements to a reference element are explicitly recorded. The explicit recording of the relationship of several road infrastructure elements to the same reference element then implicitly contains the relationship of the road infrastructure elements to each other, which can then be analysed depending on the usecase.</t>
+  </si>
+  <si>
+    <t>bcoremedia</t>
   </si>
 </sst>
 </file>
@@ -13820,19 +13820,19 @@
     </row>
     <row r="149" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C149" s="27" t="s">
         <v>1108</v>
-      </c>
-      <c r="B149" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C149" s="27" t="s">
-        <v>1109</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F149" s="29" t="s">
         <v>38</v>
@@ -13841,7 +13841,7 @@
         <v>1</v>
       </c>
       <c r="I149" s="10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="J149">
         <v>2025</v>
@@ -13850,13 +13850,13 @@
         <v>133</v>
       </c>
       <c r="L149" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="M149" s="3" t="s">
         <v>1112</v>
       </c>
-      <c r="M149" s="3" t="s">
-        <v>1113</v>
-      </c>
       <c r="N149" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="O149" s="32" t="s">
         <v>30</v>
@@ -13868,25 +13868,25 @@
     </row>
     <row r="150" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C150" s="27" t="s">
         <v>1114</v>
-      </c>
-      <c r="B150" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C150" s="27" t="s">
-        <v>1115</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="E150" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F150" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I150" s="10" t="s">
         <v>1110</v>
-      </c>
-      <c r="F150" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="I150" s="10" t="s">
-        <v>1111</v>
       </c>
       <c r="J150">
         <v>2025</v>
@@ -13895,13 +13895,13 @@
         <v>133</v>
       </c>
       <c r="L150" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="M150" s="3" t="s">
         <v>1117</v>
       </c>
-      <c r="M150" s="3" t="s">
-        <v>1118</v>
-      </c>
       <c r="N150" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="O150" s="32" t="s">
         <v>30</v>
@@ -13913,19 +13913,19 @@
     </row>
     <row r="151" spans="1:22" ht="225" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C151" s="27" t="s">
         <v>1119</v>
-      </c>
-      <c r="B151" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C151" s="27" t="s">
-        <v>1120</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F151" s="29" t="s">
         <v>38</v>
@@ -13937,7 +13937,7 @@
         <v>8</v>
       </c>
       <c r="I151" s="10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="J151">
         <v>2025</v>
@@ -13946,13 +13946,13 @@
         <v>133</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="M151" s="3" t="s">
         <v>83</v>
       </c>
       <c r="N151" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="O151" s="32" t="s">
         <v>30</v>
@@ -13964,19 +13964,19 @@
     </row>
     <row r="152" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C152" s="27" t="s">
         <v>1122</v>
-      </c>
-      <c r="B152" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C152" s="27" t="s">
-        <v>1123</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F152" s="29" t="s">
         <v>38</v>
@@ -13985,7 +13985,7 @@
         <v>1</v>
       </c>
       <c r="I152" s="10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="J152">
         <v>2025</v>
@@ -13994,13 +13994,13 @@
         <v>133</v>
       </c>
       <c r="L152" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="M152" s="3" t="s">
         <v>1124</v>
       </c>
-      <c r="M152" s="3" t="s">
+      <c r="N152" s="15" t="s">
         <v>1125</v>
-      </c>
-      <c r="N152" s="15" t="s">
-        <v>1126</v>
       </c>
       <c r="O152" s="32" t="s">
         <v>30</v>
@@ -14012,19 +14012,19 @@
     </row>
     <row r="153" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B153" t="s">
         <v>1127</v>
       </c>
-      <c r="B153" t="s">
-        <v>1128</v>
-      </c>
       <c r="C153" s="27" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D153" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F153" s="29" t="s">
         <v>38</v>
@@ -14036,7 +14036,7 @@
         <v>1</v>
       </c>
       <c r="I153" s="10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="J153">
         <v>2025</v>
@@ -14045,13 +14045,13 @@
         <v>133</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="M153" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N153" s="15" t="s">
         <v>1125</v>
-      </c>
-      <c r="N153" s="15" t="s">
-        <v>1126</v>
       </c>
       <c r="O153" s="32" t="s">
         <v>30</v>
@@ -14063,19 +14063,19 @@
     </row>
     <row r="154" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B154" t="s">
         <v>1133</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" s="27" t="s">
         <v>1134</v>
-      </c>
-      <c r="C154" s="27" t="s">
-        <v>1135</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F154" s="29" t="s">
         <v>38</v>
@@ -14087,7 +14087,7 @@
         <v>5</v>
       </c>
       <c r="I154" s="10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="J154">
         <v>2025</v>
@@ -14096,13 +14096,13 @@
         <v>133</v>
       </c>
       <c r="L154" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="M154" s="3" t="s">
         <v>1136</v>
       </c>
-      <c r="M154" s="3" t="s">
-        <v>1137</v>
-      </c>
       <c r="N154" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="O154" s="32" t="s">
         <v>30</v>
@@ -14114,13 +14114,13 @@
     </row>
     <row r="155" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B155" t="s">
         <v>1138</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C155" s="1" t="s">
         <v>1139</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>1140</v>
       </c>
       <c r="D155" s="29" t="s">
         <v>38</v>
@@ -14136,7 +14136,7 @@
         <v>11</v>
       </c>
       <c r="I155" s="10" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="J155">
         <v>2025</v>
@@ -14145,13 +14145,13 @@
         <v>133</v>
       </c>
       <c r="L155" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="M155" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="N155" s="15" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="O155" s="32" t="s">
         <v>30</v>
@@ -14163,13 +14163,13 @@
     </row>
     <row r="156" spans="1:22" ht="345" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B156" t="s">
         <v>1144</v>
       </c>
-      <c r="B156" t="s">
+      <c r="C156" s="27" t="s">
         <v>1145</v>
-      </c>
-      <c r="C156" s="27" t="s">
-        <v>1146</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="1"/>
@@ -14190,13 +14190,13 @@
         <v>133</v>
       </c>
       <c r="L156" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M156" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="N156" s="15" t="s">
         <v>1147</v>
-      </c>
-      <c r="N156" s="15" t="s">
-        <v>1148</v>
       </c>
       <c r="O156" s="32" t="s">
         <v>30</v>
@@ -14208,19 +14208,19 @@
     </row>
     <row r="157" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B157" t="s">
         <v>1150</v>
       </c>
-      <c r="B157" t="s">
+      <c r="C157" s="27" t="s">
         <v>1151</v>
       </c>
-      <c r="C157" s="27" t="s">
+      <c r="D157" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>1152</v>
-      </c>
-      <c r="D157" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>1153</v>
       </c>
       <c r="F157" s="29" t="s">
         <v>38</v>
@@ -14241,7 +14241,7 @@
         <v>133</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="N157" s="15"/>
       <c r="S157" s="33"/>
@@ -14700,6 +14700,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7e06419a-bc24-4bca-aaf1-3b90bf7d837a">
@@ -14707,15 +14716,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14923,19 +14923,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CBC734A-37E0-4A55-B328-89CFAE297459}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="7e06419a-bc24-4bca-aaf1-3b90bf7d837a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1E73802-DE0F-482B-8B75-044CD712CFB1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/source/ontologies_source.xlsx
+++ b/data/source/ontologies_source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fbosche\Documents\GitHub\BE-OLS\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8370C2A3-9DB0-4E2B-B6ED-5D0EC2F15CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7FD5EA-9E22-41E1-A3CB-F608DC1810BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21465" windowHeight="12645" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
+    <workbookView xWindow="8025" yWindow="2610" windowWidth="21465" windowHeight="12645" xr2:uid="{C460B36E-D875-4E13-ACEB-9CF2004FB6B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="14" r:id="rId1"/>
@@ -390,7 +390,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2899" uniqueCount="1155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="1169">
   <si>
     <t>BE Product (Building)</t>
   </si>
@@ -3723,9 +3723,6 @@
     <t>Bridge Core Ontology – Media Extension</t>
   </si>
   <si>
-    <t>https://w3id.org/bcore/media</t>
-  </si>
-  <si>
     <t>https://github.com/TUD-IMB/BCore</t>
   </si>
   <si>
@@ -3740,9 +3737,6 @@
     <t>Bridge Core Ontology – Zones Extension</t>
   </si>
   <si>
-    <t>https://w3id.org/bcore/zones</t>
-  </si>
-  <si>
     <t>The BCoreZones Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing spatial zones and environmental context around a bridge.
 It models regions, environmental areas, and contextual spatial relationships that help characterize where a bridge is situated and how it interacts with its surroundings.
 BCoreZones builds directly on BCore’s top‑level structure, ensuring that every spatial zone can be consistently linked to the bridge or its components. It integrates seamlessly with component, material, infrastructure, and media modules to support comprehensive, multi‑domain bridge modeling.</t>
@@ -3751,9 +3745,6 @@
     <t>Bridge Core Ontology – Infrastructure Extension</t>
   </si>
   <si>
-    <t>https://w3id.org/bcore/infra</t>
-  </si>
-  <si>
     <t>The BCoreInfra Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing bridge-related infrastructure.
 It models roads, railways, waterways, and other contextual infrastructure elements that interact with or influence the bridge. BCoreInfra builds directly on BCore’s top‑level structure, ensuring that every infrastructure element can be consistently linked to the bridge it serves or affects. It integrates seamlessly with component, material, media, and spatial‑zone modules to support comprehensive, multi‑domain bridge modeling.</t>
   </si>
@@ -3776,9 +3767,6 @@
     <t>bcorezones</t>
   </si>
   <si>
-    <t>https://w3id.org/bcore/mat</t>
-  </si>
-  <si>
     <t>The BCoreMat Ontology extends the Bridge Core Ontology (BCore) with a precise and modular vocabulary for describing materials used in bridge construction. It models concrete, steel, composites, coatings, and other material types, along with their properties and classifications. This enables consistent, semantically rich descriptions of what bridges and their components are made of. BCoreMat builds directly on BCore’s top‑level structure, ensuring that every material can be consistently linked to the bridge or its components. It integrates seamlessly with component, infrastructure, media, and spatial‑zone modules to support comprehensive, multi‑domain bridge modeling. #### BCore Ontology Suite: | Module | Purpose | |--------|---------| | BCore | Core identity, top‑level bridge concepts, and shared linking structure. | | BCoreComp | Structural and functional bridge components. | | BCoreMat | Materials used in bridge construction. | | BCoreInfra | Bridge-related transport and utility infrastructure. | | BCoreZones | Spatial zones, geometric context, and environmental regions. | | BCoreMedia | Media files, documentation, and digital assets. | #### About BCoreMat: BCoreMat provides a structured, extensible model for representing the various materials used in bridge construction. Main focus: - Material types such as concrete, steel, composites, and coatings - Material properties relevant for structural and durability assessment - Clear relationships between materials and bridge components - Consistent integration with BCore’s core identity and structure - Interoperability across all BCore modules → Thus, it is the right choice when you need to describe what a bridge is made of and how material information supports analysis, inspection, and lifecycle management.</t>
   </si>
   <si>
@@ -3788,9 +3776,6 @@
     <t>bcorecomp</t>
   </si>
   <si>
-    <t>https://w3id.org/bcore/comp</t>
-  </si>
-  <si>
     <t>The Bridge Core Ontology (BCore) enables the representation of a bridge structure, its components and material, as well as the infrastructure and media files connected to it and the environment and location of the bridge. BCore is created by the Institute of Concrete Structures (IMB) at the Dresden University of Technology (TUD). This ontology contains the corresponding components extension.</t>
   </si>
   <si>
@@ -3870,6 +3855,68 @@
   </si>
   <si>
     <t>saref, s4city, wgs84_pos</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/mat#</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/media#</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/zones#</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/infra#</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bcore/comp#</t>
+  </si>
+  <si>
+    <t>bcore, bmat</t>
+  </si>
+  <si>
+    <t>https://w3id.org/bmat</t>
+  </si>
+  <si>
+    <t>bmat</t>
+  </si>
+  <si>
+    <t>BMAT - Ontology for defining building materials.</t>
+  </si>
+  <si>
+    <t>https://alhakam.github.io/bmat/</t>
+  </si>
+  <si>
+    <t>Ontology for defining building materials.
+The suggested prefix for the BMAT namespace is bmat
+It is recommended to use BMAT in conjunction with BROT for defining a bridge construction and its aggregated components.</t>
+  </si>
+  <si>
+    <t>brcomp, brot</t>
+  </si>
+  <si>
+    <t>schema, foaf, vann, cd</t>
+  </si>
+  <si>
+    <t>he ontology for Bridge Components (BRCOMP) allows the further classification of Bridge Elements defined in BROT. Furthermore, additional domain-specific data properties can be assigned to the instances of Bridge Element.
+The namespace for BRCOMP terms is https://w3id.org//brcomp#
+The suggested prefix for the BRCOMP namespace is brcomp
+It is recommended to use BRCOMP in conjunction with BROT for defining a bridge construction and its aggregated components.</t>
+  </si>
+  <si>
+    <t>https://alhakam.github.io/brcomp/</t>
+  </si>
+  <si>
+    <t>https://w3id.org//brcomp#</t>
+  </si>
+  <si>
+    <t>brcomp</t>
+  </si>
+  <si>
+    <t>Bridge Components (BRCOMP)</t>
+  </si>
+  <si>
+    <t>vann, foaf, dc</t>
   </si>
 </sst>
 </file>
@@ -4161,8 +4208,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V157" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="A1:V157" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}" name="Table2" displayName="Table2" ref="A1:V159" totalsRowShown="0" headerRowDxfId="14">
+  <autoFilter ref="A1:V159" xr:uid="{EFE1469B-541D-4DB3-969C-63DB4F642030}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V157">
     <sortCondition ref="B1:B157"/>
   </sortState>
@@ -4579,7 +4626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6484B993-682B-477D-B31E-A58D58B7BF22}">
-  <dimension ref="A1:Z157"/>
+  <dimension ref="A1:Z159"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.5703125" customWidth="1"/>
@@ -5185,7 +5232,7 @@
         <v>1100</v>
       </c>
       <c r="B10" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>1101</v>
@@ -5218,7 +5265,7 @@
         <v>1105</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O10" s="32" t="s">
         <v>30</v>
@@ -5230,19 +5277,19 @@
     </row>
     <row r="11" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="B11" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>1127</v>
+        <v>1154</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>1099</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F11" s="29" t="s">
         <v>38</v>
@@ -5263,13 +5310,13 @@
         <v>131</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O11" s="32" t="s">
         <v>30</v>
@@ -5281,19 +5328,19 @@
     </row>
     <row r="12" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B12" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>1115</v>
+        <v>1153</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>1099</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F12" s="29" t="s">
         <v>38</v>
@@ -5311,13 +5358,13 @@
         <v>131</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O12" s="32" t="s">
         <v>30</v>
@@ -5329,19 +5376,19 @@
     </row>
     <row r="13" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B13" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>1123</v>
+        <v>1150</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>1099</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F13" s="29" t="s">
         <v>38</v>
@@ -5362,13 +5409,13 @@
         <v>131</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1117</v>
+        <v>1155</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O13" s="32" t="s">
         <v>30</v>
@@ -5383,10 +5430,10 @@
         <v>1106</v>
       </c>
       <c r="B14" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>1107</v>
+        <v>1151</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>1099</v>
@@ -5407,13 +5454,13 @@
         <v>131</v>
       </c>
       <c r="L14" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>1109</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>1110</v>
-      </c>
       <c r="N14" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O14" s="32" t="s">
         <v>30</v>
@@ -5425,19 +5472,19 @@
     </row>
     <row r="15" spans="1:22" ht="225" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B15" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>1112</v>
+        <v>1152</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>1099</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F15" s="29" t="s">
         <v>38</v>
@@ -5458,13 +5505,13 @@
         <v>131</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>83</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O15" s="32" t="s">
         <v>30</v>
@@ -5476,13 +5523,13 @@
     </row>
     <row r="16" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="B16" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="1"/>
@@ -5503,13 +5550,13 @@
         <v>131</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="O16" s="32" t="s">
         <v>30</v>
@@ -5521,13 +5568,13 @@
     </row>
     <row r="17" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="B17" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="D17" s="29" t="s">
         <v>38</v>
@@ -5543,7 +5590,7 @@
         <v>11</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="J17">
         <v>2025</v>
@@ -5552,13 +5599,13 @@
         <v>131</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="O17" s="32" t="s">
         <v>30</v>
@@ -5568,7 +5615,7 @@
       <c r="U17" s="32"/>
       <c r="V17" s="34"/>
     </row>
-    <row r="18" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -5633,7 +5680,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -5695,7 +5742,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="270" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>514</v>
       </c>
@@ -5754,7 +5801,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>64</v>
       </c>
@@ -5816,7 +5863,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -6059,7 +6106,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -6121,7 +6168,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -6183,7 +6230,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>95</v>
       </c>
@@ -6251,7 +6298,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>102</v>
       </c>
@@ -6348,7 +6395,7 @@
         <v>110</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="N30" s="3" t="s">
         <v>28</v>
@@ -6378,7 +6425,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -6443,7 +6490,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="300" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>564</v>
       </c>
@@ -6502,7 +6549,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -6567,7 +6614,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>122</v>
       </c>
@@ -6694,7 +6741,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>565</v>
       </c>
@@ -6756,7 +6803,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="37" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>124</v>
       </c>
@@ -6818,7 +6865,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>585</v>
       </c>
@@ -6942,7 +6989,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>129</v>
       </c>
@@ -7001,7 +7048,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>571</v>
       </c>
@@ -7063,7 +7110,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="42" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -7128,7 +7175,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="43" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>140</v>
       </c>
@@ -7190,7 +7237,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>146</v>
       </c>
@@ -7249,7 +7296,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="210" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>150</v>
       </c>
@@ -7311,7 +7358,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>156</v>
       </c>
@@ -7373,7 +7420,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>161</v>
       </c>
@@ -7497,7 +7544,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="49" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>138</v>
       </c>
@@ -7681,7 +7728,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="52" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>180</v>
       </c>
@@ -7743,7 +7790,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="53" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>185</v>
       </c>
@@ -7794,7 +7841,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="54" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" ht="210" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>187</v>
       </c>
@@ -7854,7 +7901,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" ht="180" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>189</v>
       </c>
@@ -7916,7 +7963,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="56" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>193</v>
       </c>
@@ -7981,7 +8028,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>616</v>
       </c>
@@ -8105,7 +8152,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" ht="360" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>201</v>
       </c>
@@ -8170,7 +8217,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="60" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>207</v>
       </c>
@@ -8335,10 +8382,10 @@
         <v>224</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="O62" s="32" t="s">
         <v>29</v>
@@ -8362,7 +8409,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="63" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>749</v>
       </c>
@@ -8421,7 +8468,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="64" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="s">
         <v>226</v>
       </c>
@@ -8483,7 +8530,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="65" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>231</v>
       </c>
@@ -8545,7 +8592,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="66" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>236</v>
       </c>
@@ -8734,7 +8781,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="69" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>254</v>
       </c>
@@ -8796,7 +8843,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="70" spans="1:22" ht="225" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="s">
         <v>648</v>
       </c>
@@ -8859,7 +8906,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="71" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>259</v>
       </c>
@@ -8986,7 +9033,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="73" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>756</v>
       </c>
@@ -9048,7 +9095,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="74" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>264</v>
       </c>
@@ -9110,7 +9157,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="75" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>520</v>
       </c>
@@ -9175,7 +9222,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>611</v>
       </c>
@@ -9240,7 +9287,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="77" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>613</v>
       </c>
@@ -9305,7 +9352,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="78" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>577</v>
       </c>
@@ -9362,7 +9409,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="79" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:22" ht="225" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>498</v>
       </c>
@@ -9425,7 +9472,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="80" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>535</v>
       </c>
@@ -9487,7 +9534,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="81" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>763</v>
       </c>
@@ -9549,7 +9596,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="82" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>270</v>
       </c>
@@ -9617,7 +9664,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="83" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>276</v>
       </c>
@@ -9679,7 +9726,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="84" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>281</v>
       </c>
@@ -9745,21 +9792,21 @@
         <v>985</v>
       </c>
     </row>
-    <row r="85" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="B85" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="C85" s="27" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="D85" s="7" t="s">
         <v>38</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="F85" s="29" t="s">
         <v>38</v>
@@ -9780,7 +9827,7 @@
         <v>131</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="N85" s="15"/>
       <c r="S85" s="33"/>
@@ -9788,7 +9835,7 @@
       <c r="U85" s="32"/>
       <c r="V85" s="34"/>
     </row>
-    <row r="86" spans="1:22" s="17" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:22" s="17" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>284</v>
       </c>
@@ -9917,7 +9964,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="88" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>291</v>
       </c>
@@ -9979,7 +10026,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="89" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>294</v>
       </c>
@@ -10041,7 +10088,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="90" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>300</v>
       </c>
@@ -10137,7 +10184,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="92" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>304</v>
       </c>
@@ -10199,7 +10246,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="93" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>309</v>
       </c>
@@ -10264,7 +10311,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="94" spans="1:22" ht="165" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>312</v>
       </c>
@@ -10326,7 +10373,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="95" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>316</v>
       </c>
@@ -10388,7 +10435,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="96" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>322</v>
       </c>
@@ -10512,7 +10559,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="98" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1077</v>
       </c>
@@ -10567,7 +10614,7 @@
       <c r="U98" s="32"/>
       <c r="V98" s="34"/>
     </row>
-    <row r="99" spans="1:26" ht="135" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>331</v>
       </c>
@@ -10629,7 +10676,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="100" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>547</v>
       </c>
@@ -10729,10 +10776,10 @@
         <v>865</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="O101" s="32" t="s">
         <v>29</v>
@@ -10756,7 +10803,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="150" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
         <v>529</v>
       </c>
@@ -10818,7 +10865,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="103" spans="1:26" ht="150" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>341</v>
       </c>
@@ -10880,7 +10927,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="104" spans="1:26" ht="285" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26" ht="120" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>345</v>
       </c>
@@ -10942,7 +10989,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="105" spans="1:26" ht="195" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:26" ht="165" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>349</v>
       </c>
@@ -11004,7 +11051,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="106" spans="1:26" ht="105" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:26" ht="75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>354</v>
       </c>
@@ -11066,7 +11113,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="107" spans="1:26" ht="90" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:26" ht="105" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>358</v>
       </c>
@@ -11190,7 +11237,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="109" spans="1:26" ht="165" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:26" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>366</v>
       </c>
@@ -11252,7 +11299,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="110" spans="1:26" ht="75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:26" ht="135" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>824</v>
       </c>
@@ -11379,7 +11426,7 @@
       </c>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="150" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:26" ht="90" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>375</v>
       </c>
@@ -11484,7 +11531,7 @@
       <c r="U113" s="32"/>
       <c r="V113" s="34"/>
     </row>
-    <row r="114" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>380</v>
       </c>
@@ -11546,7 +11593,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="115" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:22" ht="285" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>596</v>
       </c>
@@ -11605,7 +11652,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="116" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:22" ht="195" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>386</v>
       </c>
@@ -11667,7 +11714,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="117" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>388</v>
       </c>
@@ -11729,7 +11776,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="118" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>394</v>
       </c>
@@ -11791,7 +11838,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="119" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>416</v>
       </c>
@@ -11853,7 +11900,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="120" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:22" ht="165" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>421</v>
       </c>
@@ -11915,7 +11962,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="121" spans="1:22" ht="60" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>427</v>
       </c>
@@ -12040,7 +12087,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="123" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:22" ht="150" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
         <v>633</v>
       </c>
@@ -12105,7 +12152,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="124" spans="1:22" ht="150" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:22" ht="285" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>619</v>
       </c>
@@ -12170,7 +12217,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="125" spans="1:22" s="17" customFormat="1" ht="150" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>621</v>
       </c>
@@ -12236,7 +12283,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="126" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:22" ht="255" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
         <v>637</v>
       </c>
@@ -12299,7 +12346,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="127" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:22" ht="135" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>620</v>
       </c>
@@ -12364,7 +12411,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="128" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:22" s="17" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>625</v>
       </c>
@@ -12430,7 +12477,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="129" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:22" s="17" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>624</v>
       </c>
@@ -12496,7 +12543,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="130" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
         <v>641</v>
       </c>
@@ -12561,7 +12608,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="131" spans="1:22" ht="300" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>623</v>
       </c>
@@ -12626,7 +12673,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="132" spans="1:22" ht="270" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>627</v>
       </c>
@@ -12688,7 +12735,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="133" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>622</v>
       </c>
@@ -12753,7 +12800,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="134" spans="1:22" s="17" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:22" s="17" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
         <v>644</v>
       </c>
@@ -12881,7 +12928,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="136" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>436</v>
       </c>
@@ -13000,7 +13047,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="138" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>444</v>
       </c>
@@ -13128,7 +13175,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="140" spans="1:22" s="16" customFormat="1" ht="105" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:22" s="16" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>451</v>
       </c>
@@ -13194,7 +13241,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="141" spans="1:22" ht="105" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:22" ht="75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>543</v>
       </c>
@@ -13259,7 +13306,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="142" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:22" ht="300" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>455</v>
       </c>
@@ -13321,7 +13368,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="143" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:22" ht="270" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>458</v>
       </c>
@@ -13449,7 +13496,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="145" spans="1:22" ht="315" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>217</v>
       </c>
@@ -13508,7 +13555,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="146" spans="1:22" ht="315" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>468</v>
       </c>
@@ -13570,7 +13617,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="147" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>472</v>
       </c>
@@ -13632,7 +13679,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="148" spans="1:22" ht="240" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>475</v>
       </c>
@@ -13697,7 +13744,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="120" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>478</v>
       </c>
@@ -13759,7 +13806,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="150" spans="1:22" ht="255" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>566</v>
       </c>
@@ -13821,7 +13868,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="151" spans="1:22" ht="225" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:22" ht="105" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>481</v>
       </c>
@@ -13883,7 +13930,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="152" spans="1:22" ht="210" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>484</v>
       </c>
@@ -13945,7 +13992,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="153" spans="1:22" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>523</v>
       </c>
@@ -14007,7 +14054,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="154" spans="1:22" ht="135" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:22" ht="120" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>487</v>
       </c>
@@ -14102,10 +14149,10 @@
         <v>1046</v>
       </c>
       <c r="M155" s="3" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="N155" s="3" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="O155" s="32" t="s">
         <v>29</v>
@@ -14129,7 +14176,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="156" spans="1:22" ht="345" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:22" ht="315" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>734</v>
       </c>
@@ -14241,6 +14288,91 @@
       <c r="T157" s="32"/>
       <c r="U157" s="32"/>
       <c r="V157" s="34"/>
+    </row>
+    <row r="158" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C158" s="27" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F158" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G158" t="s">
+        <v>11</v>
+      </c>
+      <c r="I158" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="L158" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="M158" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="N158" s="15" t="s">
+        <v>1162</v>
+      </c>
+      <c r="O158" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S158" s="33"/>
+      <c r="T158" s="32"/>
+      <c r="U158" s="32"/>
+      <c r="V158" s="34"/>
+    </row>
+    <row r="159" spans="1:22" ht="180" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C159" s="27" t="s">
+        <v>1165</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F159" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="G159" t="s">
+        <v>1</v>
+      </c>
+      <c r="H159" s="1"/>
+      <c r="I159" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="L159" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="M159" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="N159" s="15" t="s">
+        <v>1168</v>
+      </c>
+      <c r="O159" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S159" s="33"/>
+      <c r="T159" s="32"/>
+      <c r="U159" s="32"/>
+      <c r="V159" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -14509,12 +14641,16 @@
     <hyperlink ref="C16" r:id="rId262" xr:uid="{1C6A0EA2-A8D6-4C7E-8833-72CD216F91B6}"/>
     <hyperlink ref="C85" r:id="rId263" xr:uid="{3EAB1B23-E180-46E2-9E59-CF59E174BE8D}"/>
     <hyperlink ref="E85" r:id="rId264" xr:uid="{9C03D4EC-81F8-4A0E-AE28-7FCE9FEC76F3}"/>
+    <hyperlink ref="C158" r:id="rId265" xr:uid="{F18D5489-B8E3-498D-8754-A7EFD69CA755}"/>
+    <hyperlink ref="E158" r:id="rId266" xr:uid="{67F2FA68-03F0-4457-B9F2-784DD703595B}"/>
+    <hyperlink ref="E159" r:id="rId267" xr:uid="{04870334-A1AD-48DB-ADAC-FB5BD11031A6}"/>
+    <hyperlink ref="C159" r:id="rId268" xr:uid="{366A4D26-021B-4981-B78E-49DB8CD72564}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId265"/>
-  <legacyDrawing r:id="rId266"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId269"/>
+  <legacyDrawing r:id="rId270"/>
   <tableParts count="1">
-    <tablePart r:id="rId267"/>
+    <tablePart r:id="rId271"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -14523,7 +14659,7 @@
           <x14:formula1>
             <xm:f>Domains!$A$2:$A$28</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H157</xm:sqref>
+          <xm:sqref>G2:H2 G4:H53 G55:H62 G64:H69 G71:H158 G159</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
